--- a/examples/HO_SO_CAU_KM19_529/03_KINH_TE_QS_DU_TOAN_THANH_TOAN/09_Thanh_Toan_Khoi_Luong_Phu_Luc_03a.xlsx
+++ b/examples/HO_SO_CAU_KM19_529/03_KINH_TE_QS_DU_TOAN_THANH_TOAN/09_Thanh_Toan_Khoi_Luong_Phu_Luc_03a.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="THANH_TOAN_KY_PHU_LUC_03A" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QS_DIEN_GIAI_CHI_TIET" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NGHI_VAN" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,8 +63,20 @@
       <b val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -100,8 +113,23 @@
         <bgColor rgb="00F9FAFB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F497D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -181,11 +209,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00999999"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -258,6 +300,31 @@
     <xf numFmtId="4" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -623,7 +690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A2:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -638,9 +705,9 @@
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="70" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -662,7 +729,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
@@ -732,6 +798,11 @@
           <t>Ghi chú</t>
         </is>
       </c>
+      <c r="M6" s="34" t="inlineStr">
+        <is>
+          <t>NGHI VẤN (soát &amp; ghim)</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -792,6 +863,11 @@
           <t>Nghiệm thu 100% 26 cọc</t>
         </is>
       </c>
+      <c r="M8" s="35" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D8*1.0). Ghi chú cột L 'Nghiệm thu 100% 26 cọc' là số cũ, không cập nhật theo D — soát lại</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
@@ -809,12 +885,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D9" s="8">
-        <f>QS_DIEN_GIAI_CHI_TIET!J13</f>
-        <v/>
-      </c>
-      <c r="E9" s="9">
-        <f>QS_DIEN_GIAI_CHI_TIET!K13</f>
+      <c r="D9" s="36">
+        <f>QS_DIEN_GIAI_CHI_TIET!J12</f>
+        <v/>
+      </c>
+      <c r="E9" s="37">
+        <f>QS_DIEN_GIAI_CHI_TIET!K12</f>
         <v/>
       </c>
       <c r="F9" s="9">
@@ -845,6 +921,11 @@
           <t>Luân chuyển hoàn thành</t>
         </is>
       </c>
+      <c r="M9" s="35" t="inlineStr">
+        <is>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J13 → =QS_DIEN_GIAI_CHI_TIET!J12 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0) | Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D9*1.0)</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
@@ -862,12 +943,12 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="D10" s="8">
-        <f>QS_DIEN_GIAI_CHI_TIET!J18</f>
-        <v/>
-      </c>
-      <c r="E10" s="9">
-        <f>QS_DIEN_GIAI_CHI_TIET!K18</f>
+      <c r="D10" s="36">
+        <f>QS_DIEN_GIAI_CHI_TIET!J17</f>
+        <v/>
+      </c>
+      <c r="E10" s="37">
+        <f>QS_DIEN_GIAI_CHI_TIET!K17</f>
         <v/>
       </c>
       <c r="F10" s="9">
@@ -898,6 +979,11 @@
           <t>Đổ xong 1100.86 m3</t>
         </is>
       </c>
+      <c r="M10" s="35" t="inlineStr">
+        <is>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J18 → =QS_DIEN_GIAI_CHI_TIET!J17 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0) | Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D10*1.0). Ghi chú cột L 'Đổ xong 1100.86 m3' là số cũ, không cập nhật theo D — soát lại</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
@@ -915,12 +1001,12 @@
           <t>Tấn</t>
         </is>
       </c>
-      <c r="D11" s="8">
-        <f>QS_DIEN_GIAI_CHI_TIET!J23</f>
-        <v/>
-      </c>
-      <c r="E11" s="9">
-        <f>QS_DIEN_GIAI_CHI_TIET!K23</f>
+      <c r="D11" s="36">
+        <f>QS_DIEN_GIAI_CHI_TIET!J22</f>
+        <v/>
+      </c>
+      <c r="E11" s="37">
+        <f>QS_DIEN_GIAI_CHI_TIET!K22</f>
         <v/>
       </c>
       <c r="F11" s="9">
@@ -951,6 +1037,11 @@
           <t>118.98 tấn</t>
         </is>
       </c>
+      <c r="M11" s="35" t="inlineStr">
+        <is>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J23 → =QS_DIEN_GIAI_CHI_TIET!J22 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0) | Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D11*1.0). Ghi chú cột L '118.98 tấn' là số cũ, không cập nhật theo D — soát lại</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
@@ -968,12 +1059,12 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="D12" s="8">
-        <f>QS_DIEN_GIAI_CHI_TIET!J28</f>
-        <v/>
-      </c>
-      <c r="E12" s="9">
-        <f>QS_DIEN_GIAI_CHI_TIET!K28</f>
+      <c r="D12" s="36">
+        <f>QS_DIEN_GIAI_CHI_TIET!J27</f>
+        <v/>
+      </c>
+      <c r="E12" s="37">
+        <f>QS_DIEN_GIAI_CHI_TIET!K27</f>
         <v/>
       </c>
       <c r="F12" s="9">
@@ -1004,6 +1095,11 @@
           <t>Đập đầu cọc xong</t>
         </is>
       </c>
+      <c r="M12" s="35" t="inlineStr">
+        <is>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J28 → =QS_DIEN_GIAI_CHI_TIET!J27 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0) | Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D12*1.0)</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
@@ -1021,12 +1117,12 @@
           <t>Gói</t>
         </is>
       </c>
-      <c r="D13" s="8">
-        <f>QS_DIEN_GIAI_CHI_TIET!J30</f>
-        <v/>
-      </c>
-      <c r="E13" s="9">
-        <f>QS_DIEN_GIAI_CHI_TIET!K30</f>
+      <c r="D13" s="36">
+        <f>QS_DIEN_GIAI_CHI_TIET!J29</f>
+        <v/>
+      </c>
+      <c r="E13" s="37">
+        <f>QS_DIEN_GIAI_CHI_TIET!K29</f>
         <v/>
       </c>
       <c r="F13" s="9">
@@ -1057,6 +1153,11 @@
           <t>Đạt kết quả kiểm tra</t>
         </is>
       </c>
+      <c r="M13" s="35" t="inlineStr">
+        <is>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J30 → =QS_DIEN_GIAI_CHI_TIET!J29 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0) | Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D13*1.0)</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
@@ -1117,6 +1218,11 @@
           <t>Nghiệm thu hố móng</t>
         </is>
       </c>
+      <c r="M15" s="35" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D15*1.0)</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
@@ -1170,6 +1276,11 @@
           <t>Đổ xong 4 hố móng</t>
         </is>
       </c>
+      <c r="M16" s="35" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D16*1.0). Ghi chú cột L 'Đổ xong 4 hố móng' là số cũ, không cập nhật theo D — soát lại</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
@@ -1187,12 +1298,12 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="D17" s="8">
-        <f>QS_DIEN_GIAI_CHI_TIET!J37</f>
-        <v/>
-      </c>
-      <c r="E17" s="9">
-        <f>QS_DIEN_GIAI_CHI_TIET!K37</f>
+      <c r="D17" s="36">
+        <f>QS_DIEN_GIAI_CHI_TIET!J39</f>
+        <v/>
+      </c>
+      <c r="E17" s="37">
+        <f>QS_DIEN_GIAI_CHI_TIET!K39</f>
         <v/>
       </c>
       <c r="F17" s="9">
@@ -1223,6 +1334,11 @@
           <t>517.48 m3 đạt R28</t>
         </is>
       </c>
+      <c r="M17" s="35" t="inlineStr">
+        <is>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J37 → =QS_DIEN_GIAI_CHI_TIET!J39 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0) | Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D17*1.0). Ghi chú cột L '517.48 m3 đạt R28' là số cũ, không cập nhật theo D — soát lại</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
@@ -1240,12 +1356,12 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="D18" s="8">
-        <f>QS_DIEN_GIAI_CHI_TIET!J42</f>
-        <v/>
-      </c>
-      <c r="E18" s="9">
-        <f>QS_DIEN_GIAI_CHI_TIET!K42</f>
+      <c r="D18" s="36">
+        <f>QS_DIEN_GIAI_CHI_TIET!J44</f>
+        <v/>
+      </c>
+      <c r="E18" s="37">
+        <f>QS_DIEN_GIAI_CHI_TIET!K44</f>
         <v/>
       </c>
       <c r="F18" s="9">
@@ -1276,6 +1392,11 @@
           <t>Nghiệm thu đợt 1 thân mố</t>
         </is>
       </c>
+      <c r="M18" s="35" t="inlineStr">
+        <is>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J42 → =QS_DIEN_GIAI_CHI_TIET!J44 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0) | Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D18*0.8). Ghi chú cột L 'Nghiệm thu đợt 1 thân mố' là số cũ, không cập nhật theo D — soát lại</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
@@ -1285,7 +1406,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Bê tông thân đặc trụ T1 và T2 mác C30 (H=14.5m &amp; 11.4m)</t>
+          <t>Bê tông thân đặc trụ T1 và T2 mác C30</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -1293,12 +1414,12 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="D19" s="8">
-        <f>QS_DIEN_GIAI_CHI_TIET!J47</f>
-        <v/>
-      </c>
-      <c r="E19" s="9">
-        <f>QS_DIEN_GIAI_CHI_TIET!K47</f>
+      <c r="D19" s="36">
+        <f>QS_DIEN_GIAI_CHI_TIET!J50</f>
+        <v/>
+      </c>
+      <c r="E19" s="37">
+        <f>QS_DIEN_GIAI_CHI_TIET!K50</f>
         <v/>
       </c>
       <c r="F19" s="9">
@@ -1329,6 +1450,11 @@
           <t>Đổ 3/4 chiều cao trụ</t>
         </is>
       </c>
+      <c r="M19" s="35" t="inlineStr">
+        <is>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J47 → =QS_DIEN_GIAI_CHI_TIET!J50 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0) | Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D19*0.75). Ghi chú cột L 'Đổ 3/4 chiều cao trụ' là số cũ, không cập nhật theo D — soát lại</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
@@ -1346,12 +1472,12 @@
           <t>Tấn</t>
         </is>
       </c>
-      <c r="D20" s="8">
-        <f>QS_DIEN_GIAI_CHI_TIET!J53</f>
-        <v/>
-      </c>
-      <c r="E20" s="9">
-        <f>QS_DIEN_GIAI_CHI_TIET!K53</f>
+      <c r="D20" s="36">
+        <f>QS_DIEN_GIAI_CHI_TIET!J56</f>
+        <v/>
+      </c>
+      <c r="E20" s="37">
+        <f>QS_DIEN_GIAI_CHI_TIET!K56</f>
         <v/>
       </c>
       <c r="F20" s="9">
@@ -1382,6 +1508,11 @@
           <t>Lắp dựng nghiệm thu đợt 1</t>
         </is>
       </c>
+      <c r="M20" s="35" t="inlineStr">
+        <is>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J53 → =QS_DIEN_GIAI_CHI_TIET!J56 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0) | Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D20*0.8). Ghi chú cột L 'Lắp dựng nghiệm thu đợt 1' là số cũ, không cập nhật theo D — soát lại</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
@@ -1406,12 +1537,12 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="D22" s="8">
-        <f>QS_DIEN_GIAI_CHI_TIET!J57</f>
-        <v/>
-      </c>
-      <c r="E22" s="9">
-        <f>QS_DIEN_GIAI_CHI_TIET!K57</f>
+      <c r="D22" s="36">
+        <f>QS_DIEN_GIAI_CHI_TIET!J62</f>
+        <v/>
+      </c>
+      <c r="E22" s="37">
+        <f>QS_DIEN_GIAI_CHI_TIET!K62</f>
         <v/>
       </c>
       <c r="F22" s="9">
@@ -1442,6 +1573,11 @@
           <t>Đúc xong 9/15 phiến dầm</t>
         </is>
       </c>
+      <c r="M22" s="35" t="inlineStr">
+        <is>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J57 → =QS_DIEN_GIAI_CHI_TIET!J62 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0) | Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D22*0.6). Ghi chú cột L 'Đúc xong 9/15 phiến dầm' là số cũ, không cập nhật theo D — soát lại</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
@@ -1459,12 +1595,12 @@
           <t>Tấn</t>
         </is>
       </c>
-      <c r="D23" s="8">
-        <f>QS_DIEN_GIAI_CHI_TIET!J59</f>
-        <v/>
-      </c>
-      <c r="E23" s="9">
-        <f>QS_DIEN_GIAI_CHI_TIET!K59</f>
+      <c r="D23" s="36">
+        <f>QS_DIEN_GIAI_CHI_TIET!J64</f>
+        <v/>
+      </c>
+      <c r="E23" s="37">
+        <f>QS_DIEN_GIAI_CHI_TIET!K64</f>
         <v/>
       </c>
       <c r="F23" s="9">
@@ -1495,6 +1631,11 @@
           <t>Căng kéo 9 phiến dầm</t>
         </is>
       </c>
+      <c r="M23" s="35" t="inlineStr">
+        <is>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J59 → =QS_DIEN_GIAI_CHI_TIET!J64 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0) | Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D23*0.6). Ghi chú cột L 'Căng kéo 9 phiến dầm' là số cũ, không cập nhật theo D — soát lại</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
@@ -1512,12 +1653,12 @@
           <t>Tấn</t>
         </is>
       </c>
-      <c r="D24" s="8">
-        <f>QS_DIEN_GIAI_CHI_TIET!J61</f>
-        <v/>
-      </c>
-      <c r="E24" s="9">
-        <f>QS_DIEN_GIAI_CHI_TIET!K61</f>
+      <c r="D24" s="36">
+        <f>QS_DIEN_GIAI_CHI_TIET!J66</f>
+        <v/>
+      </c>
+      <c r="E24" s="37">
+        <f>QS_DIEN_GIAI_CHI_TIET!K66</f>
         <v/>
       </c>
       <c r="F24" s="9">
@@ -1548,6 +1689,11 @@
           <t>9 phiến dầm</t>
         </is>
       </c>
+      <c r="M24" s="35" t="inlineStr">
+        <is>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J61 → =QS_DIEN_GIAI_CHI_TIET!J66 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0) | Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D24*0.6). Ghi chú cột L '9 phiến dầm' là số cũ, không cập nhật theo D — soát lại</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
@@ -1565,12 +1711,12 @@
           <t>Phiến</t>
         </is>
       </c>
-      <c r="D25" s="8">
-        <f>QS_DIEN_GIAI_CHI_TIET!J63</f>
-        <v/>
-      </c>
-      <c r="E25" s="9">
-        <f>QS_DIEN_GIAI_CHI_TIET!K63</f>
+      <c r="D25" s="36">
+        <f>QS_DIEN_GIAI_CHI_TIET!J68</f>
+        <v/>
+      </c>
+      <c r="E25" s="37">
+        <f>QS_DIEN_GIAI_CHI_TIET!K68</f>
         <v/>
       </c>
       <c r="F25" s="9">
@@ -1601,6 +1747,11 @@
           <t>Kỳ sau thực hiện</t>
         </is>
       </c>
+      <c r="M25" s="35" t="inlineStr">
+        <is>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J63 → =QS_DIEN_GIAI_CHI_TIET!J68 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0) | Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D25*0.0)</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
@@ -1618,12 +1769,12 @@
           <t>Cái</t>
         </is>
       </c>
-      <c r="D26" s="8">
-        <f>QS_DIEN_GIAI_CHI_TIET!J65</f>
-        <v/>
-      </c>
-      <c r="E26" s="9">
-        <f>QS_DIEN_GIAI_CHI_TIET!K65</f>
+      <c r="D26" s="36">
+        <f>QS_DIEN_GIAI_CHI_TIET!J70</f>
+        <v/>
+      </c>
+      <c r="E26" s="37">
+        <f>QS_DIEN_GIAI_CHI_TIET!K70</f>
         <v/>
       </c>
       <c r="F26" s="9">
@@ -1654,6 +1805,11 @@
           <t>Kỳ sau thực hiện</t>
         </is>
       </c>
+      <c r="M26" s="35" t="inlineStr">
+        <is>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J65 → =QS_DIEN_GIAI_CHI_TIET!J70 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0) | Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D26*0.0)</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
@@ -1671,12 +1827,12 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="D27" s="8">
-        <f>QS_DIEN_GIAI_CHI_TIET!J74</f>
-        <v/>
-      </c>
-      <c r="E27" s="9">
-        <f>QS_DIEN_GIAI_CHI_TIET!K74</f>
+      <c r="D27" s="36">
+        <f>QS_DIEN_GIAI_CHI_TIET!J77+QS_DIEN_GIAI_CHI_TIET!J79</f>
+        <v/>
+      </c>
+      <c r="E27" s="37">
+        <f>(QS_DIEN_GIAI_CHI_TIET!L77+QS_DIEN_GIAI_CHI_TIET!L79)/D27</f>
         <v/>
       </c>
       <c r="F27" s="9">
@@ -1705,6 +1861,11 @@
       <c r="L27" s="7" t="inlineStr">
         <is>
           <t>Kỳ sau thực hiện</t>
+        </is>
+      </c>
+      <c r="M27" s="35" t="inlineStr">
+        <is>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J74 → =QS_DIEN_GIAI_CHI_TIET!J77+QS_DIEN_GIAI_CHI_TIET!J79 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0) | Gộp bản mặt cầu (QS dòng 77) và liên tục nhiệt (QS dòng 79); đơn giá = bình quân gia quyền theo thành tiền 2 dòng. | Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D27*0.0)</t>
         </is>
       </c>
     </row>
@@ -1734,8 +1895,12 @@
         <v/>
       </c>
       <c r="L28" s="14" t="n"/>
-    </row>
-    <row r="29"/>
+      <c r="M28" s="35" t="inlineStr">
+        <is>
+          <t>Chưa có trong 03a: bê tông tường đỉnh/tường cánh mố, xà mũ trụ, dầm ngang, bản quá độ và các hạng mục hoàn thiện (QS dòng 47, 53, 73, 86...) — kiểm tra phạm vi hợp đồng.</t>
+        </is>
+      </c>
+    </row>
     <row r="30" ht="24" customHeight="1">
       <c r="B30" s="2" t="inlineStr">
         <is>
@@ -1846,7 +2011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:N101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1861,9 +2026,17 @@
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="70" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1">
+      <c r="A1" s="38" t="inlineStr">
+        <is>
+          <t>ĐÃ SỬA THEO BẢN VẼ THẨM ĐỊNH ngày 11/10/2026 — ô vàng: số theo bản vẽ; cột M: NGHI VẤN; cột N: khối lượng cũ. Xem sheet NGHI_VAN để soát và ghim.</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1952,6 +2125,16 @@
         <is>
           <t>Thành tiền
 (VNĐ)</t>
+        </is>
+      </c>
+      <c r="M5" s="39" t="inlineStr">
+        <is>
+          <t>NGHI VẤN (soát &amp; ghim)</t>
+        </is>
+      </c>
+      <c r="N5" s="39" t="inlineStr">
+        <is>
+          <t>Khối lượng cũ (trước sửa)</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2544,7 @@
       <c r="B18" s="26" t="n"/>
       <c r="C18" s="27" t="inlineStr">
         <is>
-          <t>- Bê tông 3 cọc mố M1 (L=20m, D=1.2m, hs nở thành 1.12)</t>
+          <t>- Bê tông 3 cọc mố M1 L=20m (bản vẽ tr.64, gồm bê tông đầu cọc)</t>
         </is>
       </c>
       <c r="D18" s="28" t="inlineStr">
@@ -2369,34 +2552,42 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="E18" s="29" t="n">
+      <c r="E18" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="29" t="n">
-        <v>20</v>
-      </c>
-      <c r="G18" s="29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H18" s="29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I18" s="30" t="n">
-        <v>3.5186</v>
-      </c>
-      <c r="J18" s="31">
+      <c r="F18" s="36" t="n">
+        <v>23.58</v>
+      </c>
+      <c r="G18" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="41">
         <f>E18*F18*G18*H18*I18</f>
         <v/>
       </c>
       <c r="K18" s="26" t="n"/>
       <c r="L18" s="26" t="n"/>
+      <c r="M18" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 76,002 → 70,740. Bỏ hệ số I = 3,5186 (π × 1,12 nở thành): lấy thể tích thiết kế tr.64. Nếu hợp đồng cho tính nở thành thì ghim lại hệ số.</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>76.002</v>
+      </c>
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="26" t="n"/>
       <c r="B19" s="26" t="n"/>
       <c r="C19" s="27" t="inlineStr">
         <is>
-          <t>- Bê tông 8 cọc trụ T1 (L=40m, D=1.2m, hs nở thành 1.12)</t>
+          <t>- Bê tông 8 cọc trụ T1 L=40m (bản vẽ tr.68, gồm bê tông đầu cọc)</t>
         </is>
       </c>
       <c r="D19" s="28" t="inlineStr">
@@ -2404,34 +2595,42 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="E19" s="29" t="n">
+      <c r="E19" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="F19" s="29" t="n">
-        <v>40</v>
-      </c>
-      <c r="G19" s="29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H19" s="29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I19" s="30" t="n">
-        <v>3.5186</v>
-      </c>
-      <c r="J19" s="31">
+      <c r="F19" s="36" t="n">
+        <v>45.88</v>
+      </c>
+      <c r="G19" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="41">
         <f>E19*F19*G19*H19*I19</f>
         <v/>
       </c>
       <c r="K19" s="26" t="n"/>
       <c r="L19" s="26" t="n"/>
+      <c r="M19" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 405,343 → 367,040. Bỏ hệ số nở thành 3,5186 — lấy thể tích thiết kế tr.68.</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>405.343</v>
+      </c>
     </row>
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="26" t="n"/>
       <c r="B20" s="26" t="n"/>
       <c r="C20" s="27" t="inlineStr">
         <is>
-          <t>- Bê tông 8 cọc trụ T2 (L=30m, D=1.2m, hs nở thành 1.12)</t>
+          <t>- Bê tông 8 cọc trụ T2 L=30m (bản vẽ tr.70, gồm bê tông đầu cọc)</t>
         </is>
       </c>
       <c r="D20" s="28" t="inlineStr">
@@ -2439,34 +2638,42 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="E20" s="29" t="n">
+      <c r="E20" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="F20" s="29" t="n">
-        <v>30</v>
-      </c>
-      <c r="G20" s="29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H20" s="29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I20" s="30" t="n">
-        <v>3.5186</v>
-      </c>
-      <c r="J20" s="31">
+      <c r="F20" s="36" t="n">
+        <v>34.73</v>
+      </c>
+      <c r="G20" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="41">
         <f>E20*F20*G20*H20*I20</f>
         <v/>
       </c>
       <c r="K20" s="26" t="n"/>
       <c r="L20" s="26" t="n"/>
+      <c r="M20" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 304,007 → 277,840. Bỏ hệ số nở thành 3,5186 — lấy thể tích thiết kế tr.70.</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>304.007</v>
+      </c>
     </row>
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="26" t="n"/>
       <c r="B21" s="26" t="n"/>
       <c r="C21" s="27" t="inlineStr">
         <is>
-          <t>- Bê tông 7 cọc mố M2 (L=36m, D=1.2m, hs nở thành 1.12)</t>
+          <t>- Bê tông 7 cọc mố M2 L=36m (bản vẽ tr.66, gồm bê tông đầu cọc)</t>
         </is>
       </c>
       <c r="D21" s="28" t="inlineStr">
@@ -2474,27 +2681,35 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="E21" s="29" t="n">
+      <c r="E21" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="F21" s="29" t="n">
-        <v>36</v>
-      </c>
-      <c r="G21" s="29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H21" s="29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I21" s="30" t="n">
-        <v>3.5186</v>
-      </c>
-      <c r="J21" s="31">
+      <c r="F21" s="36" t="n">
+        <v>41.56</v>
+      </c>
+      <c r="G21" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="41">
         <f>E21*F21*G21*H21*I21</f>
         <v/>
       </c>
       <c r="K21" s="26" t="n"/>
       <c r="L21" s="26" t="n"/>
+      <c r="M21" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 319,207 → 290,920. Bỏ hệ số nở thành 3,5186 — lấy thể tích thiết kế tr.66.</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>319.207</v>
+      </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="23" t="inlineStr">
@@ -2522,8 +2737,9 @@
       <c r="G22" s="18" t="n"/>
       <c r="H22" s="18" t="n"/>
       <c r="I22" s="18" t="n"/>
-      <c r="J22" s="32" t="n">
-        <v>108.76599036</v>
+      <c r="J22" s="42">
+        <f>SUM(J23:J26)</f>
+        <v/>
       </c>
       <c r="K22" s="19" t="n">
         <v>18500000</v>
@@ -2531,6 +2747,14 @@
       <c r="L22" s="25">
         <f>J22*K22</f>
         <v/>
+      </c>
+      <c r="M22" s="35" t="inlineStr">
+        <is>
+          <t>Tiêu đề ghi cứng 108,766 — đổi thành tổng các dòng diễn giải (=SUM(J23:J26))</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>108.76599036</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
@@ -2538,7 +2762,7 @@
       <c r="B23" s="26" t="n"/>
       <c r="C23" s="27" t="inlineStr">
         <is>
-          <t>- Cốt thép cọc mố M1 (3 cọc x 5.889 tấn/cọc)</t>
+          <t>- Cốt thép cọc mố M1 (3 cọc, bản vẽ tr.64 tấn/cọc)</t>
         </is>
       </c>
       <c r="D23" s="28" t="inlineStr">
@@ -2546,34 +2770,42 @@
           <t>Tấn</t>
         </is>
       </c>
-      <c r="E23" s="29" t="n">
+      <c r="E23" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="F23" s="29" t="n">
-        <v>5.889</v>
-      </c>
-      <c r="G23" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="31">
+      <c r="F23" s="36" t="n">
+        <v>2.50753</v>
+      </c>
+      <c r="G23" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="41">
         <f>E23*F23*G23*H23*I23</f>
         <v/>
       </c>
       <c r="K23" s="26" t="n"/>
       <c r="L23" s="26" t="n"/>
+      <c r="M23" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 17,667 → 7,523</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>17.667</v>
+      </c>
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="26" t="n"/>
       <c r="B24" s="26" t="n"/>
       <c r="C24" s="27" t="inlineStr">
         <is>
-          <t>- Cốt thép cọc trụ T1 (8 cọc x 4.845 tấn/cọc)</t>
+          <t>- Cốt thép cọc trụ T1 (8 cọc, bản vẽ tr.68 tấn/cọc)</t>
         </is>
       </c>
       <c r="D24" s="28" t="inlineStr">
@@ -2581,34 +2813,42 @@
           <t>Tấn</t>
         </is>
       </c>
-      <c r="E24" s="29" t="n">
+      <c r="E24" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="F24" s="29" t="n">
-        <v>4.845</v>
-      </c>
-      <c r="G24" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="31">
+      <c r="F24" s="36" t="n">
+        <v>4.82866</v>
+      </c>
+      <c r="G24" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="41">
         <f>E24*F24*G24*H24*I24</f>
         <v/>
       </c>
       <c r="K24" s="26" t="n"/>
       <c r="L24" s="26" t="n"/>
+      <c r="M24" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 38,760 → 38,629</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>38.76</v>
+      </c>
     </row>
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="26" t="n"/>
       <c r="B25" s="26" t="n"/>
       <c r="C25" s="27" t="inlineStr">
         <is>
-          <t>- Cốt thép cọc trụ T2 (8 cọc x 3.687 tấn/cọc)</t>
+          <t>- Cốt thép cọc trụ T2 (8 cọc, bản vẽ tr.70 tấn/cọc)</t>
         </is>
       </c>
       <c r="D25" s="28" t="inlineStr">
@@ -2616,34 +2856,42 @@
           <t>Tấn</t>
         </is>
       </c>
-      <c r="E25" s="29" t="n">
+      <c r="E25" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="F25" s="29" t="n">
-        <v>3.687</v>
-      </c>
-      <c r="G25" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="31">
+      <c r="F25" s="36" t="n">
+        <v>3.67107</v>
+      </c>
+      <c r="G25" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="41">
         <f>E25*F25*G25*H25*I25</f>
         <v/>
       </c>
       <c r="K25" s="26" t="n"/>
       <c r="L25" s="26" t="n"/>
+      <c r="M25" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 29,496 → 29,369</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>29.496</v>
+      </c>
     </row>
     <row r="26" ht="19" customHeight="1">
       <c r="A26" s="26" t="n"/>
       <c r="B26" s="26" t="n"/>
       <c r="C26" s="27" t="inlineStr">
         <is>
-          <t>- Cốt thép cọc mố M2 (7 cọc x 4.721 tấn/cọc)</t>
+          <t>- Cốt thép cọc mố M2 (7 cọc, bản vẽ tr.66 tấn/cọc)</t>
         </is>
       </c>
       <c r="D26" s="28" t="inlineStr">
@@ -2651,27 +2899,35 @@
           <t>Tấn</t>
         </is>
       </c>
-      <c r="E26" s="29" t="n">
+      <c r="E26" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="F26" s="29" t="n">
-        <v>4.721</v>
-      </c>
-      <c r="G26" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="31">
+      <c r="F26" s="36" t="n">
+        <v>4.70588</v>
+      </c>
+      <c r="G26" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="41">
         <f>E26*F26*G26*H26*I26</f>
         <v/>
       </c>
       <c r="K26" s="26" t="n"/>
       <c r="L26" s="26" t="n"/>
+      <c r="M26" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 33,047 → 32,941. Tổng 4 trang cọc 108,462 t; bảng tổng hợp tr.175 ghi 108,884 t (nhóm 10&lt;D&lt;=18: 0,982 t so với 0,559 t trên các trang cọc) — xem PDF tr.175.</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>33.047</v>
+      </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="23" t="inlineStr">
@@ -2716,7 +2972,7 @@
       <c r="B28" s="26" t="n"/>
       <c r="C28" s="27" t="inlineStr">
         <is>
-          <t>- Đập đầu 26 cọc khoan nhồi (chiều cao đập h=1.0m)</t>
+          <t>- Đập đầu 26 cọc (bản vẽ tr.64/66/68/70: 3×M1 + 8×T1 + 8×T2 + 7×M2)</t>
         </is>
       </c>
       <c r="D28" s="28" t="inlineStr">
@@ -2724,27 +2980,36 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="E28" s="29" t="n">
-        <v>26</v>
-      </c>
-      <c r="F28" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H28" s="29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I28" s="30" t="n">
-        <v>3.1416</v>
-      </c>
-      <c r="J28" s="31">
+      <c r="E28" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="36">
+        <f>3*1.13+8*1.13+8*1.13+7*1.27</f>
+        <v/>
+      </c>
+      <c r="G28" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="41">
         <f>E28*F28*G28*H28*I28</f>
         <v/>
       </c>
       <c r="K28" s="26" t="n"/>
       <c r="L28" s="26" t="n"/>
+      <c r="M28" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 29,405 → 30,360</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>29.405</v>
+      </c>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="23" t="inlineStr">
@@ -2897,6 +3162,11 @@
       </c>
       <c r="K33" s="26" t="n"/>
       <c r="L33" s="26" t="n"/>
+      <c r="M33" s="35" t="inlineStr">
+        <is>
+          <t>Khối lượng đào lấy từ sheet đào đắp (6.245 m³) — chưa đối chiếu bản vẽ.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="23" t="inlineStr">
@@ -2941,7 +3211,7 @@
       <c r="B35" s="26" t="n"/>
       <c r="C35" s="27" t="inlineStr">
         <is>
-          <t>- Lớp bê tông lót đáy bệ mố M1 chân dê</t>
+          <t>- Bê tông đệm C10 mố M1 (bản vẽ tr.31)</t>
         </is>
       </c>
       <c r="D35" s="28" t="inlineStr">
@@ -2949,34 +3219,42 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="E35" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="G35" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="H35" s="29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I35" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" s="31">
+      <c r="E35" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="36" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G35" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="41">
         <f>E35*F35*G35*H35*I35</f>
         <v/>
       </c>
       <c r="K35" s="26" t="n"/>
       <c r="L35" s="26" t="n"/>
+      <c r="M35" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 7,500 → 2,460</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="26" t="n"/>
       <c r="B36" s="26" t="n"/>
       <c r="C36" s="27" t="inlineStr">
         <is>
-          <t>- Lớp bê tông lót đáy bệ mố M2 chữ U</t>
+          <t>- Bê tông đệm C10 mố M2 (bản vẽ tr.40)</t>
         </is>
       </c>
       <c r="D36" s="28" t="inlineStr">
@@ -2984,34 +3262,42 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="E36" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="29" t="n">
-        <v>14</v>
-      </c>
-      <c r="G36" s="29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H36" s="29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I36" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="31">
+      <c r="E36" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="36" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="G36" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="41">
         <f>E36*F36*G36*H36*I36</f>
         <v/>
       </c>
       <c r="K36" s="26" t="n"/>
       <c r="L36" s="26" t="n"/>
+      <c r="M36" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 9,100 → 7,090</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>9.1</v>
+      </c>
     </row>
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="26" t="n"/>
       <c r="B37" s="26" t="n"/>
       <c r="C37" s="27" t="inlineStr">
         <is>
-          <t>- Lớp bê tông lót đáy bệ trụ T1</t>
+          <t>- Bê tông đệm C10 bệ trụ T1 (bản vẽ tr.44)</t>
         </is>
       </c>
       <c r="D37" s="28" t="inlineStr">
@@ -3019,34 +3305,42 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="E37" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="29" t="n">
-        <v>13</v>
-      </c>
-      <c r="G37" s="29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H37" s="29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I37" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" s="31">
+      <c r="E37" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="36" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="G37" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="41">
         <f>E37*F37*G37*H37*I37</f>
         <v/>
       </c>
       <c r="K37" s="26" t="n"/>
       <c r="L37" s="26" t="n"/>
+      <c r="M37" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 8,450 → 8,770</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>8.449999999999999</v>
+      </c>
     </row>
     <row r="38" ht="19" customHeight="1">
       <c r="A38" s="26" t="n"/>
       <c r="B38" s="26" t="n"/>
       <c r="C38" s="27" t="inlineStr">
         <is>
-          <t>- Lớp bê tông lót đáy bệ trụ T2</t>
+          <t>- Bê tông đệm C10 bệ trụ T2 (bản vẽ tr.55)</t>
         </is>
       </c>
       <c r="D38" s="28" t="inlineStr">
@@ -3054,27 +3348,35 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="E38" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="29" t="n">
-        <v>13</v>
-      </c>
-      <c r="G38" s="29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H38" s="29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I38" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="31">
+      <c r="E38" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="36" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="G38" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="41">
         <f>E38*F38*G38*H38*I38</f>
         <v/>
       </c>
       <c r="K38" s="26" t="n"/>
       <c r="L38" s="26" t="n"/>
+      <c r="M38" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 8,450 → 8,770</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>8.449999999999999</v>
+      </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="23" t="inlineStr">
@@ -3119,7 +3421,7 @@
       <c r="B40" s="26" t="n"/>
       <c r="C40" s="27" t="inlineStr">
         <is>
-          <t>- Bệ móng mố M1 chân dê (chiều cao bệ h=2.0m)</t>
+          <t>- Bệ móng mố M1 + M2 (bảng tổng hợp tr.175)</t>
         </is>
       </c>
       <c r="D40" s="28" t="inlineStr">
@@ -3127,34 +3429,42 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="E40" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="29" t="n">
-        <v>12</v>
-      </c>
-      <c r="G40" s="29" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H40" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="I40" s="30" t="n">
-        <v>1.1287</v>
-      </c>
-      <c r="J40" s="31">
+      <c r="E40" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="36" t="n">
+        <v>148.992</v>
+      </c>
+      <c r="G40" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="41">
         <f>E40*F40*G40*H40*I40</f>
         <v/>
       </c>
       <c r="K40" s="26" t="n"/>
       <c r="L40" s="26" t="n"/>
+      <c r="M40" s="35" t="inlineStr">
+        <is>
+          <t>Khớp bản vẽ. Bản vẽ chỉ ghi bê tông bệ mố gộp 2 mố (tr.175) — dòng M2 bên dưới để 0. Tổng bê tông mố (bệ + tường thân + tường đỉnh + tường cánh + ụ) 376,357 m³ khớp tr.31 (75,12) + tr.40 (301,24).</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>148.988</v>
+      </c>
     </row>
     <row r="41" ht="19" customHeight="1">
       <c r="A41" s="26" t="n"/>
       <c r="B41" s="26" t="n"/>
       <c r="C41" s="27" t="inlineStr">
         <is>
-          <t>- Bệ móng mố M2 chữ U (chiều cao bệ h=2.0m)</t>
+          <t>- Bệ móng mố M2: đã gộp vào dòng trên (bản vẽ tr.175 ghi chung 2 mố)</t>
         </is>
       </c>
       <c r="D41" s="28" t="inlineStr">
@@ -3162,34 +3472,42 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="E41" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="29" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="G41" s="29" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H41" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="I41" s="30" t="n">
-        <v>1.0033</v>
-      </c>
-      <c r="J41" s="31">
+      <c r="E41" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="41">
         <f>E41*F41*G41*H41*I41</f>
         <v/>
       </c>
       <c r="K41" s="26" t="n"/>
       <c r="L41" s="26" t="n"/>
+      <c r="M41" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 148,990 → 0,000</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>148.99</v>
+      </c>
     </row>
     <row r="42" ht="19" customHeight="1">
       <c r="A42" s="26" t="n"/>
       <c r="B42" s="26" t="n"/>
       <c r="C42" s="27" t="inlineStr">
         <is>
-          <t>- Bệ móng trụ T1 thân đặc (chiều cao bệ h=2.5m)</t>
+          <t>- Bệ móng trụ T1 (bản vẽ tr.44)</t>
         </is>
       </c>
       <c r="D42" s="28" t="inlineStr">
@@ -3197,34 +3515,42 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="E42" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="29" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="G42" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="H42" s="29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I42" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" s="31">
+      <c r="E42" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="36" t="n">
+        <v>184.24</v>
+      </c>
+      <c r="G42" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="41">
         <f>E42*F42*G42*H42*I42</f>
         <v/>
       </c>
       <c r="K42" s="26" t="n"/>
       <c r="L42" s="26" t="n"/>
+      <c r="M42" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 184,500 → 184,240</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>184.5</v>
+      </c>
     </row>
     <row r="43" ht="19" customHeight="1">
       <c r="A43" s="26" t="n"/>
       <c r="B43" s="26" t="n"/>
       <c r="C43" s="27" t="inlineStr">
         <is>
-          <t>- Bệ móng trụ T2 thân đặc (chiều cao bệ h=2.5m)</t>
+          <t>- Bệ móng trụ T2 (bản vẽ tr.55)</t>
         </is>
       </c>
       <c r="D43" s="28" t="inlineStr">
@@ -3232,27 +3558,35 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="E43" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="29" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="G43" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="H43" s="29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I43" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="31">
+      <c r="E43" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="36" t="n">
+        <v>184.24</v>
+      </c>
+      <c r="G43" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="41">
         <f>E43*F43*G43*H43*I43</f>
         <v/>
       </c>
       <c r="K43" s="26" t="n"/>
       <c r="L43" s="26" t="n"/>
+      <c r="M43" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 184,500 → 184,240</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>184.5</v>
+      </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="23" t="inlineStr">
@@ -3297,7 +3631,7 @@
       <c r="B45" s="26" t="n"/>
       <c r="C45" s="27" t="inlineStr">
         <is>
-          <t>- Thân mố M1 chân dê</t>
+          <t>- Tường thân mố M1 + M2 (bảng tổng hợp tr.175)</t>
         </is>
       </c>
       <c r="D45" s="28" t="inlineStr">
@@ -3305,34 +3639,42 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="E45" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="29" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="G45" s="29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H45" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="I45" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="31">
+      <c r="E45" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="36" t="n">
+        <v>168.871</v>
+      </c>
+      <c r="G45" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="41">
         <f>E45*F45*G45*H45*I45</f>
         <v/>
       </c>
       <c r="K45" s="26" t="n"/>
       <c r="L45" s="26" t="n"/>
+      <c r="M45" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 84,600 → 168,871. Bản vẽ ghi tường thân gộp 2 mố (tr.175) — dòng M2 bên dưới để 0.</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>84.59999999999999</v>
+      </c>
     </row>
     <row r="46" ht="19" customHeight="1">
       <c r="A46" s="26" t="n"/>
       <c r="B46" s="26" t="n"/>
       <c r="C46" s="27" t="inlineStr">
         <is>
-          <t>- Thân mố M2 chữ U (tường thân trước)</t>
+          <t>- Tường thân mố M2: đã gộp vào dòng trên (bản vẽ tr.175 ghi chung 2 mố)</t>
         </is>
       </c>
       <c r="D46" s="28" t="inlineStr">
@@ -3340,27 +3682,35 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="E46" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="29" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="G46" s="29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H46" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="I46" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" s="31">
+      <c r="E46" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="41">
         <f>E46*F46*G46*H46*I46</f>
         <v/>
       </c>
       <c r="K46" s="26" t="n"/>
       <c r="L46" s="26" t="n"/>
+      <c r="M46" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 84,600 → 0,000</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>84.59999999999999</v>
+      </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="23" t="inlineStr">
@@ -3405,7 +3755,7 @@
       <c r="B48" s="26" t="n"/>
       <c r="C48" s="27" t="inlineStr">
         <is>
-          <t>- Tường đỉnh mố M1 và M2</t>
+          <t>- Tường đỉnh mố M1 + M2 (bảng tổng hợp tr.175)</t>
         </is>
       </c>
       <c r="D48" s="28" t="inlineStr">
@@ -3413,34 +3763,37 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="E48" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="F48" s="29" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="G48" s="29" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H48" s="29" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="I48" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="31">
+      <c r="E48" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="36" t="n">
+        <v>28.652</v>
+      </c>
+      <c r="G48" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" s="41">
         <f>E48*F48*G48*H48*I48</f>
         <v/>
       </c>
       <c r="K48" s="26" t="n"/>
       <c r="L48" s="26" t="n"/>
+      <c r="N48" t="n">
+        <v>28.658</v>
+      </c>
     </row>
     <row r="49" ht="19" customHeight="1">
       <c r="A49" s="26" t="n"/>
       <c r="B49" s="26" t="n"/>
       <c r="C49" s="27" t="inlineStr">
         <is>
-          <t>- Tường cánh mố M1 và M2 (4 tường cánh vát)</t>
+          <t>- Tường cánh mố M1 + M2 + gờ lan can, ụ chống chuyển vị tường tai (tr.175)</t>
         </is>
       </c>
       <c r="D49" s="28" t="inlineStr">
@@ -3448,27 +3801,36 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="E49" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="F49" s="29" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G49" s="29" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H49" s="29" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="I49" s="30" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J49" s="31">
+      <c r="E49" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="36">
+        <f>20.254+9.588</f>
+        <v/>
+      </c>
+      <c r="G49" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="41">
         <f>E49*F49*G49*H49*I49</f>
         <v/>
       </c>
       <c r="K49" s="26" t="n"/>
       <c r="L49" s="26" t="n"/>
+      <c r="M49" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 20,256 → 29,842. Gộp 'gờ lan can, ụ chống chuyển vị tường tai' của mố (tr.175) vào hạng mục tường cánh/tường đỉnh vì cùng mác C30 — tách mã nếu đơn giá khác.</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>20.256</v>
+      </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="23" t="inlineStr">
@@ -3513,7 +3875,7 @@
       <c r="B51" s="26" t="n"/>
       <c r="C51" s="27" t="inlineStr">
         <is>
-          <t>- Thân đặc trụ T1 (chiều cao trụ H=14.5m)</t>
+          <t>- Thân trụ T1 (bản vẽ tr.48)</t>
         </is>
       </c>
       <c r="D51" s="28" t="inlineStr">
@@ -3521,34 +3883,42 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="E51" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" s="29" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="G51" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="H51" s="29" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="I51" s="30" t="n">
-        <v>0.995</v>
-      </c>
-      <c r="J51" s="31">
+      <c r="E51" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="36" t="n">
+        <v>234.92</v>
+      </c>
+      <c r="G51" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" s="41">
         <f>E51*F51*G51*H51*I51</f>
         <v/>
       </c>
       <c r="K51" s="26" t="n"/>
       <c r="L51" s="26" t="n"/>
+      <c r="M51" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 281,336 → 234,920. Dự toán cũ ghi H = 14,5 m; cao độ trên bản vẽ cho thân trụ T1 cao khoảng 23,35 m. Đã lấy thể tích bản vẽ.</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>281.336</v>
+      </c>
     </row>
     <row r="52" ht="19" customHeight="1">
       <c r="A52" s="26" t="n"/>
       <c r="B52" s="26" t="n"/>
       <c r="C52" s="27" t="inlineStr">
         <is>
-          <t>- Thân đặc trụ T2 (chiều cao trụ H=11.4m)</t>
+          <t>- Thân trụ T2 (bản vẽ tr.59)</t>
         </is>
       </c>
       <c r="D52" s="28" t="inlineStr">
@@ -3556,27 +3926,35 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="E52" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" s="29" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="G52" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="H52" s="29" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="I52" s="30" t="n">
-        <v>0.995</v>
-      </c>
-      <c r="J52" s="31">
+      <c r="E52" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="36" t="n">
+        <v>266.79</v>
+      </c>
+      <c r="G52" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" s="41">
         <f>E52*F52*G52*H52*I52</f>
         <v/>
       </c>
       <c r="K52" s="26" t="n"/>
       <c r="L52" s="26" t="n"/>
+      <c r="M52" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 221,189 → 266,790. Dự toán cũ ghi H = 11,4 m; cao độ trên bản vẽ cho thân trụ T2 cao khoảng 25,45 m. Đã lấy thể tích bản vẽ.</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>221.189</v>
+      </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="23" t="inlineStr">
@@ -3621,7 +3999,7 @@
       <c r="B54" s="26" t="n"/>
       <c r="C54" s="27" t="inlineStr">
         <is>
-          <t>- Xà mũ trụ T1 (kích thước vát 12.3m x 3.3m x 1.8m)</t>
+          <t>- Xà mũ trụ T1 (bản vẽ tr.51)</t>
         </is>
       </c>
       <c r="D54" s="28" t="inlineStr">
@@ -3629,34 +4007,42 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="E54" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F54" s="29" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="G54" s="29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H54" s="29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="I54" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="31">
+      <c r="E54" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="36" t="n">
+        <v>72.51000000000001</v>
+      </c>
+      <c r="G54" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" s="41">
         <f>E54*F54*G54*H54*I54</f>
         <v/>
       </c>
       <c r="K54" s="26" t="n"/>
       <c r="L54" s="26" t="n"/>
+      <c r="M54" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 73,062 → 72,510</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>73.062</v>
+      </c>
     </row>
     <row r="55" ht="19" customHeight="1">
       <c r="A55" s="26" t="n"/>
       <c r="B55" s="26" t="n"/>
       <c r="C55" s="27" t="inlineStr">
         <is>
-          <t>- Xà mũ trụ T2 (kích thước vát 12.3m x 3.3m x 1.8m)</t>
+          <t>- Xà mũ trụ T2 (bản vẽ tr.62)</t>
         </is>
       </c>
       <c r="D55" s="28" t="inlineStr">
@@ -3664,27 +4050,35 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="E55" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" s="29" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="G55" s="29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H55" s="29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="I55" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" s="31">
+      <c r="E55" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="36" t="n">
+        <v>72.51000000000001</v>
+      </c>
+      <c r="G55" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" s="41">
         <f>E55*F55*G55*H55*I55</f>
         <v/>
       </c>
       <c r="K55" s="26" t="n"/>
       <c r="L55" s="26" t="n"/>
+      <c r="M55" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 73,062 → 72,510</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>73.062</v>
+      </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="23" t="inlineStr">
@@ -3712,8 +4106,9 @@
       <c r="G56" s="18" t="n"/>
       <c r="H56" s="18" t="n"/>
       <c r="I56" s="18" t="n"/>
-      <c r="J56" s="32" t="n">
-        <v>224.6522560819999</v>
+      <c r="J56" s="42">
+        <f>SUM(J57:J60)</f>
+        <v/>
       </c>
       <c r="K56" s="19" t="n">
         <v>18500000</v>
@@ -3721,6 +4116,14 @@
       <c r="L56" s="25">
         <f>J56*K56</f>
         <v/>
+      </c>
+      <c r="M56" s="35" t="inlineStr">
+        <is>
+          <t>Tiêu đề ghi cứng 224,652 — đổi thành tổng các dòng diễn giải (=SUM(J57:J60))</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>224.6522560819999</v>
       </c>
     </row>
     <row r="57" ht="19" customHeight="1">
@@ -3728,7 +4131,7 @@
       <c r="B57" s="26" t="n"/>
       <c r="C57" s="27" t="inlineStr">
         <is>
-          <t>- Cốt thép mố M1 (tổng hợp bản vẽ Trang 31)</t>
+          <t>- Cốt thép mố M1 (bản vẽ tr.31)</t>
         </is>
       </c>
       <c r="D57" s="28" t="inlineStr">
@@ -3736,34 +4139,42 @@
           <t>Tấn</t>
         </is>
       </c>
-      <c r="E57" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F57" s="29" t="n">
-        <v>23.45</v>
-      </c>
-      <c r="G57" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H57" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I57" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" s="31">
+      <c r="E57" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="36" t="n">
+        <v>7.95856</v>
+      </c>
+      <c r="G57" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" s="41">
         <f>E57*F57*G57*H57*I57</f>
         <v/>
       </c>
       <c r="K57" s="26" t="n"/>
       <c r="L57" s="26" t="n"/>
+      <c r="M57" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 23,450 → 7,959</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>23.45</v>
+      </c>
     </row>
     <row r="58" ht="19" customHeight="1">
       <c r="A58" s="26" t="n"/>
       <c r="B58" s="26" t="n"/>
       <c r="C58" s="27" t="inlineStr">
         <is>
-          <t>- Cốt thép mố M2 (tổng hợp bản vẽ Trang 40)</t>
+          <t>- Cốt thép mố M2 (bản vẽ tr.40)</t>
         </is>
       </c>
       <c r="D58" s="28" t="inlineStr">
@@ -3771,34 +4182,42 @@
           <t>Tấn</t>
         </is>
       </c>
-      <c r="E58" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F58" s="29" t="n">
-        <v>31.85</v>
-      </c>
-      <c r="G58" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H58" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I58" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" s="31">
+      <c r="E58" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="36" t="n">
+        <v>19.64873</v>
+      </c>
+      <c r="G58" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" s="41">
         <f>E58*F58*G58*H58*I58</f>
         <v/>
       </c>
       <c r="K58" s="26" t="n"/>
       <c r="L58" s="26" t="n"/>
+      <c r="M58" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 31,850 → 19,649</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>31.85</v>
+      </c>
     </row>
     <row r="59" ht="19" customHeight="1">
       <c r="A59" s="26" t="n"/>
       <c r="B59" s="26" t="n"/>
       <c r="C59" s="27" t="inlineStr">
         <is>
-          <t>- Cốt thép trụ T1 (bệ, thân, xà mũ)</t>
+          <t>- Cốt thép trụ T1: bệ tr.44 + thân tr.48 + xà mũ tr.51</t>
         </is>
       </c>
       <c r="D59" s="28" t="inlineStr">
@@ -3806,34 +4225,43 @@
           <t>Tấn</t>
         </is>
       </c>
-      <c r="E59" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F59" s="29" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="G59" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H59" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I59" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J59" s="31">
+      <c r="E59" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="36">
+        <f>16.1778+32.5585+13.0131</f>
+        <v/>
+      </c>
+      <c r="G59" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" s="41">
         <f>E59*F59*G59*H59*I59</f>
         <v/>
       </c>
       <c r="K59" s="26" t="n"/>
       <c r="L59" s="26" t="n"/>
+      <c r="M59" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 38,600 → 61,749</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>38.6</v>
+      </c>
     </row>
     <row r="60" ht="19" customHeight="1">
       <c r="A60" s="26" t="n"/>
       <c r="B60" s="26" t="n"/>
       <c r="C60" s="27" t="inlineStr">
         <is>
-          <t>- Cốt thép trụ T2 (bệ, thân, xà mũ)</t>
+          <t>- Cốt thép trụ T2: bệ tr.55 + thân tr.59 + xà mũ tr.62</t>
         </is>
       </c>
       <c r="D60" s="28" t="inlineStr">
@@ -3841,27 +4269,36 @@
           <t>Tấn</t>
         </is>
       </c>
-      <c r="E60" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" s="29" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="G60" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H60" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I60" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="31">
+      <c r="E60" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="36">
+        <f>16.1778+35.1868+13.0131</f>
+        <v/>
+      </c>
+      <c r="G60" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" s="41">
         <f>E60*F60*G60*H60*I60</f>
         <v/>
       </c>
       <c r="K60" s="26" t="n"/>
       <c r="L60" s="26" t="n"/>
+      <c r="M60" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 34,200 → 64,378</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>34.2</v>
+      </c>
     </row>
     <row r="61" ht="24" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
@@ -3913,7 +4350,7 @@
       <c r="B63" s="26" t="n"/>
       <c r="C63" s="27" t="inlineStr">
         <is>
-          <t>- Bê tông 15 phiến dầm Super-T (chiều dài L=38.2m, F_tb=0.759m2)</t>
+          <t>- Bê tông 15 phiến dầm Super-T 45MPa (bảng tổng hợp tr.175)</t>
         </is>
       </c>
       <c r="D63" s="28" t="inlineStr">
@@ -3921,27 +4358,30 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="E63" s="29" t="n">
-        <v>15</v>
-      </c>
-      <c r="F63" s="29" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="G63" s="29" t="n">
-        <v>0.759</v>
-      </c>
-      <c r="H63" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I63" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" s="31">
+      <c r="E63" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="36" t="n">
+        <v>434.803</v>
+      </c>
+      <c r="G63" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" s="41">
         <f>E63*F63*G63*H63*I63</f>
         <v/>
       </c>
       <c r="K63" s="26" t="n"/>
       <c r="L63" s="26" t="n"/>
+      <c r="N63" t="n">
+        <v>434.907</v>
+      </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="23" t="inlineStr">
@@ -3969,8 +4409,9 @@
       <c r="G64" s="18" t="n"/>
       <c r="H64" s="18" t="n"/>
       <c r="I64" s="18" t="n"/>
-      <c r="J64" s="32" t="n">
-        <v>27.78362400000001</v>
+      <c r="J64" s="42">
+        <f>SUM(J65:J65)</f>
+        <v/>
       </c>
       <c r="K64" s="19" t="n">
         <v>42000000</v>
@@ -3978,6 +4419,14 @@
       <c r="L64" s="25">
         <f>J64*K64</f>
         <v/>
+      </c>
+      <c r="M64" s="35" t="inlineStr">
+        <is>
+          <t>Tiêu đề ghi cứng 27,784 — đổi thành tổng các dòng diễn giải (=SUM(J65:J65))</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>27.78362400000001</v>
       </c>
     </row>
     <row r="65" ht="19" customHeight="1">
@@ -3985,7 +4434,7 @@
       <c r="B65" s="26" t="n"/>
       <c r="C65" s="27" t="inlineStr">
         <is>
-          <t>- Cáp DUL 15 phiến dầm Super-T (15 phiến x 1.994 tấn/phiến)</t>
+          <t>- Cáp DƯL 15,2mm 15 phiến dầm Super-T (bảng tổng hợp tr.175)</t>
         </is>
       </c>
       <c r="D65" s="28" t="inlineStr">
@@ -3993,27 +4442,35 @@
           <t>Tấn</t>
         </is>
       </c>
-      <c r="E65" s="29" t="n">
-        <v>15</v>
-      </c>
-      <c r="F65" s="29" t="n">
-        <v>1.994</v>
-      </c>
-      <c r="G65" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H65" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I65" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" s="31">
+      <c r="E65" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="36" t="n">
+        <v>29.911</v>
+      </c>
+      <c r="G65" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" s="41">
         <f>E65*F65*G65*H65*I65</f>
         <v/>
       </c>
       <c r="K65" s="26" t="n"/>
       <c r="L65" s="26" t="n"/>
+      <c r="M65" s="35" t="inlineStr">
+        <is>
+          <t>Khớp bản vẽ. Dòng tiêu đề cũ ghi cứng 27,784 t, khác dòng diễn giải (15 × 1,994 = 29,91 t). Bảng tổng hợp tr.175 ghi 29,911 t — đã lấy theo bản vẽ và đổi tiêu đề thành tổng công thức.</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>29.91</v>
+      </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="23" t="inlineStr">
@@ -4041,8 +4498,9 @@
       <c r="G66" s="18" t="n"/>
       <c r="H66" s="18" t="n"/>
       <c r="I66" s="18" t="n"/>
-      <c r="J66" s="32" t="n">
-        <v>361.5960984</v>
+      <c r="J66" s="42">
+        <f>SUM(J67:J67)</f>
+        <v/>
       </c>
       <c r="K66" s="19" t="n">
         <v>18800000</v>
@@ -4050,6 +4508,14 @@
       <c r="L66" s="25">
         <f>J66*K66</f>
         <v/>
+      </c>
+      <c r="M66" s="35" t="inlineStr">
+        <is>
+          <t>Tiêu đề ghi cứng 361,596 — đổi thành tổng các dòng diễn giải (=SUM(J67:J67))</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>361.5960984</v>
       </c>
     </row>
     <row r="67" ht="19" customHeight="1">
@@ -4057,7 +4523,7 @@
       <c r="B67" s="26" t="n"/>
       <c r="C67" s="27" t="inlineStr">
         <is>
-          <t>- Cốt thép thường 15 phiến dầm Super-T (15 phiến x 6.042 tấn/phiến)</t>
+          <t>- Cốt thép thường 15 phiến: 3 × S1B1 (tr.88) + 3 × S1B2 (tr.91) + 9 × S1G (tr.94)</t>
         </is>
       </c>
       <c r="D67" s="28" t="inlineStr">
@@ -4065,27 +4531,36 @@
           <t>Tấn</t>
         </is>
       </c>
-      <c r="E67" s="29" t="n">
-        <v>15</v>
-      </c>
-      <c r="F67" s="29" t="n">
-        <v>6.042</v>
-      </c>
-      <c r="G67" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H67" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I67" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" s="31">
+      <c r="E67" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="36">
+        <f>3*6.07125+3*6.06528+9*5.92008</f>
+        <v/>
+      </c>
+      <c r="G67" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" s="41">
         <f>E67*F67*G67*H67*I67</f>
         <v/>
       </c>
       <c r="K67" s="26" t="n"/>
       <c r="L67" s="26" t="n"/>
+      <c r="M67" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 90,630 → 89,690. Dòng tiêu đề cũ ghi cứng 361,596 t (= BBS cũ, gấp khoảng 4 lần bản vẽ). Bản vẽ: 89,690 t = tr.175 (77,743 + 11,947 t). Số phiến 3/3/9 suy từ tổng tr.175 — xác nhận theo mặt cắt ngang.</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>90.63</v>
+      </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="23" t="inlineStr">
@@ -4311,7 +4786,7 @@
       <c r="B74" s="26" t="n"/>
       <c r="C74" s="27" t="inlineStr">
         <is>
-          <t>- Dầm ngang tại 2 mố và 2 trụ</t>
+          <t>- Dầm ngang (bản vẽ tr.96: 3 dầm × 6,46 m³)</t>
         </is>
       </c>
       <c r="D74" s="28" t="inlineStr">
@@ -4319,27 +4794,35 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="E74" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="F74" s="29" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="G74" s="29" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H74" s="29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="I74" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J74" s="31">
+      <c r="E74" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="36" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="G74" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" s="41">
         <f>E74*F74*G74*H74*I74</f>
         <v/>
       </c>
       <c r="K74" s="26" t="n"/>
       <c r="L74" s="26" t="n"/>
+      <c r="M74" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 39,852 → 19,380. Dự toán cũ: 4 dầm 12,3 × 0,45 × 1,8 m. Bản vẽ tr.96 và tr.175 ghi 19,38 m³.</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>39.852</v>
+      </c>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="23" t="inlineStr">
@@ -4457,7 +4940,7 @@
       <c r="B78" s="26" t="n"/>
       <c r="C78" s="27" t="inlineStr">
         <is>
-          <t>- Bê tông bản mặt cầu 3 nhịp (L=118.2m, B=12.615m, d=0.18m, trừ dầm)</t>
+          <t>- Bê tông bản mặt cầu 35MPa (bảng tổng hợp tr.175)</t>
         </is>
       </c>
       <c r="D78" s="28" t="inlineStr">
@@ -4465,27 +4948,30 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="E78" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F78" s="29" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="G78" s="29" t="n">
-        <v>12.615</v>
-      </c>
-      <c r="H78" s="29" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="I78" s="30" t="n">
-        <v>1.1378</v>
-      </c>
-      <c r="J78" s="31">
+      <c r="E78" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="36" t="n">
+        <v>305.465</v>
+      </c>
+      <c r="G78" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" s="41">
         <f>E78*F78*G78*H78*I78</f>
         <v/>
       </c>
       <c r="K78" s="26" t="n"/>
       <c r="L78" s="26" t="n"/>
+      <c r="N78" t="n">
+        <v>305.382</v>
+      </c>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="23" t="inlineStr">
@@ -4530,7 +5016,7 @@
       <c r="B80" s="26" t="n"/>
       <c r="C80" s="27" t="inlineStr">
         <is>
-          <t>- Bản liên tục nhiệt tại trụ T1 và T2</t>
+          <t>- Bê tông bản liên tục nhiệt 35MPa tại trụ T1, T2 (bảng tổng hợp tr.175)</t>
         </is>
       </c>
       <c r="D80" s="28" t="inlineStr">
@@ -4538,27 +5024,35 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="E80" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="F80" s="29" t="n">
-        <v>12.615</v>
-      </c>
-      <c r="G80" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="H80" s="29" t="n">
-        <v>0.216</v>
-      </c>
-      <c r="I80" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="31">
+      <c r="E80" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="36" t="n">
+        <v>21.868</v>
+      </c>
+      <c r="G80" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" s="41">
         <f>E80*F80*G80*H80*I80</f>
         <v/>
       </c>
       <c r="K80" s="26" t="n"/>
       <c r="L80" s="26" t="n"/>
+      <c r="M80" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 21,799 → 21,868</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>21.799</v>
+      </c>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="23" t="inlineStr">
@@ -4603,7 +5097,7 @@
       <c r="B82" s="26" t="n"/>
       <c r="C82" s="27" t="inlineStr">
         <is>
-          <t>- Thép bản mặt cầu loại 1, loại 2, loại 3 &amp; liên tục nhiệt</t>
+          <t>- Thép bản mặt cầu và liên tục nhiệt (tr.175: D&lt;=10 + 10&lt;D&lt;=18 + D&gt;18)</t>
         </is>
       </c>
       <c r="D82" s="28" t="inlineStr">
@@ -4611,27 +5105,36 @@
           <t>Tấn</t>
         </is>
       </c>
-      <c r="E82" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F82" s="29" t="n">
-        <v>33.07</v>
-      </c>
-      <c r="G82" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H82" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I82" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J82" s="31">
+      <c r="E82" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" s="36">
+        <f>1.573+78.951+5.071</f>
+        <v/>
+      </c>
+      <c r="G82" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J82" s="41">
         <f>E82*F82*G82*H82*I82</f>
         <v/>
       </c>
       <c r="K82" s="26" t="n"/>
       <c r="L82" s="26" t="n"/>
+      <c r="M82" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 33,070 → 85,595. Dự toán cũ 33,07 t. Bản vẽ tr.175: 85,595 t (khớp tr.112: 2 × 25.691,33 + 25.293,79 + 2 × 4.458,97 kg).</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>33.07</v>
+      </c>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="23" t="inlineStr">
@@ -4756,7 +5259,7 @@
       <c r="B87" s="26" t="n"/>
       <c r="C87" s="27" t="inlineStr">
         <is>
-          <t>- Bản quá độ sau mố M1 (L=8.0m, B=12.5m, d=0.35m)</t>
+          <t>- Bản quá độ sau mố M1 (bản vẽ tr.126)</t>
         </is>
       </c>
       <c r="D87" s="28" t="inlineStr">
@@ -4764,34 +5267,42 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="E87" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F87" s="29" t="n">
-        <v>8</v>
-      </c>
-      <c r="G87" s="29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="H87" s="29" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="I87" s="30" t="n">
-        <v>0.9626</v>
-      </c>
-      <c r="J87" s="31">
+      <c r="E87" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" s="36" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="G87" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" s="41">
         <f>E87*F87*G87*H87*I87</f>
         <v/>
       </c>
       <c r="K87" s="26" t="n"/>
       <c r="L87" s="26" t="n"/>
+      <c r="M87" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 33,691 → 29,100</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>33.691</v>
+      </c>
     </row>
     <row r="88" ht="19" customHeight="1">
       <c r="A88" s="26" t="n"/>
       <c r="B88" s="26" t="n"/>
       <c r="C88" s="27" t="inlineStr">
         <is>
-          <t>- Bản quá độ sau mố M2 (L=8.0m, B=12.5m, d=0.35m)</t>
+          <t>- Bản quá độ sau mố M2 (bản vẽ tr.128)</t>
         </is>
       </c>
       <c r="D88" s="28" t="inlineStr">
@@ -4799,27 +5310,35 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="E88" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F88" s="29" t="n">
-        <v>8</v>
-      </c>
-      <c r="G88" s="29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="H88" s="29" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="I88" s="30" t="n">
-        <v>0.9626</v>
-      </c>
-      <c r="J88" s="31">
+      <c r="E88" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" s="36" t="n">
+        <v>38.28</v>
+      </c>
+      <c r="G88" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" s="41">
         <f>E88*F88*G88*H88*I88</f>
         <v/>
       </c>
       <c r="K88" s="26" t="n"/>
       <c r="L88" s="26" t="n"/>
+      <c r="M88" s="35" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 33,691 → 38,280</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>33.691</v>
+      </c>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="23" t="inlineStr">
@@ -4864,7 +5383,7 @@
       <c r="B90" s="26" t="n"/>
       <c r="C90" s="27" t="inlineStr">
         <is>
-          <t>- Đoạn đắp chuyển tiếp sau mố M1 và M2</t>
+          <t>- Vật liệu dạng hạt trong lòng mố K98 (bảng tổng hợp tr.175)</t>
         </is>
       </c>
       <c r="D90" s="28" t="inlineStr">
@@ -4872,27 +5391,35 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="E90" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="F90" s="29" t="n">
-        <v>18</v>
-      </c>
-      <c r="G90" s="29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="H90" s="29" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I90" s="30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J90" s="31">
+      <c r="E90" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="36" t="n">
+        <v>1012.955</v>
+      </c>
+      <c r="G90" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I90" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" s="41">
         <f>E90*F90*G90*H90*I90</f>
         <v/>
       </c>
       <c r="K90" s="26" t="n"/>
       <c r="L90" s="26" t="n"/>
+      <c r="M90" s="35" t="inlineStr">
+        <is>
+          <t>Khớp bản vẽ. Dự toán cũ diễn giải 'đắp chuyển tiếp sau mố' 2 × 18 × 12,5 × 4,5 × 0,5 = 1.012,5 m³; tr.175 ghi 'vật liệu dạng hạt trong lòng mố K98' 1.012,955 m³ — xác nhận đúng hạng mục.</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>1012.5</v>
+      </c>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="23" t="inlineStr">
@@ -4966,6 +5493,11 @@
       </c>
       <c r="K92" s="26" t="n"/>
       <c r="L92" s="26" t="n"/>
+      <c r="M92" s="35" t="inlineStr">
+        <is>
+          <t>Gờ lan can tính theo m dài (2 × 130,4 m). Bản vẽ tr.119/tr.175: bê tông 104,277 m³ C25 và cốt thép 20,069 t — thép gờ lan can chưa có trong dự toán; đơn giá 1.650.000 đ/m giống đơn giá m³.</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="23" t="inlineStr">
@@ -5083,7 +5615,7 @@
       <c r="B96" s="26" t="n"/>
       <c r="C96" s="27" t="inlineStr">
         <is>
-          <t>- Diện tích mặt cầu xe chạy (L=118.2m x B=11.68m)</t>
+          <t>- Diện tích mặt cầu (bảng tổng hợp tr.175: BTN C16 dày 7cm)</t>
         </is>
       </c>
       <c r="D96" s="28" t="inlineStr">
@@ -5091,27 +5623,30 @@
           <t>m2</t>
         </is>
       </c>
-      <c r="E96" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F96" s="29" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="G96" s="29" t="n">
-        <v>11.678</v>
-      </c>
-      <c r="H96" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I96" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J96" s="31">
+      <c r="E96" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="36" t="n">
+        <v>1380.39</v>
+      </c>
+      <c r="G96" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I96" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J96" s="41">
         <f>E96*F96*G96*H96*I96</f>
         <v/>
       </c>
       <c r="K96" s="26" t="n"/>
       <c r="L96" s="26" t="n"/>
+      <c r="N96" t="n">
+        <v>1380.34</v>
+      </c>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="23" t="inlineStr">
@@ -5185,6 +5720,11 @@
       </c>
       <c r="K98" s="26" t="n"/>
       <c r="L98" s="26" t="n"/>
+      <c r="M98" s="35" t="inlineStr">
+        <is>
+          <t>Tứ nón đá hộc 52,216 m³ — tr.175 ghi 'đá hộc xây vữa' 104,738 m³ và 'chân khay đá hộc' 4,0 m³ (đường sau mố). Chưa rõ tương ứng — soát PDF tr.175.</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="23" t="inlineStr">
@@ -5290,4 +5830,2739 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I81"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="90" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="43" t="inlineStr">
+        <is>
+          <t>NGHI VẤN PHỤ LỤC 03a — soát và ghim (cột I)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="34" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B3" s="34" t="inlineStr">
+        <is>
+          <t>Sheet</t>
+        </is>
+      </c>
+      <c r="C3" s="34" t="inlineStr">
+        <is>
+          <t>Dòng</t>
+        </is>
+      </c>
+      <c r="D3" s="34" t="inlineStr">
+        <is>
+          <t>Hạng mục</t>
+        </is>
+      </c>
+      <c r="E3" s="34" t="inlineStr">
+        <is>
+          <t>Nội dung nghi vấn</t>
+        </is>
+      </c>
+      <c r="F3" s="34" t="inlineStr">
+        <is>
+          <t>Giá trị cũ</t>
+        </is>
+      </c>
+      <c r="G3" s="34" t="inlineStr">
+        <is>
+          <t>Giá trị mới</t>
+        </is>
+      </c>
+      <c r="H3" s="34" t="inlineStr">
+        <is>
+          <t>Trang bản vẽ</t>
+        </is>
+      </c>
+      <c r="I3" s="34" t="inlineStr">
+        <is>
+          <t>Đã soát / Ghim</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C4" s="44" t="n">
+        <v>22</v>
+      </c>
+      <c r="D4" s="44" t="inlineStr">
+        <is>
+          <t>4. Cốt thép cọc khoan nhồi D1200mm (Thép chủ D25, đai D16, D10)</t>
+        </is>
+      </c>
+      <c r="E4" s="44" t="inlineStr">
+        <is>
+          <t>Tiêu đề ghi cứng 108,766 — đổi thành tổng các dòng diễn giải (=SUM(J23:J26))</t>
+        </is>
+      </c>
+      <c r="F4" s="44" t="inlineStr">
+        <is>
+          <t>108,766</t>
+        </is>
+      </c>
+      <c r="G4" s="44">
+        <f>SUM(J23:J26)</f>
+        <v/>
+      </c>
+      <c r="H4" s="44" t="inlineStr"/>
+      <c r="I4" s="44" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C5" s="44" t="n">
+        <v>56</v>
+      </c>
+      <c r="D5" s="44" t="inlineStr">
+        <is>
+          <t>14. Cốt thép mố và trụ (D&lt;=10, 10&lt;D&lt;=18, D&gt;18)</t>
+        </is>
+      </c>
+      <c r="E5" s="44" t="inlineStr">
+        <is>
+          <t>Tiêu đề ghi cứng 224,652 — đổi thành tổng các dòng diễn giải (=SUM(J57:J60))</t>
+        </is>
+      </c>
+      <c r="F5" s="44" t="inlineStr">
+        <is>
+          <t>224,652</t>
+        </is>
+      </c>
+      <c r="G5" s="44">
+        <f>SUM(J57:J60)</f>
+        <v/>
+      </c>
+      <c r="H5" s="44" t="inlineStr"/>
+      <c r="I5" s="44" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C6" s="44" t="n">
+        <v>64</v>
+      </c>
+      <c r="D6" s="44" t="inlineStr">
+        <is>
+          <t>16. Cáp dự ứng lực tao xoắn 15.2mm Grade 270 kéo căng trước/sau</t>
+        </is>
+      </c>
+      <c r="E6" s="44" t="inlineStr">
+        <is>
+          <t>Tiêu đề ghi cứng 27,784 — đổi thành tổng các dòng diễn giải (=SUM(J65:J65))</t>
+        </is>
+      </c>
+      <c r="F6" s="44" t="inlineStr">
+        <is>
+          <t>27,784</t>
+        </is>
+      </c>
+      <c r="G6" s="44">
+        <f>SUM(J65:J65)</f>
+        <v/>
+      </c>
+      <c r="H6" s="44" t="inlineStr"/>
+      <c r="I6" s="44" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="44" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C7" s="44" t="n">
+        <v>66</v>
+      </c>
+      <c r="D7" s="44" t="inlineStr">
+        <is>
+          <t>17. Cốt thép thường dầm chủ Super-T (D10, D14, D16, D20)</t>
+        </is>
+      </c>
+      <c r="E7" s="44" t="inlineStr">
+        <is>
+          <t>Tiêu đề ghi cứng 361,596 — đổi thành tổng các dòng diễn giải (=SUM(J67:J67))</t>
+        </is>
+      </c>
+      <c r="F7" s="44" t="inlineStr">
+        <is>
+          <t>361,596</t>
+        </is>
+      </c>
+      <c r="G7" s="44">
+        <f>SUM(J67:J67)</f>
+        <v/>
+      </c>
+      <c r="H7" s="44" t="inlineStr"/>
+      <c r="I7" s="44" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="44" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C8" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D8" s="44" t="inlineStr">
+        <is>
+          <t>3. Bê tông cọc khoan nhồi C30/37 đổ bằng phương pháp rút ống tremie</t>
+        </is>
+      </c>
+      <c r="E8" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 76,002 → 70,740. Bỏ hệ số I = 3,5186 (π × 1,12 nở thành): lấy thể tích thiết kế tr.64. Nếu hợp đồng cho tính nở thành thì ghim lại hệ số.</t>
+        </is>
+      </c>
+      <c r="F8" s="44" t="inlineStr">
+        <is>
+          <t>76,002</t>
+        </is>
+      </c>
+      <c r="G8" s="44" t="inlineStr">
+        <is>
+          <t>70,740</t>
+        </is>
+      </c>
+      <c r="H8" s="44" t="inlineStr">
+        <is>
+          <t>tr.64</t>
+        </is>
+      </c>
+      <c r="I8" s="44" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="44" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C9" s="44" t="n">
+        <v>19</v>
+      </c>
+      <c r="D9" s="44" t="inlineStr">
+        <is>
+          <t>3. Bê tông cọc khoan nhồi C30/37 đổ bằng phương pháp rút ống tremie</t>
+        </is>
+      </c>
+      <c r="E9" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 405,343 → 367,040. Bỏ hệ số nở thành 3,5186 — lấy thể tích thiết kế tr.68.</t>
+        </is>
+      </c>
+      <c r="F9" s="44" t="inlineStr">
+        <is>
+          <t>405,343</t>
+        </is>
+      </c>
+      <c r="G9" s="44" t="inlineStr">
+        <is>
+          <t>367,040</t>
+        </is>
+      </c>
+      <c r="H9" s="44" t="inlineStr">
+        <is>
+          <t>tr.68</t>
+        </is>
+      </c>
+      <c r="I9" s="44" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="44" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C10" s="44" t="n">
+        <v>20</v>
+      </c>
+      <c r="D10" s="44" t="inlineStr">
+        <is>
+          <t>3. Bê tông cọc khoan nhồi C30/37 đổ bằng phương pháp rút ống tremie</t>
+        </is>
+      </c>
+      <c r="E10" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 304,007 → 277,840. Bỏ hệ số nở thành 3,5186 — lấy thể tích thiết kế tr.70.</t>
+        </is>
+      </c>
+      <c r="F10" s="44" t="inlineStr">
+        <is>
+          <t>304,007</t>
+        </is>
+      </c>
+      <c r="G10" s="44" t="inlineStr">
+        <is>
+          <t>277,840</t>
+        </is>
+      </c>
+      <c r="H10" s="44" t="inlineStr">
+        <is>
+          <t>tr.70</t>
+        </is>
+      </c>
+      <c r="I10" s="44" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="44" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C11" s="44" t="n">
+        <v>21</v>
+      </c>
+      <c r="D11" s="44" t="inlineStr">
+        <is>
+          <t>3. Bê tông cọc khoan nhồi C30/37 đổ bằng phương pháp rút ống tremie</t>
+        </is>
+      </c>
+      <c r="E11" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 319,207 → 290,920. Bỏ hệ số nở thành 3,5186 — lấy thể tích thiết kế tr.66.</t>
+        </is>
+      </c>
+      <c r="F11" s="44" t="inlineStr">
+        <is>
+          <t>319,207</t>
+        </is>
+      </c>
+      <c r="G11" s="44" t="inlineStr">
+        <is>
+          <t>290,920</t>
+        </is>
+      </c>
+      <c r="H11" s="44" t="inlineStr">
+        <is>
+          <t>tr.66</t>
+        </is>
+      </c>
+      <c r="I11" s="44" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="44" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C12" s="44" t="n">
+        <v>23</v>
+      </c>
+      <c r="D12" s="44" t="inlineStr">
+        <is>
+          <t>4. Cốt thép cọc khoan nhồi D1200mm (Thép chủ D25, đai D16, D10)</t>
+        </is>
+      </c>
+      <c r="E12" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 17,667 → 7,523</t>
+        </is>
+      </c>
+      <c r="F12" s="44" t="inlineStr">
+        <is>
+          <t>17,667</t>
+        </is>
+      </c>
+      <c r="G12" s="44" t="inlineStr">
+        <is>
+          <t>7,523</t>
+        </is>
+      </c>
+      <c r="H12" s="44" t="inlineStr">
+        <is>
+          <t>tr.64</t>
+        </is>
+      </c>
+      <c r="I12" s="44" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="44" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C13" s="44" t="n">
+        <v>24</v>
+      </c>
+      <c r="D13" s="44" t="inlineStr">
+        <is>
+          <t>4. Cốt thép cọc khoan nhồi D1200mm (Thép chủ D25, đai D16, D10)</t>
+        </is>
+      </c>
+      <c r="E13" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 38,760 → 38,629</t>
+        </is>
+      </c>
+      <c r="F13" s="44" t="inlineStr">
+        <is>
+          <t>38,760</t>
+        </is>
+      </c>
+      <c r="G13" s="44" t="inlineStr">
+        <is>
+          <t>38,629</t>
+        </is>
+      </c>
+      <c r="H13" s="44" t="inlineStr">
+        <is>
+          <t>tr.68</t>
+        </is>
+      </c>
+      <c r="I13" s="44" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="44" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C14" s="44" t="n">
+        <v>25</v>
+      </c>
+      <c r="D14" s="44" t="inlineStr">
+        <is>
+          <t>4. Cốt thép cọc khoan nhồi D1200mm (Thép chủ D25, đai D16, D10)</t>
+        </is>
+      </c>
+      <c r="E14" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 29,496 → 29,369</t>
+        </is>
+      </c>
+      <c r="F14" s="44" t="inlineStr">
+        <is>
+          <t>29,496</t>
+        </is>
+      </c>
+      <c r="G14" s="44" t="inlineStr">
+        <is>
+          <t>29,369</t>
+        </is>
+      </c>
+      <c r="H14" s="44" t="inlineStr">
+        <is>
+          <t>tr.70</t>
+        </is>
+      </c>
+      <c r="I14" s="44" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="44" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C15" s="44" t="n">
+        <v>26</v>
+      </c>
+      <c r="D15" s="44" t="inlineStr">
+        <is>
+          <t>4. Cốt thép cọc khoan nhồi D1200mm (Thép chủ D25, đai D16, D10)</t>
+        </is>
+      </c>
+      <c r="E15" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 33,047 → 32,941. Tổng 4 trang cọc 108,462 t; bảng tổng hợp tr.175 ghi 108,884 t (nhóm 10&lt;D&lt;=18: 0,982 t so với 0,559 t trên các trang cọc) — xem PDF tr.175.</t>
+        </is>
+      </c>
+      <c r="F15" s="44" t="inlineStr">
+        <is>
+          <t>33,047</t>
+        </is>
+      </c>
+      <c r="G15" s="44" t="inlineStr">
+        <is>
+          <t>32,941</t>
+        </is>
+      </c>
+      <c r="H15" s="44" t="inlineStr">
+        <is>
+          <t>tr.66</t>
+        </is>
+      </c>
+      <c r="I15" s="44" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="44" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C16" s="44" t="n">
+        <v>28</v>
+      </c>
+      <c r="D16" s="44" t="inlineStr">
+        <is>
+          <t>5. Đập đầu cọc khoan nhồi nhô lên đáy bệ ngàm vào kết cấu</t>
+        </is>
+      </c>
+      <c r="E16" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 29,405 → 30,360</t>
+        </is>
+      </c>
+      <c r="F16" s="44" t="inlineStr">
+        <is>
+          <t>29,405</t>
+        </is>
+      </c>
+      <c r="G16" s="44" t="inlineStr">
+        <is>
+          <t>30,360</t>
+        </is>
+      </c>
+      <c r="H16" s="44" t="inlineStr">
+        <is>
+          <t>tr.64</t>
+        </is>
+      </c>
+      <c r="I16" s="44" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="44" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C17" s="44" t="n">
+        <v>35</v>
+      </c>
+      <c r="D17" s="44" t="inlineStr">
+        <is>
+          <t>8. Bê tông lót đáy bệ móng mác C10 dày 10cm</t>
+        </is>
+      </c>
+      <c r="E17" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 7,500 → 2,460</t>
+        </is>
+      </c>
+      <c r="F17" s="44" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="G17" s="44" t="inlineStr">
+        <is>
+          <t>2,460</t>
+        </is>
+      </c>
+      <c r="H17" s="44" t="inlineStr">
+        <is>
+          <t>tr.31</t>
+        </is>
+      </c>
+      <c r="I17" s="44" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="44" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C18" s="44" t="n">
+        <v>36</v>
+      </c>
+      <c r="D18" s="44" t="inlineStr">
+        <is>
+          <t>8. Bê tông lót đáy bệ móng mác C10 dày 10cm</t>
+        </is>
+      </c>
+      <c r="E18" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 9,100 → 7,090</t>
+        </is>
+      </c>
+      <c r="F18" s="44" t="inlineStr">
+        <is>
+          <t>9,100</t>
+        </is>
+      </c>
+      <c r="G18" s="44" t="inlineStr">
+        <is>
+          <t>7,090</t>
+        </is>
+      </c>
+      <c r="H18" s="44" t="inlineStr">
+        <is>
+          <t>tr.40</t>
+        </is>
+      </c>
+      <c r="I18" s="44" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="44" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C19" s="44" t="n">
+        <v>37</v>
+      </c>
+      <c r="D19" s="44" t="inlineStr">
+        <is>
+          <t>8. Bê tông lót đáy bệ móng mác C10 dày 10cm</t>
+        </is>
+      </c>
+      <c r="E19" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 8,450 → 8,770</t>
+        </is>
+      </c>
+      <c r="F19" s="44" t="inlineStr">
+        <is>
+          <t>8,450</t>
+        </is>
+      </c>
+      <c r="G19" s="44" t="inlineStr">
+        <is>
+          <t>8,770</t>
+        </is>
+      </c>
+      <c r="H19" s="44" t="inlineStr">
+        <is>
+          <t>tr.44</t>
+        </is>
+      </c>
+      <c r="I19" s="44" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="44" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C20" s="44" t="n">
+        <v>38</v>
+      </c>
+      <c r="D20" s="44" t="inlineStr">
+        <is>
+          <t>8. Bê tông lót đáy bệ móng mác C10 dày 10cm</t>
+        </is>
+      </c>
+      <c r="E20" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 8,450 → 8,770</t>
+        </is>
+      </c>
+      <c r="F20" s="44" t="inlineStr">
+        <is>
+          <t>8,450</t>
+        </is>
+      </c>
+      <c r="G20" s="44" t="inlineStr">
+        <is>
+          <t>8,770</t>
+        </is>
+      </c>
+      <c r="H20" s="44" t="inlineStr">
+        <is>
+          <t>tr.55</t>
+        </is>
+      </c>
+      <c r="I20" s="44" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C21" s="44" t="n">
+        <v>40</v>
+      </c>
+      <c r="D21" s="44" t="inlineStr">
+        <is>
+          <t>9. Bê tông bệ móng mố M1, M2 và bệ trụ T1, T2 mác C30</t>
+        </is>
+      </c>
+      <c r="E21" s="44" t="inlineStr">
+        <is>
+          <t>Khớp bản vẽ. Bản vẽ chỉ ghi bê tông bệ mố gộp 2 mố (tr.175) — dòng M2 bên dưới để 0. Tổng bê tông mố (bệ + tường thân + tường đỉnh + tường cánh + ụ) 376,357 m³ khớp tr.31 (75,12) + tr.40 (301,24).</t>
+        </is>
+      </c>
+      <c r="F21" s="44" t="inlineStr">
+        <is>
+          <t>148,988</t>
+        </is>
+      </c>
+      <c r="G21" s="44" t="inlineStr">
+        <is>
+          <t>148,992</t>
+        </is>
+      </c>
+      <c r="H21" s="44" t="inlineStr">
+        <is>
+          <t>tr.175</t>
+        </is>
+      </c>
+      <c r="I21" s="44" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="44" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C22" s="44" t="n">
+        <v>41</v>
+      </c>
+      <c r="D22" s="44" t="inlineStr">
+        <is>
+          <t>9. Bê tông bệ móng mố M1, M2 và bệ trụ T1, T2 mác C30</t>
+        </is>
+      </c>
+      <c r="E22" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 148,990 → 0,000</t>
+        </is>
+      </c>
+      <c r="F22" s="44" t="inlineStr">
+        <is>
+          <t>148,990</t>
+        </is>
+      </c>
+      <c r="G22" s="44" t="inlineStr">
+        <is>
+          <t>0,000</t>
+        </is>
+      </c>
+      <c r="H22" s="44" t="inlineStr">
+        <is>
+          <t>tr.175</t>
+        </is>
+      </c>
+      <c r="I22" s="44" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="44" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C23" s="44" t="n">
+        <v>42</v>
+      </c>
+      <c r="D23" s="44" t="inlineStr">
+        <is>
+          <t>9. Bê tông bệ móng mố M1, M2 và bệ trụ T1, T2 mác C30</t>
+        </is>
+      </c>
+      <c r="E23" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 184,500 → 184,240</t>
+        </is>
+      </c>
+      <c r="F23" s="44" t="inlineStr">
+        <is>
+          <t>184,500</t>
+        </is>
+      </c>
+      <c r="G23" s="44" t="inlineStr">
+        <is>
+          <t>184,240</t>
+        </is>
+      </c>
+      <c r="H23" s="44" t="inlineStr">
+        <is>
+          <t>tr.44</t>
+        </is>
+      </c>
+      <c r="I23" s="44" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="44" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C24" s="44" t="n">
+        <v>43</v>
+      </c>
+      <c r="D24" s="44" t="inlineStr">
+        <is>
+          <t>9. Bê tông bệ móng mố M1, M2 và bệ trụ T1, T2 mác C30</t>
+        </is>
+      </c>
+      <c r="E24" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 184,500 → 184,240</t>
+        </is>
+      </c>
+      <c r="F24" s="44" t="inlineStr">
+        <is>
+          <t>184,500</t>
+        </is>
+      </c>
+      <c r="G24" s="44" t="inlineStr">
+        <is>
+          <t>184,240</t>
+        </is>
+      </c>
+      <c r="H24" s="44" t="inlineStr">
+        <is>
+          <t>tr.55</t>
+        </is>
+      </c>
+      <c r="I24" s="44" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="44" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C25" s="44" t="n">
+        <v>45</v>
+      </c>
+      <c r="D25" s="44" t="inlineStr">
+        <is>
+          <t>10. Bê tông thân mố chân dê M1 và mố chữ U M2 mác C30</t>
+        </is>
+      </c>
+      <c r="E25" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 84,600 → 168,871. Bản vẽ ghi tường thân gộp 2 mố (tr.175) — dòng M2 bên dưới để 0.</t>
+        </is>
+      </c>
+      <c r="F25" s="44" t="inlineStr">
+        <is>
+          <t>84,600</t>
+        </is>
+      </c>
+      <c r="G25" s="44" t="inlineStr">
+        <is>
+          <t>168,871</t>
+        </is>
+      </c>
+      <c r="H25" s="44" t="inlineStr">
+        <is>
+          <t>tr.175</t>
+        </is>
+      </c>
+      <c r="I25" s="44" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="44" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C26" s="44" t="n">
+        <v>46</v>
+      </c>
+      <c r="D26" s="44" t="inlineStr">
+        <is>
+          <t>10. Bê tông thân mố chân dê M1 và mố chữ U M2 mác C30</t>
+        </is>
+      </c>
+      <c r="E26" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 84,600 → 0,000</t>
+        </is>
+      </c>
+      <c r="F26" s="44" t="inlineStr">
+        <is>
+          <t>84,600</t>
+        </is>
+      </c>
+      <c r="G26" s="44" t="inlineStr">
+        <is>
+          <t>0,000</t>
+        </is>
+      </c>
+      <c r="H26" s="44" t="inlineStr">
+        <is>
+          <t>tr.175</t>
+        </is>
+      </c>
+      <c r="I26" s="44" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="44" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C27" s="44" t="n">
+        <v>49</v>
+      </c>
+      <c r="D27" s="44" t="inlineStr">
+        <is>
+          <t>11. Bê tông tường cánh và tường đỉnh mố M1, M2 mác C30</t>
+        </is>
+      </c>
+      <c r="E27" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 20,256 → 29,842. Gộp 'gờ lan can, ụ chống chuyển vị tường tai' của mố (tr.175) vào hạng mục tường cánh/tường đỉnh vì cùng mác C30 — tách mã nếu đơn giá khác.</t>
+        </is>
+      </c>
+      <c r="F27" s="44" t="inlineStr">
+        <is>
+          <t>20,256</t>
+        </is>
+      </c>
+      <c r="G27" s="44" t="inlineStr">
+        <is>
+          <t>29,842</t>
+        </is>
+      </c>
+      <c r="H27" s="44" t="inlineStr">
+        <is>
+          <t>tr.175</t>
+        </is>
+      </c>
+      <c r="I27" s="44" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="44" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C28" s="44" t="n">
+        <v>51</v>
+      </c>
+      <c r="D28" s="44" t="inlineStr">
+        <is>
+          <t>12. Bê tông thân đặc trụ T1 và T2 mác C30</t>
+        </is>
+      </c>
+      <c r="E28" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 281,336 → 234,920. Dự toán cũ ghi H = 14,5 m; cao độ trên bản vẽ cho thân trụ T1 cao khoảng 23,35 m. Đã lấy thể tích bản vẽ.</t>
+        </is>
+      </c>
+      <c r="F28" s="44" t="inlineStr">
+        <is>
+          <t>281,336</t>
+        </is>
+      </c>
+      <c r="G28" s="44" t="inlineStr">
+        <is>
+          <t>234,920</t>
+        </is>
+      </c>
+      <c r="H28" s="44" t="inlineStr">
+        <is>
+          <t>tr.48</t>
+        </is>
+      </c>
+      <c r="I28" s="44" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="44" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C29" s="44" t="n">
+        <v>52</v>
+      </c>
+      <c r="D29" s="44" t="inlineStr">
+        <is>
+          <t>12. Bê tông thân đặc trụ T1 và T2 mác C30</t>
+        </is>
+      </c>
+      <c r="E29" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 221,189 → 266,790. Dự toán cũ ghi H = 11,4 m; cao độ trên bản vẽ cho thân trụ T2 cao khoảng 25,45 m. Đã lấy thể tích bản vẽ.</t>
+        </is>
+      </c>
+      <c r="F29" s="44" t="inlineStr">
+        <is>
+          <t>221,189</t>
+        </is>
+      </c>
+      <c r="G29" s="44" t="inlineStr">
+        <is>
+          <t>266,790</t>
+        </is>
+      </c>
+      <c r="H29" s="44" t="inlineStr">
+        <is>
+          <t>tr.59</t>
+        </is>
+      </c>
+      <c r="I29" s="44" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="44" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C30" s="44" t="n">
+        <v>54</v>
+      </c>
+      <c r="D30" s="44" t="inlineStr">
+        <is>
+          <t>13. Bê tông xà mũ trụ T1, T2 mác C30</t>
+        </is>
+      </c>
+      <c r="E30" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 73,062 → 72,510</t>
+        </is>
+      </c>
+      <c r="F30" s="44" t="inlineStr">
+        <is>
+          <t>73,062</t>
+        </is>
+      </c>
+      <c r="G30" s="44" t="inlineStr">
+        <is>
+          <t>72,510</t>
+        </is>
+      </c>
+      <c r="H30" s="44" t="inlineStr">
+        <is>
+          <t>tr.51</t>
+        </is>
+      </c>
+      <c r="I30" s="44" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="44" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C31" s="44" t="n">
+        <v>55</v>
+      </c>
+      <c r="D31" s="44" t="inlineStr">
+        <is>
+          <t>13. Bê tông xà mũ trụ T1, T2 mác C30</t>
+        </is>
+      </c>
+      <c r="E31" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 73,062 → 72,510</t>
+        </is>
+      </c>
+      <c r="F31" s="44" t="inlineStr">
+        <is>
+          <t>73,062</t>
+        </is>
+      </c>
+      <c r="G31" s="44" t="inlineStr">
+        <is>
+          <t>72,510</t>
+        </is>
+      </c>
+      <c r="H31" s="44" t="inlineStr">
+        <is>
+          <t>tr.62</t>
+        </is>
+      </c>
+      <c r="I31" s="44" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="44" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C32" s="44" t="n">
+        <v>57</v>
+      </c>
+      <c r="D32" s="44" t="inlineStr">
+        <is>
+          <t>14. Cốt thép mố và trụ (D&lt;=10, 10&lt;D&lt;=18, D&gt;18)</t>
+        </is>
+      </c>
+      <c r="E32" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 23,450 → 7,959</t>
+        </is>
+      </c>
+      <c r="F32" s="44" t="inlineStr">
+        <is>
+          <t>23,450</t>
+        </is>
+      </c>
+      <c r="G32" s="44" t="inlineStr">
+        <is>
+          <t>7,959</t>
+        </is>
+      </c>
+      <c r="H32" s="44" t="inlineStr">
+        <is>
+          <t>tr.31</t>
+        </is>
+      </c>
+      <c r="I32" s="44" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C33" s="44" t="n">
+        <v>58</v>
+      </c>
+      <c r="D33" s="44" t="inlineStr">
+        <is>
+          <t>14. Cốt thép mố và trụ (D&lt;=10, 10&lt;D&lt;=18, D&gt;18)</t>
+        </is>
+      </c>
+      <c r="E33" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 31,850 → 19,649</t>
+        </is>
+      </c>
+      <c r="F33" s="44" t="inlineStr">
+        <is>
+          <t>31,850</t>
+        </is>
+      </c>
+      <c r="G33" s="44" t="inlineStr">
+        <is>
+          <t>19,649</t>
+        </is>
+      </c>
+      <c r="H33" s="44" t="inlineStr">
+        <is>
+          <t>tr.40</t>
+        </is>
+      </c>
+      <c r="I33" s="44" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="44" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C34" s="44" t="n">
+        <v>59</v>
+      </c>
+      <c r="D34" s="44" t="inlineStr">
+        <is>
+          <t>14. Cốt thép mố và trụ (D&lt;=10, 10&lt;D&lt;=18, D&gt;18)</t>
+        </is>
+      </c>
+      <c r="E34" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 38,600 → 61,749</t>
+        </is>
+      </c>
+      <c r="F34" s="44" t="inlineStr">
+        <is>
+          <t>38,600</t>
+        </is>
+      </c>
+      <c r="G34" s="44" t="inlineStr">
+        <is>
+          <t>61,749</t>
+        </is>
+      </c>
+      <c r="H34" s="44" t="inlineStr">
+        <is>
+          <t>tr.44, tr.48, tr.51</t>
+        </is>
+      </c>
+      <c r="I34" s="44" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="44" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C35" s="44" t="n">
+        <v>60</v>
+      </c>
+      <c r="D35" s="44" t="inlineStr">
+        <is>
+          <t>14. Cốt thép mố và trụ (D&lt;=10, 10&lt;D&lt;=18, D&gt;18)</t>
+        </is>
+      </c>
+      <c r="E35" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 34,200 → 64,378</t>
+        </is>
+      </c>
+      <c r="F35" s="44" t="inlineStr">
+        <is>
+          <t>34,200</t>
+        </is>
+      </c>
+      <c r="G35" s="44" t="inlineStr">
+        <is>
+          <t>64,378</t>
+        </is>
+      </c>
+      <c r="H35" s="44" t="inlineStr">
+        <is>
+          <t>tr.55, tr.59, tr.62</t>
+        </is>
+      </c>
+      <c r="I35" s="44" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="44" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C36" s="44" t="n">
+        <v>65</v>
+      </c>
+      <c r="D36" s="44" t="inlineStr">
+        <is>
+          <t>16. Cáp dự ứng lực tao xoắn 15.2mm Grade 270 kéo căng trước/sau</t>
+        </is>
+      </c>
+      <c r="E36" s="44" t="inlineStr">
+        <is>
+          <t>Khớp bản vẽ. Dòng tiêu đề cũ ghi cứng 27,784 t, khác dòng diễn giải (15 × 1,994 = 29,91 t). Bảng tổng hợp tr.175 ghi 29,911 t — đã lấy theo bản vẽ và đổi tiêu đề thành tổng công thức.</t>
+        </is>
+      </c>
+      <c r="F36" s="44" t="inlineStr">
+        <is>
+          <t>29,910</t>
+        </is>
+      </c>
+      <c r="G36" s="44" t="inlineStr">
+        <is>
+          <t>29,911</t>
+        </is>
+      </c>
+      <c r="H36" s="44" t="inlineStr">
+        <is>
+          <t>tr.175</t>
+        </is>
+      </c>
+      <c r="I36" s="44" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="44" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C37" s="44" t="n">
+        <v>67</v>
+      </c>
+      <c r="D37" s="44" t="inlineStr">
+        <is>
+          <t>17. Cốt thép thường dầm chủ Super-T (D10, D14, D16, D20)</t>
+        </is>
+      </c>
+      <c r="E37" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 90,630 → 89,690. Dòng tiêu đề cũ ghi cứng 361,596 t (= BBS cũ, gấp khoảng 4 lần bản vẽ). Bản vẽ: 89,690 t = tr.175 (77,743 + 11,947 t). Số phiến 3/3/9 suy từ tổng tr.175 — xác nhận theo mặt cắt ngang.</t>
+        </is>
+      </c>
+      <c r="F37" s="44" t="inlineStr">
+        <is>
+          <t>90,630</t>
+        </is>
+      </c>
+      <c r="G37" s="44" t="inlineStr">
+        <is>
+          <t>89,690</t>
+        </is>
+      </c>
+      <c r="H37" s="44" t="inlineStr">
+        <is>
+          <t>tr.88, tr.91, tr.94</t>
+        </is>
+      </c>
+      <c r="I37" s="44" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="44" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C38" s="44" t="n">
+        <v>74</v>
+      </c>
+      <c r="D38" s="44" t="inlineStr">
+        <is>
+          <t>20. Bê tông dầm ngang mố và trụ mác C35</t>
+        </is>
+      </c>
+      <c r="E38" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 39,852 → 19,380. Dự toán cũ: 4 dầm 12,3 × 0,45 × 1,8 m. Bản vẽ tr.96 và tr.175 ghi 19,38 m³.</t>
+        </is>
+      </c>
+      <c r="F38" s="44" t="inlineStr">
+        <is>
+          <t>39,852</t>
+        </is>
+      </c>
+      <c r="G38" s="44" t="inlineStr">
+        <is>
+          <t>19,380</t>
+        </is>
+      </c>
+      <c r="H38" s="44" t="inlineStr">
+        <is>
+          <t>tr.96</t>
+        </is>
+      </c>
+      <c r="I38" s="44" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="44" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C39" s="44" t="n">
+        <v>80</v>
+      </c>
+      <c r="D39" s="44" t="inlineStr">
+        <is>
+          <t>23. Bê tông mối nối liên tục nhiệt đỉnh trụ T1, T2 mác C35</t>
+        </is>
+      </c>
+      <c r="E39" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 21,799 → 21,868</t>
+        </is>
+      </c>
+      <c r="F39" s="44" t="inlineStr">
+        <is>
+          <t>21,799</t>
+        </is>
+      </c>
+      <c r="G39" s="44" t="inlineStr">
+        <is>
+          <t>21,868</t>
+        </is>
+      </c>
+      <c r="H39" s="44" t="inlineStr">
+        <is>
+          <t>tr.175</t>
+        </is>
+      </c>
+      <c r="I39" s="44" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="44" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C40" s="44" t="n">
+        <v>82</v>
+      </c>
+      <c r="D40" s="44" t="inlineStr">
+        <is>
+          <t>24. Cốt thép bản mặt cầu và mối nối liên tục nhiệt (D14, D16)</t>
+        </is>
+      </c>
+      <c r="E40" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 33,070 → 85,595. Dự toán cũ 33,07 t. Bản vẽ tr.175: 85,595 t (khớp tr.112: 2 × 25.691,33 + 25.293,79 + 2 × 4.458,97 kg).</t>
+        </is>
+      </c>
+      <c r="F40" s="44" t="inlineStr">
+        <is>
+          <t>33,070</t>
+        </is>
+      </c>
+      <c r="G40" s="44" t="inlineStr">
+        <is>
+          <t>85,595</t>
+        </is>
+      </c>
+      <c r="H40" s="44" t="inlineStr">
+        <is>
+          <t>tr.175</t>
+        </is>
+      </c>
+      <c r="I40" s="44" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="44" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C41" s="44" t="n">
+        <v>87</v>
+      </c>
+      <c r="D41" s="44" t="inlineStr">
+        <is>
+          <t>26. Bê tông bản quá độ sau mố M1, M2 mác C25</t>
+        </is>
+      </c>
+      <c r="E41" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 33,691 → 29,100</t>
+        </is>
+      </c>
+      <c r="F41" s="44" t="inlineStr">
+        <is>
+          <t>33,691</t>
+        </is>
+      </c>
+      <c r="G41" s="44" t="inlineStr">
+        <is>
+          <t>29,100</t>
+        </is>
+      </c>
+      <c r="H41" s="44" t="inlineStr">
+        <is>
+          <t>tr.126</t>
+        </is>
+      </c>
+      <c r="I41" s="44" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="44" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C42" s="44" t="n">
+        <v>88</v>
+      </c>
+      <c r="D42" s="44" t="inlineStr">
+        <is>
+          <t>26. Bê tông bản quá độ sau mố M1, M2 mác C25</t>
+        </is>
+      </c>
+      <c r="E42" s="44" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ: 33,691 → 38,280</t>
+        </is>
+      </c>
+      <c r="F42" s="44" t="inlineStr">
+        <is>
+          <t>33,691</t>
+        </is>
+      </c>
+      <c r="G42" s="44" t="inlineStr">
+        <is>
+          <t>38,280</t>
+        </is>
+      </c>
+      <c r="H42" s="44" t="inlineStr">
+        <is>
+          <t>tr.128</t>
+        </is>
+      </c>
+      <c r="I42" s="44" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="44" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C43" s="44" t="n">
+        <v>90</v>
+      </c>
+      <c r="D43" s="44" t="inlineStr">
+        <is>
+          <t>27. Đắp vật liệu dạng hạt chọn lọc sau mố đầm chặt K &gt;= 0.98</t>
+        </is>
+      </c>
+      <c r="E43" s="44" t="inlineStr">
+        <is>
+          <t>Khớp bản vẽ. Dự toán cũ diễn giải 'đắp chuyển tiếp sau mố' 2 × 18 × 12,5 × 4,5 × 0,5 = 1.012,5 m³; tr.175 ghi 'vật liệu dạng hạt trong lòng mố K98' 1.012,955 m³ — xác nhận đúng hạng mục.</t>
+        </is>
+      </c>
+      <c r="F43" s="44" t="inlineStr">
+        <is>
+          <t>1.012,500</t>
+        </is>
+      </c>
+      <c r="G43" s="44" t="inlineStr">
+        <is>
+          <t>1.012,955</t>
+        </is>
+      </c>
+      <c r="H43" s="44" t="inlineStr">
+        <is>
+          <t>tr.175</t>
+        </is>
+      </c>
+      <c r="I43" s="44" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="44" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C44" s="44" t="n">
+        <v>33</v>
+      </c>
+      <c r="D44" s="44" t="inlineStr">
+        <is>
+          <t>7. Đào đất đá hố móng bệ mố M1, M2 và bệ trụ T1, T2 (Link Sheet Đào Đắp)</t>
+        </is>
+      </c>
+      <c r="E44" s="44" t="inlineStr">
+        <is>
+          <t>Khối lượng đào lấy từ sheet đào đắp (6.245 m³) — chưa đối chiếu bản vẽ.</t>
+        </is>
+      </c>
+      <c r="F44" s="44" t="inlineStr"/>
+      <c r="G44" s="44" t="inlineStr"/>
+      <c r="H44" s="44" t="inlineStr"/>
+      <c r="I44" s="44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C45" s="44" t="n">
+        <v>92</v>
+      </c>
+      <c r="D45" s="44" t="inlineStr">
+        <is>
+          <t>28. Bê tông gờ lan can mác C25 và lắp tay vịn thép mạ kẽm</t>
+        </is>
+      </c>
+      <c r="E45" s="44" t="inlineStr">
+        <is>
+          <t>Gờ lan can tính theo m dài (2 × 130,4 m). Bản vẽ tr.119/tr.175: bê tông 104,277 m³ C25 và cốt thép 20,069 t — thép gờ lan can chưa có trong dự toán; đơn giá 1.650.000 đ/m giống đơn giá m³.</t>
+        </is>
+      </c>
+      <c r="F45" s="44" t="inlineStr"/>
+      <c r="G45" s="44" t="inlineStr"/>
+      <c r="H45" s="44" t="inlineStr"/>
+      <c r="I45" s="44" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" s="44" t="inlineStr">
+        <is>
+          <t>QS_DIEN_GIAI_CHI_TIET</t>
+        </is>
+      </c>
+      <c r="C46" s="44" t="n">
+        <v>98</v>
+      </c>
+      <c r="D46" s="44" t="inlineStr">
+        <is>
+          <t>31. Gia cố mái taluy tứ nón mố bằng đá hộc xây vữa VXM M100</t>
+        </is>
+      </c>
+      <c r="E46" s="44" t="inlineStr">
+        <is>
+          <t>Tứ nón đá hộc 52,216 m³ — tr.175 ghi 'đá hộc xây vữa' 104,738 m³ và 'chân khay đá hộc' 4,0 m³ (đường sau mố). Chưa rõ tương ứng — soát PDF tr.175.</t>
+        </is>
+      </c>
+      <c r="F46" s="44" t="inlineStr"/>
+      <c r="G46" s="44" t="inlineStr"/>
+      <c r="H46" s="44" t="inlineStr"/>
+      <c r="I46" s="44" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="44" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C47" s="44" t="n">
+        <v>8</v>
+      </c>
+      <c r="D47" s="44" t="inlineStr">
+        <is>
+          <t>1. Khoan tạo lỗ cọc khoan nhồi D1200mm vào đất và đá gốc (26 cọc)</t>
+        </is>
+      </c>
+      <c r="E47" s="44" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D8*1.0). Ghi chú cột L 'Nghiệm thu 100% 26 cọc' là số cũ, không cập nhật theo D — soát lại</t>
+        </is>
+      </c>
+      <c r="F47" s="44" t="inlineStr"/>
+      <c r="G47" s="44" t="inlineStr"/>
+      <c r="H47" s="44" t="inlineStr"/>
+      <c r="I47" s="44" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="44" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C48" s="44" t="n">
+        <v>9</v>
+      </c>
+      <c r="D48" s="44" t="inlineStr">
+        <is>
+          <t>2. Hạ và nhổ ống vách thép dẫn hướng D1300mm d=8mm</t>
+        </is>
+      </c>
+      <c r="E48" s="44" t="inlineStr">
+        <is>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J13 → =QS_DIEN_GIAI_CHI_TIET!J12 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
+        </is>
+      </c>
+      <c r="F48" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J13</f>
+        <v/>
+      </c>
+      <c r="G48" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J12</f>
+        <v/>
+      </c>
+      <c r="H48" s="44" t="inlineStr"/>
+      <c r="I48" s="44" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="44" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C49" s="44" t="n">
+        <v>9</v>
+      </c>
+      <c r="D49" s="44" t="inlineStr">
+        <is>
+          <t>2. Hạ và nhổ ống vách thép dẫn hướng D1300mm d=8mm</t>
+        </is>
+      </c>
+      <c r="E49" s="44" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D9*1.0)</t>
+        </is>
+      </c>
+      <c r="F49" s="44" t="inlineStr"/>
+      <c r="G49" s="44" t="inlineStr"/>
+      <c r="H49" s="44" t="inlineStr"/>
+      <c r="I49" s="44" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="44" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C50" s="44" t="n">
+        <v>10</v>
+      </c>
+      <c r="D50" s="44" t="inlineStr">
+        <is>
+          <t>3. Bê tông cọc khoan nhồi C30/37 đổ bằng ống tremie</t>
+        </is>
+      </c>
+      <c r="E50" s="44" t="inlineStr">
+        <is>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J18 → =QS_DIEN_GIAI_CHI_TIET!J17 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
+        </is>
+      </c>
+      <c r="F50" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J18</f>
+        <v/>
+      </c>
+      <c r="G50" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J17</f>
+        <v/>
+      </c>
+      <c r="H50" s="44" t="inlineStr"/>
+      <c r="I50" s="44" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="44" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C51" s="44" t="n">
+        <v>10</v>
+      </c>
+      <c r="D51" s="44" t="inlineStr">
+        <is>
+          <t>3. Bê tông cọc khoan nhồi C30/37 đổ bằng ống tremie</t>
+        </is>
+      </c>
+      <c r="E51" s="44" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D10*1.0). Ghi chú cột L 'Đổ xong 1100.86 m3' là số cũ, không cập nhật theo D — soát lại</t>
+        </is>
+      </c>
+      <c r="F51" s="44" t="inlineStr"/>
+      <c r="G51" s="44" t="inlineStr"/>
+      <c r="H51" s="44" t="inlineStr"/>
+      <c r="I51" s="44" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="44" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C52" s="44" t="n">
+        <v>11</v>
+      </c>
+      <c r="D52" s="44" t="inlineStr">
+        <is>
+          <t>4. Cốt thép cọc khoan nhồi D1200mm (D25, D16, D10)</t>
+        </is>
+      </c>
+      <c r="E52" s="44" t="inlineStr">
+        <is>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J23 → =QS_DIEN_GIAI_CHI_TIET!J22 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
+        </is>
+      </c>
+      <c r="F52" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J23</f>
+        <v/>
+      </c>
+      <c r="G52" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J22</f>
+        <v/>
+      </c>
+      <c r="H52" s="44" t="inlineStr"/>
+      <c r="I52" s="44" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="44" t="n">
+        <v>50</v>
+      </c>
+      <c r="B53" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C53" s="44" t="n">
+        <v>11</v>
+      </c>
+      <c r="D53" s="44" t="inlineStr">
+        <is>
+          <t>4. Cốt thép cọc khoan nhồi D1200mm (D25, D16, D10)</t>
+        </is>
+      </c>
+      <c r="E53" s="44" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D11*1.0). Ghi chú cột L '118.98 tấn' là số cũ, không cập nhật theo D — soát lại</t>
+        </is>
+      </c>
+      <c r="F53" s="44" t="inlineStr"/>
+      <c r="G53" s="44" t="inlineStr"/>
+      <c r="H53" s="44" t="inlineStr"/>
+      <c r="I53" s="44" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="44" t="n">
+        <v>51</v>
+      </c>
+      <c r="B54" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C54" s="44" t="n">
+        <v>12</v>
+      </c>
+      <c r="D54" s="44" t="inlineStr">
+        <is>
+          <t>5. Đập đầu 26 cọc khoan nhồi ngàm vào đài móng</t>
+        </is>
+      </c>
+      <c r="E54" s="44" t="inlineStr">
+        <is>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J28 → =QS_DIEN_GIAI_CHI_TIET!J27 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
+        </is>
+      </c>
+      <c r="F54" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J28</f>
+        <v/>
+      </c>
+      <c r="G54" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J27</f>
+        <v/>
+      </c>
+      <c r="H54" s="44" t="inlineStr"/>
+      <c r="I54" s="44" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="44" t="n">
+        <v>52</v>
+      </c>
+      <c r="B55" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C55" s="44" t="n">
+        <v>12</v>
+      </c>
+      <c r="D55" s="44" t="inlineStr">
+        <is>
+          <t>5. Đập đầu 26 cọc khoan nhồi ngàm vào đài móng</t>
+        </is>
+      </c>
+      <c r="E55" s="44" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D12*1.0)</t>
+        </is>
+      </c>
+      <c r="F55" s="44" t="inlineStr"/>
+      <c r="G55" s="44" t="inlineStr"/>
+      <c r="H55" s="44" t="inlineStr"/>
+      <c r="I55" s="44" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="44" t="n">
+        <v>53</v>
+      </c>
+      <c r="B56" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C56" s="44" t="n">
+        <v>13</v>
+      </c>
+      <c r="D56" s="44" t="inlineStr">
+        <is>
+          <t>6. Gói thí nghiệm kiểm soát cọc (Siêu âm 156 MC, PDA 9434kN, lấy lõi)</t>
+        </is>
+      </c>
+      <c r="E56" s="44" t="inlineStr">
+        <is>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J30 → =QS_DIEN_GIAI_CHI_TIET!J29 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
+        </is>
+      </c>
+      <c r="F56" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J30</f>
+        <v/>
+      </c>
+      <c r="G56" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J29</f>
+        <v/>
+      </c>
+      <c r="H56" s="44" t="inlineStr"/>
+      <c r="I56" s="44" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="44" t="n">
+        <v>54</v>
+      </c>
+      <c r="B57" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C57" s="44" t="n">
+        <v>13</v>
+      </c>
+      <c r="D57" s="44" t="inlineStr">
+        <is>
+          <t>6. Gói thí nghiệm kiểm soát cọc (Siêu âm 156 MC, PDA 9434kN, lấy lõi)</t>
+        </is>
+      </c>
+      <c r="E57" s="44" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D13*1.0)</t>
+        </is>
+      </c>
+      <c r="F57" s="44" t="inlineStr"/>
+      <c r="G57" s="44" t="inlineStr"/>
+      <c r="H57" s="44" t="inlineStr"/>
+      <c r="I57" s="44" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="44" t="n">
+        <v>55</v>
+      </c>
+      <c r="B58" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C58" s="44" t="n">
+        <v>15</v>
+      </c>
+      <c r="D58" s="44" t="inlineStr">
+        <is>
+          <t>7. Đào đất đá hố móng bệ mố M1, M2 và bệ trụ T1, T2</t>
+        </is>
+      </c>
+      <c r="E58" s="44" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D15*1.0)</t>
+        </is>
+      </c>
+      <c r="F58" s="44" t="inlineStr"/>
+      <c r="G58" s="44" t="inlineStr"/>
+      <c r="H58" s="44" t="inlineStr"/>
+      <c r="I58" s="44" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="44" t="n">
+        <v>56</v>
+      </c>
+      <c r="B59" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C59" s="44" t="n">
+        <v>16</v>
+      </c>
+      <c r="D59" s="44" t="inlineStr">
+        <is>
+          <t>8. Bê tông lót đáy bệ móng mác C10 dày 10cm</t>
+        </is>
+      </c>
+      <c r="E59" s="44" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D16*1.0). Ghi chú cột L 'Đổ xong 4 hố móng' là số cũ, không cập nhật theo D — soát lại</t>
+        </is>
+      </c>
+      <c r="F59" s="44" t="inlineStr"/>
+      <c r="G59" s="44" t="inlineStr"/>
+      <c r="H59" s="44" t="inlineStr"/>
+      <c r="I59" s="44" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="44" t="n">
+        <v>57</v>
+      </c>
+      <c r="B60" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C60" s="44" t="n">
+        <v>17</v>
+      </c>
+      <c r="D60" s="44" t="inlineStr">
+        <is>
+          <t>9. Bê tông bệ móng mố M1, M2 và bệ trụ T1, T2 mác C30</t>
+        </is>
+      </c>
+      <c r="E60" s="44" t="inlineStr">
+        <is>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J37 → =QS_DIEN_GIAI_CHI_TIET!J39 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
+        </is>
+      </c>
+      <c r="F60" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J37</f>
+        <v/>
+      </c>
+      <c r="G60" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J39</f>
+        <v/>
+      </c>
+      <c r="H60" s="44" t="inlineStr"/>
+      <c r="I60" s="44" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="44" t="n">
+        <v>58</v>
+      </c>
+      <c r="B61" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C61" s="44" t="n">
+        <v>17</v>
+      </c>
+      <c r="D61" s="44" t="inlineStr">
+        <is>
+          <t>9. Bê tông bệ móng mố M1, M2 và bệ trụ T1, T2 mác C30</t>
+        </is>
+      </c>
+      <c r="E61" s="44" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D17*1.0). Ghi chú cột L '517.48 m3 đạt R28' là số cũ, không cập nhật theo D — soát lại</t>
+        </is>
+      </c>
+      <c r="F61" s="44" t="inlineStr"/>
+      <c r="G61" s="44" t="inlineStr"/>
+      <c r="H61" s="44" t="inlineStr"/>
+      <c r="I61" s="44" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="44" t="n">
+        <v>59</v>
+      </c>
+      <c r="B62" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C62" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D62" s="44" t="inlineStr">
+        <is>
+          <t>10. Bê tông thân mố chân dê M1 và mố chữ U M2 mác C30</t>
+        </is>
+      </c>
+      <c r="E62" s="44" t="inlineStr">
+        <is>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J42 → =QS_DIEN_GIAI_CHI_TIET!J44 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
+        </is>
+      </c>
+      <c r="F62" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J42</f>
+        <v/>
+      </c>
+      <c r="G62" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J44</f>
+        <v/>
+      </c>
+      <c r="H62" s="44" t="inlineStr"/>
+      <c r="I62" s="44" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="44" t="n">
+        <v>60</v>
+      </c>
+      <c r="B63" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C63" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D63" s="44" t="inlineStr">
+        <is>
+          <t>10. Bê tông thân mố chân dê M1 và mố chữ U M2 mác C30</t>
+        </is>
+      </c>
+      <c r="E63" s="44" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D18*0.8). Ghi chú cột L 'Nghiệm thu đợt 1 thân mố' là số cũ, không cập nhật theo D — soát lại</t>
+        </is>
+      </c>
+      <c r="F63" s="44" t="inlineStr"/>
+      <c r="G63" s="44" t="inlineStr"/>
+      <c r="H63" s="44" t="inlineStr"/>
+      <c r="I63" s="44" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="44" t="n">
+        <v>61</v>
+      </c>
+      <c r="B64" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C64" s="44" t="n">
+        <v>19</v>
+      </c>
+      <c r="D64" s="44" t="inlineStr">
+        <is>
+          <t>11. Bê tông thân đặc trụ T1 và T2 mác C30 (H=14.5m &amp; 11.4m)</t>
+        </is>
+      </c>
+      <c r="E64" s="44" t="inlineStr">
+        <is>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J47 → =QS_DIEN_GIAI_CHI_TIET!J50 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
+        </is>
+      </c>
+      <c r="F64" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J47</f>
+        <v/>
+      </c>
+      <c r="G64" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J50</f>
+        <v/>
+      </c>
+      <c r="H64" s="44" t="inlineStr"/>
+      <c r="I64" s="44" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="44" t="n">
+        <v>62</v>
+      </c>
+      <c r="B65" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C65" s="44" t="n">
+        <v>19</v>
+      </c>
+      <c r="D65" s="44" t="inlineStr">
+        <is>
+          <t>11. Bê tông thân đặc trụ T1 và T2 mác C30</t>
+        </is>
+      </c>
+      <c r="E65" s="44" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D19*0.75). Ghi chú cột L 'Đổ 3/4 chiều cao trụ' là số cũ, không cập nhật theo D — soát lại</t>
+        </is>
+      </c>
+      <c r="F65" s="44" t="inlineStr"/>
+      <c r="G65" s="44" t="inlineStr"/>
+      <c r="H65" s="44" t="inlineStr"/>
+      <c r="I65" s="44" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="44" t="n">
+        <v>63</v>
+      </c>
+      <c r="B66" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C66" s="44" t="n">
+        <v>20</v>
+      </c>
+      <c r="D66" s="44" t="inlineStr">
+        <is>
+          <t>12. Cốt thép mố và trụ (D&lt;=10, 10&lt;D&lt;=18, D&gt;18)</t>
+        </is>
+      </c>
+      <c r="E66" s="44" t="inlineStr">
+        <is>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J53 → =QS_DIEN_GIAI_CHI_TIET!J56 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
+        </is>
+      </c>
+      <c r="F66" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J53</f>
+        <v/>
+      </c>
+      <c r="G66" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J56</f>
+        <v/>
+      </c>
+      <c r="H66" s="44" t="inlineStr"/>
+      <c r="I66" s="44" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="44" t="n">
+        <v>64</v>
+      </c>
+      <c r="B67" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C67" s="44" t="n">
+        <v>20</v>
+      </c>
+      <c r="D67" s="44" t="inlineStr">
+        <is>
+          <t>12. Cốt thép mố và trụ (D&lt;=10, 10&lt;D&lt;=18, D&gt;18)</t>
+        </is>
+      </c>
+      <c r="E67" s="44" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D20*0.8). Ghi chú cột L 'Lắp dựng nghiệm thu đợt 1' là số cũ, không cập nhật theo D — soát lại</t>
+        </is>
+      </c>
+      <c r="F67" s="44" t="inlineStr"/>
+      <c r="G67" s="44" t="inlineStr"/>
+      <c r="H67" s="44" t="inlineStr"/>
+      <c r="I67" s="44" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="44" t="n">
+        <v>65</v>
+      </c>
+      <c r="B68" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C68" s="44" t="n">
+        <v>22</v>
+      </c>
+      <c r="D68" s="44" t="inlineStr">
+        <is>
+          <t>13. Bê tông dầm chủ Super-T L=38.2m mác cao C45/55</t>
+        </is>
+      </c>
+      <c r="E68" s="44" t="inlineStr">
+        <is>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J57 → =QS_DIEN_GIAI_CHI_TIET!J62 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
+        </is>
+      </c>
+      <c r="F68" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J57</f>
+        <v/>
+      </c>
+      <c r="G68" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J62</f>
+        <v/>
+      </c>
+      <c r="H68" s="44" t="inlineStr"/>
+      <c r="I68" s="44" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="44" t="n">
+        <v>66</v>
+      </c>
+      <c r="B69" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C69" s="44" t="n">
+        <v>22</v>
+      </c>
+      <c r="D69" s="44" t="inlineStr">
+        <is>
+          <t>13. Bê tông dầm chủ Super-T L=38.2m mác cao C45/55</t>
+        </is>
+      </c>
+      <c r="E69" s="44" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D22*0.6). Ghi chú cột L 'Đúc xong 9/15 phiến dầm' là số cũ, không cập nhật theo D — soát lại</t>
+        </is>
+      </c>
+      <c r="F69" s="44" t="inlineStr"/>
+      <c r="G69" s="44" t="inlineStr"/>
+      <c r="H69" s="44" t="inlineStr"/>
+      <c r="I69" s="44" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="44" t="n">
+        <v>67</v>
+      </c>
+      <c r="B70" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C70" s="44" t="n">
+        <v>23</v>
+      </c>
+      <c r="D70" s="44" t="inlineStr">
+        <is>
+          <t>14. Cáp dự ứng lực tao xoắn 15.2mm Grade 270 kéo căng</t>
+        </is>
+      </c>
+      <c r="E70" s="44" t="inlineStr">
+        <is>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J59 → =QS_DIEN_GIAI_CHI_TIET!J64 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
+        </is>
+      </c>
+      <c r="F70" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J59</f>
+        <v/>
+      </c>
+      <c r="G70" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J64</f>
+        <v/>
+      </c>
+      <c r="H70" s="44" t="inlineStr"/>
+      <c r="I70" s="44" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="44" t="n">
+        <v>68</v>
+      </c>
+      <c r="B71" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C71" s="44" t="n">
+        <v>23</v>
+      </c>
+      <c r="D71" s="44" t="inlineStr">
+        <is>
+          <t>14. Cáp dự ứng lực tao xoắn 15.2mm Grade 270 kéo căng</t>
+        </is>
+      </c>
+      <c r="E71" s="44" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D23*0.6). Ghi chú cột L 'Căng kéo 9 phiến dầm' là số cũ, không cập nhật theo D — soát lại</t>
+        </is>
+      </c>
+      <c r="F71" s="44" t="inlineStr"/>
+      <c r="G71" s="44" t="inlineStr"/>
+      <c r="H71" s="44" t="inlineStr"/>
+      <c r="I71" s="44" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="44" t="n">
+        <v>69</v>
+      </c>
+      <c r="B72" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C72" s="44" t="n">
+        <v>24</v>
+      </c>
+      <c r="D72" s="44" t="inlineStr">
+        <is>
+          <t>15. Cốt thép thường dầm chủ Super-T (D10, D14, D16, D20)</t>
+        </is>
+      </c>
+      <c r="E72" s="44" t="inlineStr">
+        <is>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J61 → =QS_DIEN_GIAI_CHI_TIET!J66 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
+        </is>
+      </c>
+      <c r="F72" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J61</f>
+        <v/>
+      </c>
+      <c r="G72" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J66</f>
+        <v/>
+      </c>
+      <c r="H72" s="44" t="inlineStr"/>
+      <c r="I72" s="44" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="44" t="n">
+        <v>70</v>
+      </c>
+      <c r="B73" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C73" s="44" t="n">
+        <v>24</v>
+      </c>
+      <c r="D73" s="44" t="inlineStr">
+        <is>
+          <t>15. Cốt thép thường dầm chủ Super-T (D10, D14, D16, D20)</t>
+        </is>
+      </c>
+      <c r="E73" s="44" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D24*0.6). Ghi chú cột L '9 phiến dầm' là số cũ, không cập nhật theo D — soát lại</t>
+        </is>
+      </c>
+      <c r="F73" s="44" t="inlineStr"/>
+      <c r="G73" s="44" t="inlineStr"/>
+      <c r="H73" s="44" t="inlineStr"/>
+      <c r="I73" s="44" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="44" t="n">
+        <v>71</v>
+      </c>
+      <c r="B74" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C74" s="44" t="n">
+        <v>25</v>
+      </c>
+      <c r="D74" s="44" t="inlineStr">
+        <is>
+          <t>16. Vận chuyển và lao lắp 15 phiến dầm Super-T (chưa thi công)</t>
+        </is>
+      </c>
+      <c r="E74" s="44" t="inlineStr">
+        <is>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J63 → =QS_DIEN_GIAI_CHI_TIET!J68 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
+        </is>
+      </c>
+      <c r="F74" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J63</f>
+        <v/>
+      </c>
+      <c r="G74" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J68</f>
+        <v/>
+      </c>
+      <c r="H74" s="44" t="inlineStr"/>
+      <c r="I74" s="44" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="44" t="n">
+        <v>72</v>
+      </c>
+      <c r="B75" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C75" s="44" t="n">
+        <v>25</v>
+      </c>
+      <c r="D75" s="44" t="inlineStr">
+        <is>
+          <t>16. Vận chuyển và lao lắp 15 phiến dầm Super-T (chưa thi công)</t>
+        </is>
+      </c>
+      <c r="E75" s="44" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D25*0.0)</t>
+        </is>
+      </c>
+      <c r="F75" s="44" t="inlineStr"/>
+      <c r="G75" s="44" t="inlineStr"/>
+      <c r="H75" s="44" t="inlineStr"/>
+      <c r="I75" s="44" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="44" t="n">
+        <v>73</v>
+      </c>
+      <c r="B76" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C76" s="44" t="n">
+        <v>26</v>
+      </c>
+      <c r="D76" s="44" t="inlineStr">
+        <is>
+          <t>17. Gối chậu cao su di động đơn hướng và song hướng</t>
+        </is>
+      </c>
+      <c r="E76" s="44" t="inlineStr">
+        <is>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J65 → =QS_DIEN_GIAI_CHI_TIET!J70 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
+        </is>
+      </c>
+      <c r="F76" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J65</f>
+        <v/>
+      </c>
+      <c r="G76" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J70</f>
+        <v/>
+      </c>
+      <c r="H76" s="44" t="inlineStr"/>
+      <c r="I76" s="44" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="44" t="n">
+        <v>74</v>
+      </c>
+      <c r="B77" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C77" s="44" t="n">
+        <v>26</v>
+      </c>
+      <c r="D77" s="44" t="inlineStr">
+        <is>
+          <t>17. Gối chậu cao su di động đơn hướng và song hướng</t>
+        </is>
+      </c>
+      <c r="E77" s="44" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D26*0.0)</t>
+        </is>
+      </c>
+      <c r="F77" s="44" t="inlineStr"/>
+      <c r="G77" s="44" t="inlineStr"/>
+      <c r="H77" s="44" t="inlineStr"/>
+      <c r="I77" s="44" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="44" t="n">
+        <v>75</v>
+      </c>
+      <c r="B78" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C78" s="44" t="n">
+        <v>27</v>
+      </c>
+      <c r="D78" s="44" t="inlineStr">
+        <is>
+          <t>18. Bản mặt cầu C35 và mối nối liên tục nhiệt</t>
+        </is>
+      </c>
+      <c r="E78" s="44" t="inlineStr">
+        <is>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J74 → =QS_DIEN_GIAI_CHI_TIET!J77+QS_DIEN_GIAI_CHI_TIET!J79 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
+        </is>
+      </c>
+      <c r="F78" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J74</f>
+        <v/>
+      </c>
+      <c r="G78" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J77+QS_DIEN_GIAI_CHI_TIET!J79</f>
+        <v/>
+      </c>
+      <c r="H78" s="44" t="inlineStr"/>
+      <c r="I78" s="44" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="44" t="n">
+        <v>76</v>
+      </c>
+      <c r="B79" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C79" s="44" t="n">
+        <v>27</v>
+      </c>
+      <c r="D79" s="44" t="inlineStr">
+        <is>
+          <t>18. Bản mặt cầu C35 và mối nối liên tục nhiệt</t>
+        </is>
+      </c>
+      <c r="E79" s="44" t="inlineStr">
+        <is>
+          <t>Gộp bản mặt cầu (QS dòng 77) và liên tục nhiệt (QS dòng 79); đơn giá = bình quân gia quyền theo thành tiền 2 dòng.</t>
+        </is>
+      </c>
+      <c r="F79" s="44" t="inlineStr"/>
+      <c r="G79" s="44" t="inlineStr"/>
+      <c r="H79" s="44" t="inlineStr"/>
+      <c r="I79" s="44" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="44" t="n">
+        <v>77</v>
+      </c>
+      <c r="B80" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C80" s="44" t="n">
+        <v>27</v>
+      </c>
+      <c r="D80" s="44" t="inlineStr">
+        <is>
+          <t>18. Bản mặt cầu C35 và mối nối liên tục nhiệt</t>
+        </is>
+      </c>
+      <c r="E80" s="44" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D27*0.0)</t>
+        </is>
+      </c>
+      <c r="F80" s="44" t="inlineStr"/>
+      <c r="G80" s="44" t="inlineStr"/>
+      <c r="H80" s="44" t="inlineStr"/>
+      <c r="I80" s="44" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="44" t="n">
+        <v>78</v>
+      </c>
+      <c r="B81" s="44" t="inlineStr">
+        <is>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
+        </is>
+      </c>
+      <c r="C81" s="44" t="n">
+        <v>28</v>
+      </c>
+      <c r="D81" s="44" t="inlineStr">
+        <is>
+          <t>TỔNG CỘNG CHI PHÍ XÂY LẮP (VNĐ). None</t>
+        </is>
+      </c>
+      <c r="E81" s="44" t="inlineStr">
+        <is>
+          <t>Chưa có trong 03a: bê tông tường đỉnh/tường cánh mố, xà mũ trụ, dầm ngang, bản quá độ và các hạng mục hoàn thiện (QS dòng 47, 53, 73, 86...) — kiểm tra phạm vi hợp đồng.</t>
+        </is>
+      </c>
+      <c r="F81" s="44" t="inlineStr"/>
+      <c r="G81" s="44" t="inlineStr"/>
+      <c r="H81" s="44" t="inlineStr"/>
+      <c r="I81" s="44" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/examples/HO_SO_CAU_KM19_529/03_KINH_TE_QS_DU_TOAN_THANH_TOAN/09_Thanh_Toan_Khoi_Luong_Phu_Luc_03a.xlsx
+++ b/examples/HO_SO_CAU_KM19_529/03_KINH_TE_QS_DU_TOAN_THANH_TOAN/09_Thanh_Toan_Khoi_Luong_Phu_Luc_03a.xlsx
@@ -4205,7 +4205,7 @@
       <c r="L58" s="26" t="n"/>
       <c r="M58" s="35" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 31,850 → 19,649</t>
+          <t>Theo bản vẽ: 31,850 → 19,649. Tr.40 ghi 0 kg cho W6, W7, W9 dù dài × SL × kg/m = 237,05 kg (51,50 + 48,84 + 136,71). Dòng này lấy tổng bản vẽ 19,649 t; BBS vẫn gia công các thanh đó. Nếu chủ dự án ghim tính thì cộng 0,237 t.</t>
         </is>
       </c>
       <c r="N58" t="n">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="E33" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 31,850 → 19,649</t>
+          <t>Theo bản vẽ: 31,850 → 19,649. Tr.40 ghi 0 kg cho W6, W7, W9 dù dài × SL × kg/m = 237,05 kg (51,50 + 48,84 + 136,71). Dòng này lấy tổng bản vẽ 19,649 t; BBS vẫn gia công các thanh đó. Nếu chủ dự án ghim tính thì cộng 0,237 t.</t>
         </is>
       </c>
       <c r="F33" s="44" t="inlineStr">

--- a/examples/HO_SO_CAU_KM19_529/03_KINH_TE_QS_DU_TOAN_THANH_TOAN/09_Thanh_Toan_Khoi_Luong_Phu_Luc_03a.xlsx
+++ b/examples/HO_SO_CAU_KM19_529/03_KINH_TE_QS_DU_TOAN_THANH_TOAN/09_Thanh_Toan_Khoi_Luong_Phu_Luc_03a.xlsx
@@ -4174,7 +4174,7 @@
       <c r="B58" s="26" t="n"/>
       <c r="C58" s="27" t="inlineStr">
         <is>
-          <t>- Cốt thép mố M2 (bản vẽ tr.40)</t>
+          <t>- Cốt thép mố M2: tổng bản vẽ tr.40 + W6, W7, W9 (bản vẽ ghi 0 kg)</t>
         </is>
       </c>
       <c r="D58" s="28" t="inlineStr">
@@ -4185,8 +4185,9 @@
       <c r="E58" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="F58" s="36" t="n">
-        <v>19.64873</v>
+      <c r="F58" s="36">
+        <f>19.64873+0.23705</f>
+        <v/>
       </c>
       <c r="G58" s="36" t="n">
         <v>1</v>
@@ -4205,7 +4206,7 @@
       <c r="L58" s="26" t="n"/>
       <c r="M58" s="35" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 31,850 → 19,649. Tr.40 ghi 0 kg cho W6, W7, W9 dù dài × SL × kg/m = 237,05 kg (51,50 + 48,84 + 136,71). Dòng này lấy tổng bản vẽ 19,649 t; BBS vẫn gia công các thanh đó. Nếu chủ dự án ghim tính thì cộng 0,237 t.</t>
+          <t>Theo bản vẽ: 31,850 → 19,886. Tr.40 ghi 0 kg cho W6, W7, W9 dù dài × SL × kg/m = 237,05 kg (51,50 + 48,84 + 136,71). Chủ dự án quyết định 11/10/2026 tính các thanh này: 19,649 + 0,237 t.</t>
         </is>
       </c>
       <c r="N58" t="n">
@@ -4229,7 +4230,7 @@
         <v>1</v>
       </c>
       <c r="F59" s="36">
-        <f>16.1778+32.5585+13.0131</f>
+        <f>16.17783+32.55852+13.01311</f>
         <v/>
       </c>
       <c r="G59" s="36" t="n">
@@ -4273,7 +4274,7 @@
         <v>1</v>
       </c>
       <c r="F60" s="36">
-        <f>16.1778+35.1868+13.0131</f>
+        <f>16.17783+35.18685+13.01311</f>
         <v/>
       </c>
       <c r="G60" s="36" t="n">
@@ -7036,7 +7037,7 @@
       </c>
       <c r="E33" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 31,850 → 19,649. Tr.40 ghi 0 kg cho W6, W7, W9 dù dài × SL × kg/m = 237,05 kg (51,50 + 48,84 + 136,71). Dòng này lấy tổng bản vẽ 19,649 t; BBS vẫn gia công các thanh đó. Nếu chủ dự án ghim tính thì cộng 0,237 t.</t>
+          <t>Theo bản vẽ: 31,850 → 19,886. Tr.40 ghi 0 kg cho W6, W7, W9 dù dài × SL × kg/m = 237,05 kg (51,50 + 48,84 + 136,71). Chủ dự án quyết định 11/10/2026 tính các thanh này: 19,649 + 0,237 t.</t>
         </is>
       </c>
       <c r="F33" s="44" t="inlineStr">
@@ -7046,7 +7047,7 @@
       </c>
       <c r="G33" s="44" t="inlineStr">
         <is>
-          <t>19,649</t>
+          <t>19,886</t>
         </is>
       </c>
       <c r="H33" s="44" t="inlineStr">

--- a/examples/HO_SO_CAU_KM19_529/03_KINH_TE_QS_DU_TOAN_THANH_TOAN/09_Thanh_Toan_Khoi_Luong_Phu_Luc_03a.xlsx
+++ b/examples/HO_SO_CAU_KM19_529/03_KINH_TE_QS_DU_TOAN_THANH_TOAN/09_Thanh_Toan_Khoi_Luong_Phu_Luc_03a.xlsx
@@ -4524,7 +4524,7 @@
       <c r="B67" s="26" t="n"/>
       <c r="C67" s="27" t="inlineStr">
         <is>
-          <t>- Cốt thép thường 15 phiến: 3 × S1B1 (tr.88) + 3 × S1B2 (tr.91) + 9 × S1G (tr.94)</t>
+          <t>- Cốt thép thường 15 phiến: 2 × S1B1 (tr.88) + 3 × S1B2 (tr.91) + 1 × S1B3 (bảng S1B1 tr.88) + 9 × S1G (tr.94)</t>
         </is>
       </c>
       <c r="D67" s="28" t="inlineStr">
@@ -4536,7 +4536,7 @@
         <v>1</v>
       </c>
       <c r="F67" s="36">
-        <f>3*6.07125+3*6.06528+9*5.92008</f>
+        <f>2*6.07125+3*6.06528+6.07125+9*5.92008</f>
         <v/>
       </c>
       <c r="G67" s="36" t="n">
@@ -4556,7 +4556,7 @@
       <c r="L67" s="26" t="n"/>
       <c r="M67" s="35" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 90,630 → 89,690. Dòng tiêu đề cũ ghi cứng 361,596 t (= BBS cũ, gấp khoảng 4 lần bản vẽ). Bản vẽ: 89,690 t = tr.175 (77,743 + 11,947 t). Số phiến 3/3/9 suy từ tổng tr.175 — xác nhận theo mặt cắt ngang.</t>
+          <t>Theo bản vẽ: 90,630 → 89,690. Dòng tiêu đề cũ ghi cứng 361,596 t (= BBS cũ, gấp khoảng 4 lần bản vẽ). Số phiến 2/3/1/9 theo chủ dự án (sơ đồ tr.75). Hồ sơ không có bảng thép S1B3 — tạm dùng bảng S1B1; tổng 89,690 t khớp tr.175 (77,743 + 11,947 t).</t>
         </is>
       </c>
       <c r="N67" t="n">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="E37" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 90,630 → 89,690. Dòng tiêu đề cũ ghi cứng 361,596 t (= BBS cũ, gấp khoảng 4 lần bản vẽ). Bản vẽ: 89,690 t = tr.175 (77,743 + 11,947 t). Số phiến 3/3/9 suy từ tổng tr.175 — xác nhận theo mặt cắt ngang.</t>
+          <t>Theo bản vẽ: 90,630 → 89,690. Dòng tiêu đề cũ ghi cứng 361,596 t (= BBS cũ, gấp khoảng 4 lần bản vẽ). Số phiến 2/3/1/9 theo chủ dự án (sơ đồ tr.75). Hồ sơ không có bảng thép S1B3 — tạm dùng bảng S1B1; tổng 89,690 t khớp tr.175 (77,743 + 11,947 t).</t>
         </is>
       </c>
       <c r="F37" s="44" t="inlineStr">

--- a/examples/HO_SO_CAU_KM19_529/03_KINH_TE_QS_DU_TOAN_THANH_TOAN/09_Thanh_Toan_Khoi_Luong_Phu_Luc_03a.xlsx
+++ b/examples/HO_SO_CAU_KM19_529/03_KINH_TE_QS_DU_TOAN_THANH_TOAN/09_Thanh_Toan_Khoi_Luong_Phu_Luc_03a.xlsx
@@ -4524,7 +4524,7 @@
       <c r="B67" s="26" t="n"/>
       <c r="C67" s="27" t="inlineStr">
         <is>
-          <t>- Cốt thép thường 15 phiến: 2 × S1B1 (tr.88) + 3 × S1B2 (tr.91) + 1 × S1B3 (bảng S1B1 tr.88) + 9 × S1G (tr.94)</t>
+          <t>- Cốt thép thường 15 phiến: 2 × S1B1 (tr.88) + 3 × S1B2 (tr.91) + 1 × S1B3 (bảng thép như S1B1, tr.88) + 9 × S1G (tr.94)</t>
         </is>
       </c>
       <c r="D67" s="28" t="inlineStr">
@@ -4556,7 +4556,7 @@
       <c r="L67" s="26" t="n"/>
       <c r="M67" s="35" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 90,630 → 89,690. Dòng tiêu đề cũ ghi cứng 361,596 t (= BBS cũ, gấp khoảng 4 lần bản vẽ). Số phiến 2/3/1/9 theo chủ dự án (sơ đồ tr.75). Hồ sơ không có bảng thép S1B3 — tạm dùng bảng S1B1; tổng 89,690 t khớp tr.175 (77,743 + 11,947 t).</t>
+          <t>Theo bản vẽ: 90,630 → 89,690. Dòng tiêu đề cũ ghi cứng 361,596 t (= BBS cũ, gấp khoảng 4 lần bản vẽ). Số phiến 2/3/1/9 và S1B3 dùng bảng thép S1B1: chủ dự án xác nhận 11/10/2026 (sơ đồ tr.75); tổng 89,690 t khớp tr.175 (77,743 + 11,947 t).</t>
         </is>
       </c>
       <c r="N67" t="n">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="E37" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 90,630 → 89,690. Dòng tiêu đề cũ ghi cứng 361,596 t (= BBS cũ, gấp khoảng 4 lần bản vẽ). Số phiến 2/3/1/9 theo chủ dự án (sơ đồ tr.75). Hồ sơ không có bảng thép S1B3 — tạm dùng bảng S1B1; tổng 89,690 t khớp tr.175 (77,743 + 11,947 t).</t>
+          <t>Theo bản vẽ: 90,630 → 89,690. Dòng tiêu đề cũ ghi cứng 361,596 t (= BBS cũ, gấp khoảng 4 lần bản vẽ). Số phiến 2/3/1/9 và S1B3 dùng bảng thép S1B1: chủ dự án xác nhận 11/10/2026 (sơ đồ tr.75); tổng 89,690 t khớp tr.175 (77,743 + 11,947 t).</t>
         </is>
       </c>
       <c r="F37" s="44" t="inlineStr">

--- a/examples/HO_SO_CAU_KM19_529/03_KINH_TE_QS_DU_TOAN_THANH_TOAN/09_Thanh_Toan_Khoi_Luong_Phu_Luc_03a.xlsx
+++ b/examples/HO_SO_CAU_KM19_529/03_KINH_TE_QS_DU_TOAN_THANH_TOAN/09_Thanh_Toan_Khoi_Luong_Phu_Luc_03a.xlsx
@@ -2544,7 +2544,7 @@
       <c r="B18" s="26" t="n"/>
       <c r="C18" s="27" t="inlineStr">
         <is>
-          <t>- Bê tông 3 cọc mố M1 L=20m (bản vẽ tr.64, gồm bê tông đầu cọc)</t>
+          <t>- Bê tông 3 cọc mố M1 L=20m (bản vẽ tr.64, gồm bê tông đầu cọc) × hệ số nở thành 1,12</t>
         </is>
       </c>
       <c r="D18" s="28" t="inlineStr">
@@ -2565,7 +2565,7 @@
         <v>1</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="J18" s="41">
         <f>E18*F18*G18*H18*I18</f>
@@ -2575,7 +2575,7 @@
       <c r="L18" s="26" t="n"/>
       <c r="M18" s="35" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 76,002 → 70,740. Bỏ hệ số I = 3,5186 (π × 1,12 nở thành): lấy thể tích thiết kế tr.64. Nếu hợp đồng cho tính nở thành thì ghim lại hệ số.</t>
+          <t>Theo bản vẽ: 76,002 → 79,229. Thể tích thiết kế tr.64 × hệ số nở thành 1,12 (Chủ dự án quyết định 11/10/2026 giữ hệ số nở thành 1,12 cho bê tông cọc). Dự toán cũ: π × 0,6² × L × 1,12, chưa gồm bê tông đầu cọc.</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -2587,7 +2587,7 @@
       <c r="B19" s="26" t="n"/>
       <c r="C19" s="27" t="inlineStr">
         <is>
-          <t>- Bê tông 8 cọc trụ T1 L=40m (bản vẽ tr.68, gồm bê tông đầu cọc)</t>
+          <t>- Bê tông 8 cọc trụ T1 L=40m (bản vẽ tr.68, gồm bê tông đầu cọc) × hệ số nở thành 1,12</t>
         </is>
       </c>
       <c r="D19" s="28" t="inlineStr">
@@ -2608,7 +2608,7 @@
         <v>1</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="J19" s="41">
         <f>E19*F19*G19*H19*I19</f>
@@ -2618,7 +2618,7 @@
       <c r="L19" s="26" t="n"/>
       <c r="M19" s="35" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 405,343 → 367,040. Bỏ hệ số nở thành 3,5186 — lấy thể tích thiết kế tr.68.</t>
+          <t>Theo bản vẽ: 405,343 → 411,085. Thể tích thiết kế tr.68 × hệ số nở thành 1,12 (Chủ dự án quyết định 11/10/2026 giữ hệ số nở thành 1,12 cho bê tông cọc). Dự toán cũ: π × 0,6² × L × 1,12, chưa gồm bê tông đầu cọc.</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -2630,7 +2630,7 @@
       <c r="B20" s="26" t="n"/>
       <c r="C20" s="27" t="inlineStr">
         <is>
-          <t>- Bê tông 8 cọc trụ T2 L=30m (bản vẽ tr.70, gồm bê tông đầu cọc)</t>
+          <t>- Bê tông 8 cọc trụ T2 L=30m (bản vẽ tr.70, gồm bê tông đầu cọc) × hệ số nở thành 1,12</t>
         </is>
       </c>
       <c r="D20" s="28" t="inlineStr">
@@ -2651,7 +2651,7 @@
         <v>1</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="J20" s="41">
         <f>E20*F20*G20*H20*I20</f>
@@ -2661,7 +2661,7 @@
       <c r="L20" s="26" t="n"/>
       <c r="M20" s="35" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 304,007 → 277,840. Bỏ hệ số nở thành 3,5186 — lấy thể tích thiết kế tr.70.</t>
+          <t>Theo bản vẽ: 304,007 → 311,181. Thể tích thiết kế tr.70 × hệ số nở thành 1,12 (Chủ dự án quyết định 11/10/2026 giữ hệ số nở thành 1,12 cho bê tông cọc). Dự toán cũ: π × 0,6² × L × 1,12, chưa gồm bê tông đầu cọc.</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -2673,7 +2673,7 @@
       <c r="B21" s="26" t="n"/>
       <c r="C21" s="27" t="inlineStr">
         <is>
-          <t>- Bê tông 7 cọc mố M2 L=36m (bản vẽ tr.66, gồm bê tông đầu cọc)</t>
+          <t>- Bê tông 7 cọc mố M2 L=36m (bản vẽ tr.66, gồm bê tông đầu cọc) × hệ số nở thành 1,12</t>
         </is>
       </c>
       <c r="D21" s="28" t="inlineStr">
@@ -2694,7 +2694,7 @@
         <v>1</v>
       </c>
       <c r="I21" s="40" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="J21" s="41">
         <f>E21*F21*G21*H21*I21</f>
@@ -2704,7 +2704,7 @@
       <c r="L21" s="26" t="n"/>
       <c r="M21" s="35" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 319,207 → 290,920. Bỏ hệ số nở thành 3,5186 — lấy thể tích thiết kế tr.66.</t>
+          <t>Theo bản vẽ: 319,207 → 325,830. Thể tích thiết kế tr.66 × hệ số nở thành 1,12 (Chủ dự án quyết định 11/10/2026 giữ hệ số nở thành 1,12 cho bê tông cọc). Dự toán cũ: π × 0,6² × L × 1,12, chưa gồm bê tông đầu cọc.</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="E8" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 76,002 → 70,740. Bỏ hệ số I = 3,5186 (π × 1,12 nở thành): lấy thể tích thiết kế tr.64. Nếu hợp đồng cho tính nở thành thì ghim lại hệ số.</t>
+          <t>Theo bản vẽ: 76,002 → 79,229. Thể tích thiết kế tr.64 × hệ số nở thành 1,12 (Chủ dự án quyết định 11/10/2026 giữ hệ số nở thành 1,12 cho bê tông cọc). Dự toán cũ: π × 0,6² × L × 1,12, chưa gồm bê tông đầu cọc.</t>
         </is>
       </c>
       <c r="F8" s="44" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="G8" s="44" t="inlineStr">
         <is>
-          <t>70,740</t>
+          <t>79,229</t>
         </is>
       </c>
       <c r="H8" s="44" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="E9" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 405,343 → 367,040. Bỏ hệ số nở thành 3,5186 — lấy thể tích thiết kế tr.68.</t>
+          <t>Theo bản vẽ: 405,343 → 411,085. Thể tích thiết kế tr.68 × hệ số nở thành 1,12 (Chủ dự án quyết định 11/10/2026 giữ hệ số nở thành 1,12 cho bê tông cọc). Dự toán cũ: π × 0,6² × L × 1,12, chưa gồm bê tông đầu cọc.</t>
         </is>
       </c>
       <c r="F9" s="44" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="G9" s="44" t="inlineStr">
         <is>
-          <t>367,040</t>
+          <t>411,085</t>
         </is>
       </c>
       <c r="H9" s="44" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="E10" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 304,007 → 277,840. Bỏ hệ số nở thành 3,5186 — lấy thể tích thiết kế tr.70.</t>
+          <t>Theo bản vẽ: 304,007 → 311,181. Thể tích thiết kế tr.70 × hệ số nở thành 1,12 (Chủ dự án quyết định 11/10/2026 giữ hệ số nở thành 1,12 cho bê tông cọc). Dự toán cũ: π × 0,6² × L × 1,12, chưa gồm bê tông đầu cọc.</t>
         </is>
       </c>
       <c r="F10" s="44" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="G10" s="44" t="inlineStr">
         <is>
-          <t>277,840</t>
+          <t>311,181</t>
         </is>
       </c>
       <c r="H10" s="44" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="E11" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 319,207 → 290,920. Bỏ hệ số nở thành 3,5186 — lấy thể tích thiết kế tr.66.</t>
+          <t>Theo bản vẽ: 319,207 → 325,830. Thể tích thiết kế tr.66 × hệ số nở thành 1,12 (Chủ dự án quyết định 11/10/2026 giữ hệ số nở thành 1,12 cho bê tông cọc). Dự toán cũ: π × 0,6² × L × 1,12, chưa gồm bê tông đầu cọc.</t>
         </is>
       </c>
       <c r="F11" s="44" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="G11" s="44" t="inlineStr">
         <is>
-          <t>290,920</t>
+          <t>325,830</t>
         </is>
       </c>
       <c r="H11" s="44" t="inlineStr">

--- a/examples/HO_SO_CAU_KM19_529/03_KINH_TE_QS_DU_TOAN_THANH_TOAN/09_Thanh_Toan_Khoi_Luong_Phu_Luc_03a.xlsx
+++ b/examples/HO_SO_CAU_KM19_529/03_KINH_TE_QS_DU_TOAN_THANH_TOAN/09_Thanh_Toan_Khoi_Luong_Phu_Luc_03a.xlsx
@@ -2762,7 +2762,7 @@
       <c r="B23" s="26" t="n"/>
       <c r="C23" s="27" t="inlineStr">
         <is>
-          <t>- Cốt thép cọc mố M1 (3 cọc, bản vẽ tr.64 tấn/cọc)</t>
+          <t>- Cốt thép cọc mố M1 (3 cọc; tấn/cọc = bảng thép tr.64 + thép treo lồng P11)</t>
         </is>
       </c>
       <c r="D23" s="28" t="inlineStr">
@@ -2773,8 +2773,9 @@
       <c r="E23" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="F23" s="36" t="n">
-        <v>2.50753</v>
+      <c r="F23" s="36">
+        <f>2.50753+0.01646</f>
+        <v/>
       </c>
       <c r="G23" s="36" t="n">
         <v>1</v>
@@ -2793,7 +2794,7 @@
       <c r="L23" s="26" t="n"/>
       <c r="M23" s="35" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 17,667 → 7,523</t>
+          <t>Theo bản vẽ: 17,667 → 7,572</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -2805,7 +2806,7 @@
       <c r="B24" s="26" t="n"/>
       <c r="C24" s="27" t="inlineStr">
         <is>
-          <t>- Cốt thép cọc trụ T1 (8 cọc, bản vẽ tr.68 tấn/cọc)</t>
+          <t>- Cốt thép cọc trụ T1 (8 cọc; tấn/cọc = bảng thép tr.68 + thép treo lồng P11)</t>
         </is>
       </c>
       <c r="D24" s="28" t="inlineStr">
@@ -2816,8 +2817,9 @@
       <c r="E24" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="F24" s="36" t="n">
-        <v>4.82866</v>
+      <c r="F24" s="36">
+        <f>4.82866+0.01646</f>
+        <v/>
       </c>
       <c r="G24" s="36" t="n">
         <v>1</v>
@@ -2834,11 +2836,6 @@
       </c>
       <c r="K24" s="26" t="n"/>
       <c r="L24" s="26" t="n"/>
-      <c r="M24" s="35" t="inlineStr">
-        <is>
-          <t>Theo bản vẽ: 38,760 → 38,629</t>
-        </is>
-      </c>
       <c r="N24" t="n">
         <v>38.76</v>
       </c>
@@ -2848,7 +2845,7 @@
       <c r="B25" s="26" t="n"/>
       <c r="C25" s="27" t="inlineStr">
         <is>
-          <t>- Cốt thép cọc trụ T2 (8 cọc, bản vẽ tr.70 tấn/cọc)</t>
+          <t>- Cốt thép cọc trụ T2 (8 cọc; tấn/cọc = bảng thép tr.70 + thép treo lồng P11)</t>
         </is>
       </c>
       <c r="D25" s="28" t="inlineStr">
@@ -2859,8 +2856,9 @@
       <c r="E25" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="F25" s="36" t="n">
-        <v>3.67107</v>
+      <c r="F25" s="36">
+        <f>3.67107+0.01646</f>
+        <v/>
       </c>
       <c r="G25" s="36" t="n">
         <v>1</v>
@@ -2877,11 +2875,6 @@
       </c>
       <c r="K25" s="26" t="n"/>
       <c r="L25" s="26" t="n"/>
-      <c r="M25" s="35" t="inlineStr">
-        <is>
-          <t>Theo bản vẽ: 29,496 → 29,369</t>
-        </is>
-      </c>
       <c r="N25" t="n">
         <v>29.496</v>
       </c>
@@ -2891,7 +2884,7 @@
       <c r="B26" s="26" t="n"/>
       <c r="C26" s="27" t="inlineStr">
         <is>
-          <t>- Cốt thép cọc mố M2 (7 cọc, bản vẽ tr.66 tấn/cọc)</t>
+          <t>- Cốt thép cọc mố M2 (7 cọc; tấn/cọc = bảng thép tr.66 + thép treo lồng P11)</t>
         </is>
       </c>
       <c r="D26" s="28" t="inlineStr">
@@ -2902,8 +2895,9 @@
       <c r="E26" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="F26" s="36" t="n">
-        <v>4.70588</v>
+      <c r="F26" s="36">
+        <f>4.70588+0.0157</f>
+        <v/>
       </c>
       <c r="G26" s="36" t="n">
         <v>1</v>
@@ -2922,7 +2916,7 @@
       <c r="L26" s="26" t="n"/>
       <c r="M26" s="35" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 33,047 → 32,941. Tổng 4 trang cọc 108,462 t; bảng tổng hợp tr.175 ghi 108,884 t (nhóm 10&lt;D&lt;=18: 0,982 t so với 0,559 t trên các trang cọc) — xem PDF tr.175.</t>
+          <t>Khớp bản vẽ. Thép treo lồng P11-D16 (4 thanh/cọc) nằm ở bảng phụ trên từng trang cọc, không trong tổng thép chính — đã cộng. Tổng 4 loại cọc = 108,884 t, khớp bảng tổng hợp tr.175.</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -5839,7 +5833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6218,7 +6212,7 @@
       </c>
       <c r="E12" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 17,667 → 7,523</t>
+          <t>Theo bản vẽ: 17,667 → 7,572</t>
         </is>
       </c>
       <c r="F12" s="44" t="inlineStr">
@@ -6228,7 +6222,7 @@
       </c>
       <c r="G12" s="44" t="inlineStr">
         <is>
-          <t>7,523</t>
+          <t>7,572</t>
         </is>
       </c>
       <c r="H12" s="44" t="inlineStr">
@@ -6248,7 +6242,7 @@
         </is>
       </c>
       <c r="C13" s="44" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D13" s="44" t="inlineStr">
         <is>
@@ -6257,22 +6251,22 @@
       </c>
       <c r="E13" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 38,760 → 38,629</t>
+          <t>Khớp bản vẽ. Thép treo lồng P11-D16 (4 thanh/cọc) nằm ở bảng phụ trên từng trang cọc, không trong tổng thép chính — đã cộng. Tổng 4 loại cọc = 108,884 t, khớp bảng tổng hợp tr.175.</t>
         </is>
       </c>
       <c r="F13" s="44" t="inlineStr">
         <is>
-          <t>38,760</t>
+          <t>33,047</t>
         </is>
       </c>
       <c r="G13" s="44" t="inlineStr">
         <is>
-          <t>38,629</t>
+          <t>33,051</t>
         </is>
       </c>
       <c r="H13" s="44" t="inlineStr">
         <is>
-          <t>tr.68</t>
+          <t>tr.66</t>
         </is>
       </c>
       <c r="I13" s="44" t="inlineStr"/>
@@ -6287,31 +6281,31 @@
         </is>
       </c>
       <c r="C14" s="44" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D14" s="44" t="inlineStr">
         <is>
-          <t>4. Cốt thép cọc khoan nhồi D1200mm (Thép chủ D25, đai D16, D10)</t>
+          <t>5. Đập đầu cọc khoan nhồi nhô lên đáy bệ ngàm vào kết cấu</t>
         </is>
       </c>
       <c r="E14" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 29,496 → 29,369</t>
+          <t>Theo bản vẽ: 29,405 → 30,360</t>
         </is>
       </c>
       <c r="F14" s="44" t="inlineStr">
         <is>
-          <t>29,496</t>
+          <t>29,405</t>
         </is>
       </c>
       <c r="G14" s="44" t="inlineStr">
         <is>
-          <t>29,369</t>
+          <t>30,360</t>
         </is>
       </c>
       <c r="H14" s="44" t="inlineStr">
         <is>
-          <t>tr.70</t>
+          <t>tr.64</t>
         </is>
       </c>
       <c r="I14" s="44" t="inlineStr"/>
@@ -6326,31 +6320,31 @@
         </is>
       </c>
       <c r="C15" s="44" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D15" s="44" t="inlineStr">
         <is>
-          <t>4. Cốt thép cọc khoan nhồi D1200mm (Thép chủ D25, đai D16, D10)</t>
+          <t>8. Bê tông lót đáy bệ móng mác C10 dày 10cm</t>
         </is>
       </c>
       <c r="E15" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 33,047 → 32,941. Tổng 4 trang cọc 108,462 t; bảng tổng hợp tr.175 ghi 108,884 t (nhóm 10&lt;D&lt;=18: 0,982 t so với 0,559 t trên các trang cọc) — xem PDF tr.175.</t>
+          <t>Theo bản vẽ: 7,500 → 2,460</t>
         </is>
       </c>
       <c r="F15" s="44" t="inlineStr">
         <is>
-          <t>33,047</t>
+          <t>7,500</t>
         </is>
       </c>
       <c r="G15" s="44" t="inlineStr">
         <is>
-          <t>32,941</t>
+          <t>2,460</t>
         </is>
       </c>
       <c r="H15" s="44" t="inlineStr">
         <is>
-          <t>tr.66</t>
+          <t>tr.31</t>
         </is>
       </c>
       <c r="I15" s="44" t="inlineStr"/>
@@ -6365,31 +6359,31 @@
         </is>
       </c>
       <c r="C16" s="44" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D16" s="44" t="inlineStr">
         <is>
-          <t>5. Đập đầu cọc khoan nhồi nhô lên đáy bệ ngàm vào kết cấu</t>
+          <t>8. Bê tông lót đáy bệ móng mác C10 dày 10cm</t>
         </is>
       </c>
       <c r="E16" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 29,405 → 30,360</t>
+          <t>Theo bản vẽ: 9,100 → 7,090</t>
         </is>
       </c>
       <c r="F16" s="44" t="inlineStr">
         <is>
-          <t>29,405</t>
+          <t>9,100</t>
         </is>
       </c>
       <c r="G16" s="44" t="inlineStr">
         <is>
-          <t>30,360</t>
+          <t>7,090</t>
         </is>
       </c>
       <c r="H16" s="44" t="inlineStr">
         <is>
-          <t>tr.64</t>
+          <t>tr.40</t>
         </is>
       </c>
       <c r="I16" s="44" t="inlineStr"/>
@@ -6404,7 +6398,7 @@
         </is>
       </c>
       <c r="C17" s="44" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D17" s="44" t="inlineStr">
         <is>
@@ -6413,22 +6407,22 @@
       </c>
       <c r="E17" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 7,500 → 2,460</t>
+          <t>Theo bản vẽ: 8,450 → 8,770</t>
         </is>
       </c>
       <c r="F17" s="44" t="inlineStr">
         <is>
-          <t>7,500</t>
+          <t>8,450</t>
         </is>
       </c>
       <c r="G17" s="44" t="inlineStr">
         <is>
-          <t>2,460</t>
+          <t>8,770</t>
         </is>
       </c>
       <c r="H17" s="44" t="inlineStr">
         <is>
-          <t>tr.31</t>
+          <t>tr.44</t>
         </is>
       </c>
       <c r="I17" s="44" t="inlineStr"/>
@@ -6443,7 +6437,7 @@
         </is>
       </c>
       <c r="C18" s="44" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D18" s="44" t="inlineStr">
         <is>
@@ -6452,22 +6446,22 @@
       </c>
       <c r="E18" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 9,100 → 7,090</t>
+          <t>Theo bản vẽ: 8,450 → 8,770</t>
         </is>
       </c>
       <c r="F18" s="44" t="inlineStr">
         <is>
-          <t>9,100</t>
+          <t>8,450</t>
         </is>
       </c>
       <c r="G18" s="44" t="inlineStr">
         <is>
-          <t>7,090</t>
+          <t>8,770</t>
         </is>
       </c>
       <c r="H18" s="44" t="inlineStr">
         <is>
-          <t>tr.40</t>
+          <t>tr.55</t>
         </is>
       </c>
       <c r="I18" s="44" t="inlineStr"/>
@@ -6482,31 +6476,31 @@
         </is>
       </c>
       <c r="C19" s="44" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D19" s="44" t="inlineStr">
         <is>
-          <t>8. Bê tông lót đáy bệ móng mác C10 dày 10cm</t>
+          <t>9. Bê tông bệ móng mố M1, M2 và bệ trụ T1, T2 mác C30</t>
         </is>
       </c>
       <c r="E19" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 8,450 → 8,770</t>
+          <t>Khớp bản vẽ. Bản vẽ chỉ ghi bê tông bệ mố gộp 2 mố (tr.175) — dòng M2 bên dưới để 0. Tổng bê tông mố (bệ + tường thân + tường đỉnh + tường cánh + ụ) 376,357 m³ khớp tr.31 (75,12) + tr.40 (301,24).</t>
         </is>
       </c>
       <c r="F19" s="44" t="inlineStr">
         <is>
-          <t>8,450</t>
+          <t>148,988</t>
         </is>
       </c>
       <c r="G19" s="44" t="inlineStr">
         <is>
-          <t>8,770</t>
+          <t>148,992</t>
         </is>
       </c>
       <c r="H19" s="44" t="inlineStr">
         <is>
-          <t>tr.44</t>
+          <t>tr.175</t>
         </is>
       </c>
       <c r="I19" s="44" t="inlineStr"/>
@@ -6521,31 +6515,31 @@
         </is>
       </c>
       <c r="C20" s="44" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D20" s="44" t="inlineStr">
         <is>
-          <t>8. Bê tông lót đáy bệ móng mác C10 dày 10cm</t>
+          <t>9. Bê tông bệ móng mố M1, M2 và bệ trụ T1, T2 mác C30</t>
         </is>
       </c>
       <c r="E20" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 8,450 → 8,770</t>
+          <t>Theo bản vẽ: 148,990 → 0,000</t>
         </is>
       </c>
       <c r="F20" s="44" t="inlineStr">
         <is>
-          <t>8,450</t>
+          <t>148,990</t>
         </is>
       </c>
       <c r="G20" s="44" t="inlineStr">
         <is>
-          <t>8,770</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="H20" s="44" t="inlineStr">
         <is>
-          <t>tr.55</t>
+          <t>tr.175</t>
         </is>
       </c>
       <c r="I20" s="44" t="inlineStr"/>
@@ -6560,7 +6554,7 @@
         </is>
       </c>
       <c r="C21" s="44" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D21" s="44" t="inlineStr">
         <is>
@@ -6569,22 +6563,22 @@
       </c>
       <c r="E21" s="44" t="inlineStr">
         <is>
-          <t>Khớp bản vẽ. Bản vẽ chỉ ghi bê tông bệ mố gộp 2 mố (tr.175) — dòng M2 bên dưới để 0. Tổng bê tông mố (bệ + tường thân + tường đỉnh + tường cánh + ụ) 376,357 m³ khớp tr.31 (75,12) + tr.40 (301,24).</t>
+          <t>Theo bản vẽ: 184,500 → 184,240</t>
         </is>
       </c>
       <c r="F21" s="44" t="inlineStr">
         <is>
-          <t>148,988</t>
+          <t>184,500</t>
         </is>
       </c>
       <c r="G21" s="44" t="inlineStr">
         <is>
-          <t>148,992</t>
+          <t>184,240</t>
         </is>
       </c>
       <c r="H21" s="44" t="inlineStr">
         <is>
-          <t>tr.175</t>
+          <t>tr.44</t>
         </is>
       </c>
       <c r="I21" s="44" t="inlineStr"/>
@@ -6599,7 +6593,7 @@
         </is>
       </c>
       <c r="C22" s="44" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D22" s="44" t="inlineStr">
         <is>
@@ -6608,22 +6602,22 @@
       </c>
       <c r="E22" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 148,990 → 0,000</t>
+          <t>Theo bản vẽ: 184,500 → 184,240</t>
         </is>
       </c>
       <c r="F22" s="44" t="inlineStr">
         <is>
-          <t>148,990</t>
+          <t>184,500</t>
         </is>
       </c>
       <c r="G22" s="44" t="inlineStr">
         <is>
-          <t>0,000</t>
+          <t>184,240</t>
         </is>
       </c>
       <c r="H22" s="44" t="inlineStr">
         <is>
-          <t>tr.175</t>
+          <t>tr.55</t>
         </is>
       </c>
       <c r="I22" s="44" t="inlineStr"/>
@@ -6638,31 +6632,31 @@
         </is>
       </c>
       <c r="C23" s="44" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D23" s="44" t="inlineStr">
         <is>
-          <t>9. Bê tông bệ móng mố M1, M2 và bệ trụ T1, T2 mác C30</t>
+          <t>10. Bê tông thân mố chân dê M1 và mố chữ U M2 mác C30</t>
         </is>
       </c>
       <c r="E23" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 184,500 → 184,240</t>
+          <t>Theo bản vẽ: 84,600 → 168,871. Bản vẽ ghi tường thân gộp 2 mố (tr.175) — dòng M2 bên dưới để 0.</t>
         </is>
       </c>
       <c r="F23" s="44" t="inlineStr">
         <is>
-          <t>184,500</t>
+          <t>84,600</t>
         </is>
       </c>
       <c r="G23" s="44" t="inlineStr">
         <is>
-          <t>184,240</t>
+          <t>168,871</t>
         </is>
       </c>
       <c r="H23" s="44" t="inlineStr">
         <is>
-          <t>tr.44</t>
+          <t>tr.175</t>
         </is>
       </c>
       <c r="I23" s="44" t="inlineStr"/>
@@ -6677,31 +6671,31 @@
         </is>
       </c>
       <c r="C24" s="44" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D24" s="44" t="inlineStr">
         <is>
-          <t>9. Bê tông bệ móng mố M1, M2 và bệ trụ T1, T2 mác C30</t>
+          <t>10. Bê tông thân mố chân dê M1 và mố chữ U M2 mác C30</t>
         </is>
       </c>
       <c r="E24" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 184,500 → 184,240</t>
+          <t>Theo bản vẽ: 84,600 → 0,000</t>
         </is>
       </c>
       <c r="F24" s="44" t="inlineStr">
         <is>
-          <t>184,500</t>
+          <t>84,600</t>
         </is>
       </c>
       <c r="G24" s="44" t="inlineStr">
         <is>
-          <t>184,240</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="H24" s="44" t="inlineStr">
         <is>
-          <t>tr.55</t>
+          <t>tr.175</t>
         </is>
       </c>
       <c r="I24" s="44" t="inlineStr"/>
@@ -6716,26 +6710,26 @@
         </is>
       </c>
       <c r="C25" s="44" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D25" s="44" t="inlineStr">
         <is>
-          <t>10. Bê tông thân mố chân dê M1 và mố chữ U M2 mác C30</t>
+          <t>11. Bê tông tường cánh và tường đỉnh mố M1, M2 mác C30</t>
         </is>
       </c>
       <c r="E25" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 84,600 → 168,871. Bản vẽ ghi tường thân gộp 2 mố (tr.175) — dòng M2 bên dưới để 0.</t>
+          <t>Theo bản vẽ: 20,256 → 29,842. Gộp 'gờ lan can, ụ chống chuyển vị tường tai' của mố (tr.175) vào hạng mục tường cánh/tường đỉnh vì cùng mác C30 — tách mã nếu đơn giá khác.</t>
         </is>
       </c>
       <c r="F25" s="44" t="inlineStr">
         <is>
-          <t>84,600</t>
+          <t>20,256</t>
         </is>
       </c>
       <c r="G25" s="44" t="inlineStr">
         <is>
-          <t>168,871</t>
+          <t>29,842</t>
         </is>
       </c>
       <c r="H25" s="44" t="inlineStr">
@@ -6755,31 +6749,31 @@
         </is>
       </c>
       <c r="C26" s="44" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D26" s="44" t="inlineStr">
         <is>
-          <t>10. Bê tông thân mố chân dê M1 và mố chữ U M2 mác C30</t>
+          <t>12. Bê tông thân đặc trụ T1 và T2 mác C30</t>
         </is>
       </c>
       <c r="E26" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 84,600 → 0,000</t>
+          <t>Theo bản vẽ: 281,336 → 234,920. Dự toán cũ ghi H = 14,5 m; cao độ trên bản vẽ cho thân trụ T1 cao khoảng 23,35 m. Đã lấy thể tích bản vẽ.</t>
         </is>
       </c>
       <c r="F26" s="44" t="inlineStr">
         <is>
-          <t>84,600</t>
+          <t>281,336</t>
         </is>
       </c>
       <c r="G26" s="44" t="inlineStr">
         <is>
-          <t>0,000</t>
+          <t>234,920</t>
         </is>
       </c>
       <c r="H26" s="44" t="inlineStr">
         <is>
-          <t>tr.175</t>
+          <t>tr.48</t>
         </is>
       </c>
       <c r="I26" s="44" t="inlineStr"/>
@@ -6794,31 +6788,31 @@
         </is>
       </c>
       <c r="C27" s="44" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D27" s="44" t="inlineStr">
         <is>
-          <t>11. Bê tông tường cánh và tường đỉnh mố M1, M2 mác C30</t>
+          <t>12. Bê tông thân đặc trụ T1 và T2 mác C30</t>
         </is>
       </c>
       <c r="E27" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 20,256 → 29,842. Gộp 'gờ lan can, ụ chống chuyển vị tường tai' của mố (tr.175) vào hạng mục tường cánh/tường đỉnh vì cùng mác C30 — tách mã nếu đơn giá khác.</t>
+          <t>Theo bản vẽ: 221,189 → 266,790. Dự toán cũ ghi H = 11,4 m; cao độ trên bản vẽ cho thân trụ T2 cao khoảng 25,45 m. Đã lấy thể tích bản vẽ.</t>
         </is>
       </c>
       <c r="F27" s="44" t="inlineStr">
         <is>
-          <t>20,256</t>
+          <t>221,189</t>
         </is>
       </c>
       <c r="G27" s="44" t="inlineStr">
         <is>
-          <t>29,842</t>
+          <t>266,790</t>
         </is>
       </c>
       <c r="H27" s="44" t="inlineStr">
         <is>
-          <t>tr.175</t>
+          <t>tr.59</t>
         </is>
       </c>
       <c r="I27" s="44" t="inlineStr"/>
@@ -6833,31 +6827,31 @@
         </is>
       </c>
       <c r="C28" s="44" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D28" s="44" t="inlineStr">
         <is>
-          <t>12. Bê tông thân đặc trụ T1 và T2 mác C30</t>
+          <t>13. Bê tông xà mũ trụ T1, T2 mác C30</t>
         </is>
       </c>
       <c r="E28" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 281,336 → 234,920. Dự toán cũ ghi H = 14,5 m; cao độ trên bản vẽ cho thân trụ T1 cao khoảng 23,35 m. Đã lấy thể tích bản vẽ.</t>
+          <t>Theo bản vẽ: 73,062 → 72,510</t>
         </is>
       </c>
       <c r="F28" s="44" t="inlineStr">
         <is>
-          <t>281,336</t>
+          <t>73,062</t>
         </is>
       </c>
       <c r="G28" s="44" t="inlineStr">
         <is>
-          <t>234,920</t>
+          <t>72,510</t>
         </is>
       </c>
       <c r="H28" s="44" t="inlineStr">
         <is>
-          <t>tr.48</t>
+          <t>tr.51</t>
         </is>
       </c>
       <c r="I28" s="44" t="inlineStr"/>
@@ -6872,31 +6866,31 @@
         </is>
       </c>
       <c r="C29" s="44" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D29" s="44" t="inlineStr">
         <is>
-          <t>12. Bê tông thân đặc trụ T1 và T2 mác C30</t>
+          <t>13. Bê tông xà mũ trụ T1, T2 mác C30</t>
         </is>
       </c>
       <c r="E29" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 221,189 → 266,790. Dự toán cũ ghi H = 11,4 m; cao độ trên bản vẽ cho thân trụ T2 cao khoảng 25,45 m. Đã lấy thể tích bản vẽ.</t>
+          <t>Theo bản vẽ: 73,062 → 72,510</t>
         </is>
       </c>
       <c r="F29" s="44" t="inlineStr">
         <is>
-          <t>221,189</t>
+          <t>73,062</t>
         </is>
       </c>
       <c r="G29" s="44" t="inlineStr">
         <is>
-          <t>266,790</t>
+          <t>72,510</t>
         </is>
       </c>
       <c r="H29" s="44" t="inlineStr">
         <is>
-          <t>tr.59</t>
+          <t>tr.62</t>
         </is>
       </c>
       <c r="I29" s="44" t="inlineStr"/>
@@ -6911,31 +6905,31 @@
         </is>
       </c>
       <c r="C30" s="44" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D30" s="44" t="inlineStr">
         <is>
-          <t>13. Bê tông xà mũ trụ T1, T2 mác C30</t>
+          <t>14. Cốt thép mố và trụ (D&lt;=10, 10&lt;D&lt;=18, D&gt;18)</t>
         </is>
       </c>
       <c r="E30" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 73,062 → 72,510</t>
+          <t>Theo bản vẽ: 23,450 → 7,959</t>
         </is>
       </c>
       <c r="F30" s="44" t="inlineStr">
         <is>
-          <t>73,062</t>
+          <t>23,450</t>
         </is>
       </c>
       <c r="G30" s="44" t="inlineStr">
         <is>
-          <t>72,510</t>
+          <t>7,959</t>
         </is>
       </c>
       <c r="H30" s="44" t="inlineStr">
         <is>
-          <t>tr.51</t>
+          <t>tr.31</t>
         </is>
       </c>
       <c r="I30" s="44" t="inlineStr"/>
@@ -6950,31 +6944,31 @@
         </is>
       </c>
       <c r="C31" s="44" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D31" s="44" t="inlineStr">
         <is>
-          <t>13. Bê tông xà mũ trụ T1, T2 mác C30</t>
+          <t>14. Cốt thép mố và trụ (D&lt;=10, 10&lt;D&lt;=18, D&gt;18)</t>
         </is>
       </c>
       <c r="E31" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 73,062 → 72,510</t>
+          <t>Theo bản vẽ: 31,850 → 19,886. Tr.40 ghi 0 kg cho W6, W7, W9 dù dài × SL × kg/m = 237,05 kg (51,50 + 48,84 + 136,71). Chủ dự án quyết định 11/10/2026 tính các thanh này: 19,649 + 0,237 t.</t>
         </is>
       </c>
       <c r="F31" s="44" t="inlineStr">
         <is>
-          <t>73,062</t>
+          <t>31,850</t>
         </is>
       </c>
       <c r="G31" s="44" t="inlineStr">
         <is>
-          <t>72,510</t>
+          <t>19,886</t>
         </is>
       </c>
       <c r="H31" s="44" t="inlineStr">
         <is>
-          <t>tr.62</t>
+          <t>tr.40</t>
         </is>
       </c>
       <c r="I31" s="44" t="inlineStr"/>
@@ -6989,7 +6983,7 @@
         </is>
       </c>
       <c r="C32" s="44" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D32" s="44" t="inlineStr">
         <is>
@@ -6998,22 +6992,22 @@
       </c>
       <c r="E32" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 23,450 → 7,959</t>
+          <t>Theo bản vẽ: 38,600 → 61,749</t>
         </is>
       </c>
       <c r="F32" s="44" t="inlineStr">
         <is>
-          <t>23,450</t>
+          <t>38,600</t>
         </is>
       </c>
       <c r="G32" s="44" t="inlineStr">
         <is>
-          <t>7,959</t>
+          <t>61,749</t>
         </is>
       </c>
       <c r="H32" s="44" t="inlineStr">
         <is>
-          <t>tr.31</t>
+          <t>tr.44, tr.48, tr.51</t>
         </is>
       </c>
       <c r="I32" s="44" t="inlineStr"/>
@@ -7028,7 +7022,7 @@
         </is>
       </c>
       <c r="C33" s="44" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D33" s="44" t="inlineStr">
         <is>
@@ -7037,22 +7031,22 @@
       </c>
       <c r="E33" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 31,850 → 19,886. Tr.40 ghi 0 kg cho W6, W7, W9 dù dài × SL × kg/m = 237,05 kg (51,50 + 48,84 + 136,71). Chủ dự án quyết định 11/10/2026 tính các thanh này: 19,649 + 0,237 t.</t>
+          <t>Theo bản vẽ: 34,200 → 64,378</t>
         </is>
       </c>
       <c r="F33" s="44" t="inlineStr">
         <is>
-          <t>31,850</t>
+          <t>34,200</t>
         </is>
       </c>
       <c r="G33" s="44" t="inlineStr">
         <is>
-          <t>19,886</t>
+          <t>64,378</t>
         </is>
       </c>
       <c r="H33" s="44" t="inlineStr">
         <is>
-          <t>tr.40</t>
+          <t>tr.55, tr.59, tr.62</t>
         </is>
       </c>
       <c r="I33" s="44" t="inlineStr"/>
@@ -7067,31 +7061,31 @@
         </is>
       </c>
       <c r="C34" s="44" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D34" s="44" t="inlineStr">
         <is>
-          <t>14. Cốt thép mố và trụ (D&lt;=10, 10&lt;D&lt;=18, D&gt;18)</t>
+          <t>16. Cáp dự ứng lực tao xoắn 15.2mm Grade 270 kéo căng trước/sau</t>
         </is>
       </c>
       <c r="E34" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 38,600 → 61,749</t>
+          <t>Khớp bản vẽ. Dòng tiêu đề cũ ghi cứng 27,784 t, khác dòng diễn giải (15 × 1,994 = 29,91 t). Bảng tổng hợp tr.175 ghi 29,911 t — đã lấy theo bản vẽ và đổi tiêu đề thành tổng công thức.</t>
         </is>
       </c>
       <c r="F34" s="44" t="inlineStr">
         <is>
-          <t>38,600</t>
+          <t>29,910</t>
         </is>
       </c>
       <c r="G34" s="44" t="inlineStr">
         <is>
-          <t>61,749</t>
+          <t>29,911</t>
         </is>
       </c>
       <c r="H34" s="44" t="inlineStr">
         <is>
-          <t>tr.44, tr.48, tr.51</t>
+          <t>tr.175</t>
         </is>
       </c>
       <c r="I34" s="44" t="inlineStr"/>
@@ -7106,31 +7100,31 @@
         </is>
       </c>
       <c r="C35" s="44" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D35" s="44" t="inlineStr">
         <is>
-          <t>14. Cốt thép mố và trụ (D&lt;=10, 10&lt;D&lt;=18, D&gt;18)</t>
+          <t>17. Cốt thép thường dầm chủ Super-T (D10, D14, D16, D20)</t>
         </is>
       </c>
       <c r="E35" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 34,200 → 64,378</t>
+          <t>Theo bản vẽ: 90,630 → 89,690. Dòng tiêu đề cũ ghi cứng 361,596 t (= BBS cũ, gấp khoảng 4 lần bản vẽ). Số phiến 2/3/1/9 và S1B3 dùng bảng thép S1B1: chủ dự án xác nhận 11/10/2026 (sơ đồ tr.75); tổng 89,690 t khớp tr.175 (77,743 + 11,947 t).</t>
         </is>
       </c>
       <c r="F35" s="44" t="inlineStr">
         <is>
-          <t>34,200</t>
+          <t>90,630</t>
         </is>
       </c>
       <c r="G35" s="44" t="inlineStr">
         <is>
-          <t>64,378</t>
+          <t>89,690</t>
         </is>
       </c>
       <c r="H35" s="44" t="inlineStr">
         <is>
-          <t>tr.55, tr.59, tr.62</t>
+          <t>tr.88, tr.91, tr.94</t>
         </is>
       </c>
       <c r="I35" s="44" t="inlineStr"/>
@@ -7145,31 +7139,31 @@
         </is>
       </c>
       <c r="C36" s="44" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D36" s="44" t="inlineStr">
         <is>
-          <t>16. Cáp dự ứng lực tao xoắn 15.2mm Grade 270 kéo căng trước/sau</t>
+          <t>20. Bê tông dầm ngang mố và trụ mác C35</t>
         </is>
       </c>
       <c r="E36" s="44" t="inlineStr">
         <is>
-          <t>Khớp bản vẽ. Dòng tiêu đề cũ ghi cứng 27,784 t, khác dòng diễn giải (15 × 1,994 = 29,91 t). Bảng tổng hợp tr.175 ghi 29,911 t — đã lấy theo bản vẽ và đổi tiêu đề thành tổng công thức.</t>
+          <t>Theo bản vẽ: 39,852 → 19,380. Dự toán cũ: 4 dầm 12,3 × 0,45 × 1,8 m. Bản vẽ tr.96 và tr.175 ghi 19,38 m³.</t>
         </is>
       </c>
       <c r="F36" s="44" t="inlineStr">
         <is>
-          <t>29,910</t>
+          <t>39,852</t>
         </is>
       </c>
       <c r="G36" s="44" t="inlineStr">
         <is>
-          <t>29,911</t>
+          <t>19,380</t>
         </is>
       </c>
       <c r="H36" s="44" t="inlineStr">
         <is>
-          <t>tr.175</t>
+          <t>tr.96</t>
         </is>
       </c>
       <c r="I36" s="44" t="inlineStr"/>
@@ -7184,31 +7178,31 @@
         </is>
       </c>
       <c r="C37" s="44" t="n">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="D37" s="44" t="inlineStr">
         <is>
-          <t>17. Cốt thép thường dầm chủ Super-T (D10, D14, D16, D20)</t>
+          <t>23. Bê tông mối nối liên tục nhiệt đỉnh trụ T1, T2 mác C35</t>
         </is>
       </c>
       <c r="E37" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 90,630 → 89,690. Dòng tiêu đề cũ ghi cứng 361,596 t (= BBS cũ, gấp khoảng 4 lần bản vẽ). Số phiến 2/3/1/9 và S1B3 dùng bảng thép S1B1: chủ dự án xác nhận 11/10/2026 (sơ đồ tr.75); tổng 89,690 t khớp tr.175 (77,743 + 11,947 t).</t>
+          <t>Theo bản vẽ: 21,799 → 21,868</t>
         </is>
       </c>
       <c r="F37" s="44" t="inlineStr">
         <is>
-          <t>90,630</t>
+          <t>21,799</t>
         </is>
       </c>
       <c r="G37" s="44" t="inlineStr">
         <is>
-          <t>89,690</t>
+          <t>21,868</t>
         </is>
       </c>
       <c r="H37" s="44" t="inlineStr">
         <is>
-          <t>tr.88, tr.91, tr.94</t>
+          <t>tr.175</t>
         </is>
       </c>
       <c r="I37" s="44" t="inlineStr"/>
@@ -7223,31 +7217,31 @@
         </is>
       </c>
       <c r="C38" s="44" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="D38" s="44" t="inlineStr">
         <is>
-          <t>20. Bê tông dầm ngang mố và trụ mác C35</t>
+          <t>24. Cốt thép bản mặt cầu và mối nối liên tục nhiệt (D14, D16)</t>
         </is>
       </c>
       <c r="E38" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 39,852 → 19,380. Dự toán cũ: 4 dầm 12,3 × 0,45 × 1,8 m. Bản vẽ tr.96 và tr.175 ghi 19,38 m³.</t>
+          <t>Theo bản vẽ: 33,070 → 85,595. Dự toán cũ 33,07 t. Bản vẽ tr.175: 85,595 t (khớp tr.112: 2 × 25.691,33 + 25.293,79 + 2 × 4.458,97 kg).</t>
         </is>
       </c>
       <c r="F38" s="44" t="inlineStr">
         <is>
-          <t>39,852</t>
+          <t>33,070</t>
         </is>
       </c>
       <c r="G38" s="44" t="inlineStr">
         <is>
-          <t>19,380</t>
+          <t>85,595</t>
         </is>
       </c>
       <c r="H38" s="44" t="inlineStr">
         <is>
-          <t>tr.96</t>
+          <t>tr.175</t>
         </is>
       </c>
       <c r="I38" s="44" t="inlineStr"/>
@@ -7262,31 +7256,31 @@
         </is>
       </c>
       <c r="C39" s="44" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D39" s="44" t="inlineStr">
         <is>
-          <t>23. Bê tông mối nối liên tục nhiệt đỉnh trụ T1, T2 mác C35</t>
+          <t>26. Bê tông bản quá độ sau mố M1, M2 mác C25</t>
         </is>
       </c>
       <c r="E39" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 21,799 → 21,868</t>
+          <t>Theo bản vẽ: 33,691 → 29,100</t>
         </is>
       </c>
       <c r="F39" s="44" t="inlineStr">
         <is>
-          <t>21,799</t>
+          <t>33,691</t>
         </is>
       </c>
       <c r="G39" s="44" t="inlineStr">
         <is>
-          <t>21,868</t>
+          <t>29,100</t>
         </is>
       </c>
       <c r="H39" s="44" t="inlineStr">
         <is>
-          <t>tr.175</t>
+          <t>tr.126</t>
         </is>
       </c>
       <c r="I39" s="44" t="inlineStr"/>
@@ -7301,31 +7295,31 @@
         </is>
       </c>
       <c r="C40" s="44" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D40" s="44" t="inlineStr">
         <is>
-          <t>24. Cốt thép bản mặt cầu và mối nối liên tục nhiệt (D14, D16)</t>
+          <t>26. Bê tông bản quá độ sau mố M1, M2 mác C25</t>
         </is>
       </c>
       <c r="E40" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 33,070 → 85,595. Dự toán cũ 33,07 t. Bản vẽ tr.175: 85,595 t (khớp tr.112: 2 × 25.691,33 + 25.293,79 + 2 × 4.458,97 kg).</t>
+          <t>Theo bản vẽ: 33,691 → 38,280</t>
         </is>
       </c>
       <c r="F40" s="44" t="inlineStr">
         <is>
-          <t>33,070</t>
+          <t>33,691</t>
         </is>
       </c>
       <c r="G40" s="44" t="inlineStr">
         <is>
-          <t>85,595</t>
+          <t>38,280</t>
         </is>
       </c>
       <c r="H40" s="44" t="inlineStr">
         <is>
-          <t>tr.175</t>
+          <t>tr.128</t>
         </is>
       </c>
       <c r="I40" s="44" t="inlineStr"/>
@@ -7340,31 +7334,31 @@
         </is>
       </c>
       <c r="C41" s="44" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D41" s="44" t="inlineStr">
         <is>
-          <t>26. Bê tông bản quá độ sau mố M1, M2 mác C25</t>
+          <t>27. Đắp vật liệu dạng hạt chọn lọc sau mố đầm chặt K &gt;= 0.98</t>
         </is>
       </c>
       <c r="E41" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 33,691 → 29,100</t>
+          <t>Khớp bản vẽ. Dự toán cũ diễn giải 'đắp chuyển tiếp sau mố' 2 × 18 × 12,5 × 4,5 × 0,5 = 1.012,5 m³; tr.175 ghi 'vật liệu dạng hạt trong lòng mố K98' 1.012,955 m³ — xác nhận đúng hạng mục.</t>
         </is>
       </c>
       <c r="F41" s="44" t="inlineStr">
         <is>
-          <t>33,691</t>
+          <t>1.012,500</t>
         </is>
       </c>
       <c r="G41" s="44" t="inlineStr">
         <is>
-          <t>29,100</t>
+          <t>1.012,955</t>
         </is>
       </c>
       <c r="H41" s="44" t="inlineStr">
         <is>
-          <t>tr.126</t>
+          <t>tr.175</t>
         </is>
       </c>
       <c r="I41" s="44" t="inlineStr"/>
@@ -7379,33 +7373,21 @@
         </is>
       </c>
       <c r="C42" s="44" t="n">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="D42" s="44" t="inlineStr">
         <is>
-          <t>26. Bê tông bản quá độ sau mố M1, M2 mác C25</t>
+          <t>7. Đào đất đá hố móng bệ mố M1, M2 và bệ trụ T1, T2 (Link Sheet Đào Đắp)</t>
         </is>
       </c>
       <c r="E42" s="44" t="inlineStr">
         <is>
-          <t>Theo bản vẽ: 33,691 → 38,280</t>
-        </is>
-      </c>
-      <c r="F42" s="44" t="inlineStr">
-        <is>
-          <t>33,691</t>
-        </is>
-      </c>
-      <c r="G42" s="44" t="inlineStr">
-        <is>
-          <t>38,280</t>
-        </is>
-      </c>
-      <c r="H42" s="44" t="inlineStr">
-        <is>
-          <t>tr.128</t>
-        </is>
-      </c>
+          <t>Khối lượng đào lấy từ sheet đào đắp (6.245 m³) — chưa đối chiếu bản vẽ.</t>
+        </is>
+      </c>
+      <c r="F42" s="44" t="inlineStr"/>
+      <c r="G42" s="44" t="inlineStr"/>
+      <c r="H42" s="44" t="inlineStr"/>
       <c r="I42" s="44" t="inlineStr"/>
     </row>
     <row r="43">
@@ -7418,33 +7400,21 @@
         </is>
       </c>
       <c r="C43" s="44" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D43" s="44" t="inlineStr">
         <is>
-          <t>27. Đắp vật liệu dạng hạt chọn lọc sau mố đầm chặt K &gt;= 0.98</t>
+          <t>28. Bê tông gờ lan can mác C25 và lắp tay vịn thép mạ kẽm</t>
         </is>
       </c>
       <c r="E43" s="44" t="inlineStr">
         <is>
-          <t>Khớp bản vẽ. Dự toán cũ diễn giải 'đắp chuyển tiếp sau mố' 2 × 18 × 12,5 × 4,5 × 0,5 = 1.012,5 m³; tr.175 ghi 'vật liệu dạng hạt trong lòng mố K98' 1.012,955 m³ — xác nhận đúng hạng mục.</t>
-        </is>
-      </c>
-      <c r="F43" s="44" t="inlineStr">
-        <is>
-          <t>1.012,500</t>
-        </is>
-      </c>
-      <c r="G43" s="44" t="inlineStr">
-        <is>
-          <t>1.012,955</t>
-        </is>
-      </c>
-      <c r="H43" s="44" t="inlineStr">
-        <is>
-          <t>tr.175</t>
-        </is>
-      </c>
+          <t>Gờ lan can tính theo m dài (2 × 130,4 m). Bản vẽ tr.119/tr.175: bê tông 104,277 m³ C25 và cốt thép 20,069 t — thép gờ lan can chưa có trong dự toán; đơn giá 1.650.000 đ/m giống đơn giá m³.</t>
+        </is>
+      </c>
+      <c r="F43" s="44" t="inlineStr"/>
+      <c r="G43" s="44" t="inlineStr"/>
+      <c r="H43" s="44" t="inlineStr"/>
       <c r="I43" s="44" t="inlineStr"/>
     </row>
     <row r="44">
@@ -7457,16 +7427,16 @@
         </is>
       </c>
       <c r="C44" s="44" t="n">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="D44" s="44" t="inlineStr">
         <is>
-          <t>7. Đào đất đá hố móng bệ mố M1, M2 và bệ trụ T1, T2 (Link Sheet Đào Đắp)</t>
+          <t>31. Gia cố mái taluy tứ nón mố bằng đá hộc xây vữa VXM M100</t>
         </is>
       </c>
       <c r="E44" s="44" t="inlineStr">
         <is>
-          <t>Khối lượng đào lấy từ sheet đào đắp (6.245 m³) — chưa đối chiếu bản vẽ.</t>
+          <t>Tứ nón đá hộc 52,216 m³ — tr.175 ghi 'đá hộc xây vữa' 104,738 m³ và 'chân khay đá hộc' 4,0 m³ (đường sau mố). Chưa rõ tương ứng — soát PDF tr.175.</t>
         </is>
       </c>
       <c r="F44" s="44" t="inlineStr"/>
@@ -7480,20 +7450,20 @@
       </c>
       <c r="B45" s="44" t="inlineStr">
         <is>
-          <t>QS_DIEN_GIAI_CHI_TIET</t>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
         </is>
       </c>
       <c r="C45" s="44" t="n">
-        <v>92</v>
+        <v>8</v>
       </c>
       <c r="D45" s="44" t="inlineStr">
         <is>
-          <t>28. Bê tông gờ lan can mác C25 và lắp tay vịn thép mạ kẽm</t>
+          <t>1. Khoan tạo lỗ cọc khoan nhồi D1200mm vào đất và đá gốc (26 cọc)</t>
         </is>
       </c>
       <c r="E45" s="44" t="inlineStr">
         <is>
-          <t>Gờ lan can tính theo m dài (2 × 130,4 m). Bản vẽ tr.119/tr.175: bê tông 104,277 m³ C25 và cốt thép 20,069 t — thép gờ lan can chưa có trong dự toán; đơn giá 1.650.000 đ/m giống đơn giá m³.</t>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D8*1.0). Ghi chú cột L 'Nghiệm thu 100% 26 cọc' là số cũ, không cập nhật theo D — soát lại</t>
         </is>
       </c>
       <c r="F45" s="44" t="inlineStr"/>
@@ -7507,24 +7477,30 @@
       </c>
       <c r="B46" s="44" t="inlineStr">
         <is>
-          <t>QS_DIEN_GIAI_CHI_TIET</t>
+          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
         </is>
       </c>
       <c r="C46" s="44" t="n">
-        <v>98</v>
+        <v>9</v>
       </c>
       <c r="D46" s="44" t="inlineStr">
         <is>
-          <t>31. Gia cố mái taluy tứ nón mố bằng đá hộc xây vữa VXM M100</t>
+          <t>2. Hạ và nhổ ống vách thép dẫn hướng D1300mm d=8mm</t>
         </is>
       </c>
       <c r="E46" s="44" t="inlineStr">
         <is>
-          <t>Tứ nón đá hộc 52,216 m³ — tr.175 ghi 'đá hộc xây vữa' 104,738 m³ và 'chân khay đá hộc' 4,0 m³ (đường sau mố). Chưa rõ tương ứng — soát PDF tr.175.</t>
-        </is>
-      </c>
-      <c r="F46" s="44" t="inlineStr"/>
-      <c r="G46" s="44" t="inlineStr"/>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J13 → =QS_DIEN_GIAI_CHI_TIET!J12 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
+        </is>
+      </c>
+      <c r="F46" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J13</f>
+        <v/>
+      </c>
+      <c r="G46" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J12</f>
+        <v/>
+      </c>
       <c r="H46" s="44" t="inlineStr"/>
       <c r="I46" s="44" t="inlineStr"/>
     </row>
@@ -7538,16 +7514,16 @@
         </is>
       </c>
       <c r="C47" s="44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D47" s="44" t="inlineStr">
         <is>
-          <t>1. Khoan tạo lỗ cọc khoan nhồi D1200mm vào đất và đá gốc (26 cọc)</t>
+          <t>2. Hạ và nhổ ống vách thép dẫn hướng D1300mm d=8mm</t>
         </is>
       </c>
       <c r="E47" s="44" t="inlineStr">
         <is>
-          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D8*1.0). Ghi chú cột L 'Nghiệm thu 100% 26 cọc' là số cũ, không cập nhật theo D — soát lại</t>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D9*1.0)</t>
         </is>
       </c>
       <c r="F47" s="44" t="inlineStr"/>
@@ -7565,24 +7541,24 @@
         </is>
       </c>
       <c r="C48" s="44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D48" s="44" t="inlineStr">
         <is>
-          <t>2. Hạ và nhổ ống vách thép dẫn hướng D1300mm d=8mm</t>
+          <t>3. Bê tông cọc khoan nhồi C30/37 đổ bằng ống tremie</t>
         </is>
       </c>
       <c r="E48" s="44" t="inlineStr">
         <is>
-          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J13 → =QS_DIEN_GIAI_CHI_TIET!J12 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J18 → =QS_DIEN_GIAI_CHI_TIET!J17 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
         </is>
       </c>
       <c r="F48" s="44">
-        <f>QS_DIEN_GIAI_CHI_TIET!J13</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J18</f>
         <v/>
       </c>
       <c r="G48" s="44">
-        <f>QS_DIEN_GIAI_CHI_TIET!J12</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J17</f>
         <v/>
       </c>
       <c r="H48" s="44" t="inlineStr"/>
@@ -7598,16 +7574,16 @@
         </is>
       </c>
       <c r="C49" s="44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D49" s="44" t="inlineStr">
         <is>
-          <t>2. Hạ và nhổ ống vách thép dẫn hướng D1300mm d=8mm</t>
+          <t>3. Bê tông cọc khoan nhồi C30/37 đổ bằng ống tremie</t>
         </is>
       </c>
       <c r="E49" s="44" t="inlineStr">
         <is>
-          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D9*1.0)</t>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D10*1.0). Ghi chú cột L 'Đổ xong 1100.86 m3' là số cũ, không cập nhật theo D — soát lại</t>
         </is>
       </c>
       <c r="F49" s="44" t="inlineStr"/>
@@ -7625,24 +7601,24 @@
         </is>
       </c>
       <c r="C50" s="44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D50" s="44" t="inlineStr">
         <is>
-          <t>3. Bê tông cọc khoan nhồi C30/37 đổ bằng ống tremie</t>
+          <t>4. Cốt thép cọc khoan nhồi D1200mm (D25, D16, D10)</t>
         </is>
       </c>
       <c r="E50" s="44" t="inlineStr">
         <is>
-          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J18 → =QS_DIEN_GIAI_CHI_TIET!J17 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J23 → =QS_DIEN_GIAI_CHI_TIET!J22 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
         </is>
       </c>
       <c r="F50" s="44">
-        <f>QS_DIEN_GIAI_CHI_TIET!J18</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J23</f>
         <v/>
       </c>
       <c r="G50" s="44">
-        <f>QS_DIEN_GIAI_CHI_TIET!J17</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J22</f>
         <v/>
       </c>
       <c r="H50" s="44" t="inlineStr"/>
@@ -7658,16 +7634,16 @@
         </is>
       </c>
       <c r="C51" s="44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D51" s="44" t="inlineStr">
         <is>
-          <t>3. Bê tông cọc khoan nhồi C30/37 đổ bằng ống tremie</t>
+          <t>4. Cốt thép cọc khoan nhồi D1200mm (D25, D16, D10)</t>
         </is>
       </c>
       <c r="E51" s="44" t="inlineStr">
         <is>
-          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D10*1.0). Ghi chú cột L 'Đổ xong 1100.86 m3' là số cũ, không cập nhật theo D — soát lại</t>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D11*1.0). Ghi chú cột L '118.98 tấn' là số cũ, không cập nhật theo D — soát lại</t>
         </is>
       </c>
       <c r="F51" s="44" t="inlineStr"/>
@@ -7685,24 +7661,24 @@
         </is>
       </c>
       <c r="C52" s="44" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D52" s="44" t="inlineStr">
         <is>
-          <t>4. Cốt thép cọc khoan nhồi D1200mm (D25, D16, D10)</t>
+          <t>5. Đập đầu 26 cọc khoan nhồi ngàm vào đài móng</t>
         </is>
       </c>
       <c r="E52" s="44" t="inlineStr">
         <is>
-          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J23 → =QS_DIEN_GIAI_CHI_TIET!J22 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J28 → =QS_DIEN_GIAI_CHI_TIET!J27 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
         </is>
       </c>
       <c r="F52" s="44">
-        <f>QS_DIEN_GIAI_CHI_TIET!J23</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J28</f>
         <v/>
       </c>
       <c r="G52" s="44">
-        <f>QS_DIEN_GIAI_CHI_TIET!J22</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J27</f>
         <v/>
       </c>
       <c r="H52" s="44" t="inlineStr"/>
@@ -7718,16 +7694,16 @@
         </is>
       </c>
       <c r="C53" s="44" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D53" s="44" t="inlineStr">
         <is>
-          <t>4. Cốt thép cọc khoan nhồi D1200mm (D25, D16, D10)</t>
+          <t>5. Đập đầu 26 cọc khoan nhồi ngàm vào đài móng</t>
         </is>
       </c>
       <c r="E53" s="44" t="inlineStr">
         <is>
-          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D11*1.0). Ghi chú cột L '118.98 tấn' là số cũ, không cập nhật theo D — soát lại</t>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D12*1.0)</t>
         </is>
       </c>
       <c r="F53" s="44" t="inlineStr"/>
@@ -7745,24 +7721,24 @@
         </is>
       </c>
       <c r="C54" s="44" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D54" s="44" t="inlineStr">
         <is>
-          <t>5. Đập đầu 26 cọc khoan nhồi ngàm vào đài móng</t>
+          <t>6. Gói thí nghiệm kiểm soát cọc (Siêu âm 156 MC, PDA 9434kN, lấy lõi)</t>
         </is>
       </c>
       <c r="E54" s="44" t="inlineStr">
         <is>
-          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J28 → =QS_DIEN_GIAI_CHI_TIET!J27 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J30 → =QS_DIEN_GIAI_CHI_TIET!J29 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
         </is>
       </c>
       <c r="F54" s="44">
-        <f>QS_DIEN_GIAI_CHI_TIET!J28</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J30</f>
         <v/>
       </c>
       <c r="G54" s="44">
-        <f>QS_DIEN_GIAI_CHI_TIET!J27</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J29</f>
         <v/>
       </c>
       <c r="H54" s="44" t="inlineStr"/>
@@ -7778,16 +7754,16 @@
         </is>
       </c>
       <c r="C55" s="44" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D55" s="44" t="inlineStr">
         <is>
-          <t>5. Đập đầu 26 cọc khoan nhồi ngàm vào đài móng</t>
+          <t>6. Gói thí nghiệm kiểm soát cọc (Siêu âm 156 MC, PDA 9434kN, lấy lõi)</t>
         </is>
       </c>
       <c r="E55" s="44" t="inlineStr">
         <is>
-          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D12*1.0)</t>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D13*1.0)</t>
         </is>
       </c>
       <c r="F55" s="44" t="inlineStr"/>
@@ -7805,26 +7781,20 @@
         </is>
       </c>
       <c r="C56" s="44" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D56" s="44" t="inlineStr">
         <is>
-          <t>6. Gói thí nghiệm kiểm soát cọc (Siêu âm 156 MC, PDA 9434kN, lấy lõi)</t>
+          <t>7. Đào đất đá hố móng bệ mố M1, M2 và bệ trụ T1, T2</t>
         </is>
       </c>
       <c r="E56" s="44" t="inlineStr">
         <is>
-          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J30 → =QS_DIEN_GIAI_CHI_TIET!J29 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
-        </is>
-      </c>
-      <c r="F56" s="44">
-        <f>QS_DIEN_GIAI_CHI_TIET!J30</f>
-        <v/>
-      </c>
-      <c r="G56" s="44">
-        <f>QS_DIEN_GIAI_CHI_TIET!J29</f>
-        <v/>
-      </c>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D15*1.0)</t>
+        </is>
+      </c>
+      <c r="F56" s="44" t="inlineStr"/>
+      <c r="G56" s="44" t="inlineStr"/>
       <c r="H56" s="44" t="inlineStr"/>
       <c r="I56" s="44" t="inlineStr"/>
     </row>
@@ -7838,16 +7808,16 @@
         </is>
       </c>
       <c r="C57" s="44" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D57" s="44" t="inlineStr">
         <is>
-          <t>6. Gói thí nghiệm kiểm soát cọc (Siêu âm 156 MC, PDA 9434kN, lấy lõi)</t>
+          <t>8. Bê tông lót đáy bệ móng mác C10 dày 10cm</t>
         </is>
       </c>
       <c r="E57" s="44" t="inlineStr">
         <is>
-          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D13*1.0)</t>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D16*1.0). Ghi chú cột L 'Đổ xong 4 hố móng' là số cũ, không cập nhật theo D — soát lại</t>
         </is>
       </c>
       <c r="F57" s="44" t="inlineStr"/>
@@ -7865,20 +7835,26 @@
         </is>
       </c>
       <c r="C58" s="44" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D58" s="44" t="inlineStr">
         <is>
-          <t>7. Đào đất đá hố móng bệ mố M1, M2 và bệ trụ T1, T2</t>
+          <t>9. Bê tông bệ móng mố M1, M2 và bệ trụ T1, T2 mác C30</t>
         </is>
       </c>
       <c r="E58" s="44" t="inlineStr">
         <is>
-          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D15*1.0)</t>
-        </is>
-      </c>
-      <c r="F58" s="44" t="inlineStr"/>
-      <c r="G58" s="44" t="inlineStr"/>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J37 → =QS_DIEN_GIAI_CHI_TIET!J39 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
+        </is>
+      </c>
+      <c r="F58" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J37</f>
+        <v/>
+      </c>
+      <c r="G58" s="44">
+        <f>QS_DIEN_GIAI_CHI_TIET!J39</f>
+        <v/>
+      </c>
       <c r="H58" s="44" t="inlineStr"/>
       <c r="I58" s="44" t="inlineStr"/>
     </row>
@@ -7892,16 +7868,16 @@
         </is>
       </c>
       <c r="C59" s="44" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D59" s="44" t="inlineStr">
         <is>
-          <t>8. Bê tông lót đáy bệ móng mác C10 dày 10cm</t>
+          <t>9. Bê tông bệ móng mố M1, M2 và bệ trụ T1, T2 mác C30</t>
         </is>
       </c>
       <c r="E59" s="44" t="inlineStr">
         <is>
-          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D16*1.0). Ghi chú cột L 'Đổ xong 4 hố móng' là số cũ, không cập nhật theo D — soát lại</t>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D17*1.0). Ghi chú cột L '517.48 m3 đạt R28' là số cũ, không cập nhật theo D — soát lại</t>
         </is>
       </c>
       <c r="F59" s="44" t="inlineStr"/>
@@ -7919,24 +7895,24 @@
         </is>
       </c>
       <c r="C60" s="44" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D60" s="44" t="inlineStr">
         <is>
-          <t>9. Bê tông bệ móng mố M1, M2 và bệ trụ T1, T2 mác C30</t>
+          <t>10. Bê tông thân mố chân dê M1 và mố chữ U M2 mác C30</t>
         </is>
       </c>
       <c r="E60" s="44" t="inlineStr">
         <is>
-          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J37 → =QS_DIEN_GIAI_CHI_TIET!J39 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J42 → =QS_DIEN_GIAI_CHI_TIET!J44 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
         </is>
       </c>
       <c r="F60" s="44">
-        <f>QS_DIEN_GIAI_CHI_TIET!J37</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J42</f>
         <v/>
       </c>
       <c r="G60" s="44">
-        <f>QS_DIEN_GIAI_CHI_TIET!J39</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J44</f>
         <v/>
       </c>
       <c r="H60" s="44" t="inlineStr"/>
@@ -7952,16 +7928,16 @@
         </is>
       </c>
       <c r="C61" s="44" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D61" s="44" t="inlineStr">
         <is>
-          <t>9. Bê tông bệ móng mố M1, M2 và bệ trụ T1, T2 mác C30</t>
+          <t>10. Bê tông thân mố chân dê M1 và mố chữ U M2 mác C30</t>
         </is>
       </c>
       <c r="E61" s="44" t="inlineStr">
         <is>
-          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D17*1.0). Ghi chú cột L '517.48 m3 đạt R28' là số cũ, không cập nhật theo D — soát lại</t>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D18*0.8). Ghi chú cột L 'Nghiệm thu đợt 1 thân mố' là số cũ, không cập nhật theo D — soát lại</t>
         </is>
       </c>
       <c r="F61" s="44" t="inlineStr"/>
@@ -7979,24 +7955,24 @@
         </is>
       </c>
       <c r="C62" s="44" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D62" s="44" t="inlineStr">
         <is>
-          <t>10. Bê tông thân mố chân dê M1 và mố chữ U M2 mác C30</t>
+          <t>11. Bê tông thân đặc trụ T1 và T2 mác C30 (H=14.5m &amp; 11.4m)</t>
         </is>
       </c>
       <c r="E62" s="44" t="inlineStr">
         <is>
-          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J42 → =QS_DIEN_GIAI_CHI_TIET!J44 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J47 → =QS_DIEN_GIAI_CHI_TIET!J50 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
         </is>
       </c>
       <c r="F62" s="44">
-        <f>QS_DIEN_GIAI_CHI_TIET!J42</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J47</f>
         <v/>
       </c>
       <c r="G62" s="44">
-        <f>QS_DIEN_GIAI_CHI_TIET!J44</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J50</f>
         <v/>
       </c>
       <c r="H62" s="44" t="inlineStr"/>
@@ -8012,16 +7988,16 @@
         </is>
       </c>
       <c r="C63" s="44" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D63" s="44" t="inlineStr">
         <is>
-          <t>10. Bê tông thân mố chân dê M1 và mố chữ U M2 mác C30</t>
+          <t>11. Bê tông thân đặc trụ T1 và T2 mác C30</t>
         </is>
       </c>
       <c r="E63" s="44" t="inlineStr">
         <is>
-          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D18*0.8). Ghi chú cột L 'Nghiệm thu đợt 1 thân mố' là số cũ, không cập nhật theo D — soát lại</t>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D19*0.75). Ghi chú cột L 'Đổ 3/4 chiều cao trụ' là số cũ, không cập nhật theo D — soát lại</t>
         </is>
       </c>
       <c r="F63" s="44" t="inlineStr"/>
@@ -8039,24 +8015,24 @@
         </is>
       </c>
       <c r="C64" s="44" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D64" s="44" t="inlineStr">
         <is>
-          <t>11. Bê tông thân đặc trụ T1 và T2 mác C30 (H=14.5m &amp; 11.4m)</t>
+          <t>12. Cốt thép mố và trụ (D&lt;=10, 10&lt;D&lt;=18, D&gt;18)</t>
         </is>
       </c>
       <c r="E64" s="44" t="inlineStr">
         <is>
-          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J47 → =QS_DIEN_GIAI_CHI_TIET!J50 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J53 → =QS_DIEN_GIAI_CHI_TIET!J56 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
         </is>
       </c>
       <c r="F64" s="44">
-        <f>QS_DIEN_GIAI_CHI_TIET!J47</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J53</f>
         <v/>
       </c>
       <c r="G64" s="44">
-        <f>QS_DIEN_GIAI_CHI_TIET!J50</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J56</f>
         <v/>
       </c>
       <c r="H64" s="44" t="inlineStr"/>
@@ -8072,16 +8048,16 @@
         </is>
       </c>
       <c r="C65" s="44" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D65" s="44" t="inlineStr">
         <is>
-          <t>11. Bê tông thân đặc trụ T1 và T2 mác C30</t>
+          <t>12. Cốt thép mố và trụ (D&lt;=10, 10&lt;D&lt;=18, D&gt;18)</t>
         </is>
       </c>
       <c r="E65" s="44" t="inlineStr">
         <is>
-          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D19*0.75). Ghi chú cột L 'Đổ 3/4 chiều cao trụ' là số cũ, không cập nhật theo D — soát lại</t>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D20*0.8). Ghi chú cột L 'Lắp dựng nghiệm thu đợt 1' là số cũ, không cập nhật theo D — soát lại</t>
         </is>
       </c>
       <c r="F65" s="44" t="inlineStr"/>
@@ -8099,24 +8075,24 @@
         </is>
       </c>
       <c r="C66" s="44" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D66" s="44" t="inlineStr">
         <is>
-          <t>12. Cốt thép mố và trụ (D&lt;=10, 10&lt;D&lt;=18, D&gt;18)</t>
+          <t>13. Bê tông dầm chủ Super-T L=38.2m mác cao C45/55</t>
         </is>
       </c>
       <c r="E66" s="44" t="inlineStr">
         <is>
-          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J53 → =QS_DIEN_GIAI_CHI_TIET!J56 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J57 → =QS_DIEN_GIAI_CHI_TIET!J62 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
         </is>
       </c>
       <c r="F66" s="44">
-        <f>QS_DIEN_GIAI_CHI_TIET!J53</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J57</f>
         <v/>
       </c>
       <c r="G66" s="44">
-        <f>QS_DIEN_GIAI_CHI_TIET!J56</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J62</f>
         <v/>
       </c>
       <c r="H66" s="44" t="inlineStr"/>
@@ -8132,16 +8108,16 @@
         </is>
       </c>
       <c r="C67" s="44" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D67" s="44" t="inlineStr">
         <is>
-          <t>12. Cốt thép mố và trụ (D&lt;=10, 10&lt;D&lt;=18, D&gt;18)</t>
+          <t>13. Bê tông dầm chủ Super-T L=38.2m mác cao C45/55</t>
         </is>
       </c>
       <c r="E67" s="44" t="inlineStr">
         <is>
-          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D20*0.8). Ghi chú cột L 'Lắp dựng nghiệm thu đợt 1' là số cũ, không cập nhật theo D — soát lại</t>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D22*0.6). Ghi chú cột L 'Đúc xong 9/15 phiến dầm' là số cũ, không cập nhật theo D — soát lại</t>
         </is>
       </c>
       <c r="F67" s="44" t="inlineStr"/>
@@ -8159,24 +8135,24 @@
         </is>
       </c>
       <c r="C68" s="44" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D68" s="44" t="inlineStr">
         <is>
-          <t>13. Bê tông dầm chủ Super-T L=38.2m mác cao C45/55</t>
+          <t>14. Cáp dự ứng lực tao xoắn 15.2mm Grade 270 kéo căng</t>
         </is>
       </c>
       <c r="E68" s="44" t="inlineStr">
         <is>
-          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J57 → =QS_DIEN_GIAI_CHI_TIET!J62 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J59 → =QS_DIEN_GIAI_CHI_TIET!J64 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
         </is>
       </c>
       <c r="F68" s="44">
-        <f>QS_DIEN_GIAI_CHI_TIET!J57</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J59</f>
         <v/>
       </c>
       <c r="G68" s="44">
-        <f>QS_DIEN_GIAI_CHI_TIET!J62</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J64</f>
         <v/>
       </c>
       <c r="H68" s="44" t="inlineStr"/>
@@ -8192,16 +8168,16 @@
         </is>
       </c>
       <c r="C69" s="44" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D69" s="44" t="inlineStr">
         <is>
-          <t>13. Bê tông dầm chủ Super-T L=38.2m mác cao C45/55</t>
+          <t>14. Cáp dự ứng lực tao xoắn 15.2mm Grade 270 kéo căng</t>
         </is>
       </c>
       <c r="E69" s="44" t="inlineStr">
         <is>
-          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D22*0.6). Ghi chú cột L 'Đúc xong 9/15 phiến dầm' là số cũ, không cập nhật theo D — soát lại</t>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D23*0.6). Ghi chú cột L 'Căng kéo 9 phiến dầm' là số cũ, không cập nhật theo D — soát lại</t>
         </is>
       </c>
       <c r="F69" s="44" t="inlineStr"/>
@@ -8219,24 +8195,24 @@
         </is>
       </c>
       <c r="C70" s="44" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D70" s="44" t="inlineStr">
         <is>
-          <t>14. Cáp dự ứng lực tao xoắn 15.2mm Grade 270 kéo căng</t>
+          <t>15. Cốt thép thường dầm chủ Super-T (D10, D14, D16, D20)</t>
         </is>
       </c>
       <c r="E70" s="44" t="inlineStr">
         <is>
-          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J59 → =QS_DIEN_GIAI_CHI_TIET!J64 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J61 → =QS_DIEN_GIAI_CHI_TIET!J66 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
         </is>
       </c>
       <c r="F70" s="44">
-        <f>QS_DIEN_GIAI_CHI_TIET!J59</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J61</f>
         <v/>
       </c>
       <c r="G70" s="44">
-        <f>QS_DIEN_GIAI_CHI_TIET!J64</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J66</f>
         <v/>
       </c>
       <c r="H70" s="44" t="inlineStr"/>
@@ -8252,16 +8228,16 @@
         </is>
       </c>
       <c r="C71" s="44" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D71" s="44" t="inlineStr">
         <is>
-          <t>14. Cáp dự ứng lực tao xoắn 15.2mm Grade 270 kéo căng</t>
+          <t>15. Cốt thép thường dầm chủ Super-T (D10, D14, D16, D20)</t>
         </is>
       </c>
       <c r="E71" s="44" t="inlineStr">
         <is>
-          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D23*0.6). Ghi chú cột L 'Căng kéo 9 phiến dầm' là số cũ, không cập nhật theo D — soát lại</t>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D24*0.6). Ghi chú cột L '9 phiến dầm' là số cũ, không cập nhật theo D — soát lại</t>
         </is>
       </c>
       <c r="F71" s="44" t="inlineStr"/>
@@ -8279,24 +8255,24 @@
         </is>
       </c>
       <c r="C72" s="44" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D72" s="44" t="inlineStr">
         <is>
-          <t>15. Cốt thép thường dầm chủ Super-T (D10, D14, D16, D20)</t>
+          <t>16. Vận chuyển và lao lắp 15 phiến dầm Super-T (chưa thi công)</t>
         </is>
       </c>
       <c r="E72" s="44" t="inlineStr">
         <is>
-          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J61 → =QS_DIEN_GIAI_CHI_TIET!J66 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J63 → =QS_DIEN_GIAI_CHI_TIET!J68 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
         </is>
       </c>
       <c r="F72" s="44">
-        <f>QS_DIEN_GIAI_CHI_TIET!J61</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J63</f>
         <v/>
       </c>
       <c r="G72" s="44">
-        <f>QS_DIEN_GIAI_CHI_TIET!J66</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J68</f>
         <v/>
       </c>
       <c r="H72" s="44" t="inlineStr"/>
@@ -8312,16 +8288,16 @@
         </is>
       </c>
       <c r="C73" s="44" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D73" s="44" t="inlineStr">
         <is>
-          <t>15. Cốt thép thường dầm chủ Super-T (D10, D14, D16, D20)</t>
+          <t>16. Vận chuyển và lao lắp 15 phiến dầm Super-T (chưa thi công)</t>
         </is>
       </c>
       <c r="E73" s="44" t="inlineStr">
         <is>
-          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D24*0.6). Ghi chú cột L '9 phiến dầm' là số cũ, không cập nhật theo D — soát lại</t>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D25*0.0)</t>
         </is>
       </c>
       <c r="F73" s="44" t="inlineStr"/>
@@ -8339,24 +8315,24 @@
         </is>
       </c>
       <c r="C74" s="44" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D74" s="44" t="inlineStr">
         <is>
-          <t>16. Vận chuyển và lao lắp 15 phiến dầm Super-T (chưa thi công)</t>
+          <t>17. Gối chậu cao su di động đơn hướng và song hướng</t>
         </is>
       </c>
       <c r="E74" s="44" t="inlineStr">
         <is>
-          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J63 → =QS_DIEN_GIAI_CHI_TIET!J68 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J65 → =QS_DIEN_GIAI_CHI_TIET!J70 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
         </is>
       </c>
       <c r="F74" s="44">
-        <f>QS_DIEN_GIAI_CHI_TIET!J63</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J65</f>
         <v/>
       </c>
       <c r="G74" s="44">
-        <f>QS_DIEN_GIAI_CHI_TIET!J68</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J70</f>
         <v/>
       </c>
       <c r="H74" s="44" t="inlineStr"/>
@@ -8372,16 +8348,16 @@
         </is>
       </c>
       <c r="C75" s="44" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D75" s="44" t="inlineStr">
         <is>
-          <t>16. Vận chuyển và lao lắp 15 phiến dầm Super-T (chưa thi công)</t>
+          <t>17. Gối chậu cao su di động đơn hướng và song hướng</t>
         </is>
       </c>
       <c r="E75" s="44" t="inlineStr">
         <is>
-          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D25*0.0)</t>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D26*0.0)</t>
         </is>
       </c>
       <c r="F75" s="44" t="inlineStr"/>
@@ -8399,24 +8375,24 @@
         </is>
       </c>
       <c r="C76" s="44" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D76" s="44" t="inlineStr">
         <is>
-          <t>17. Gối chậu cao su di động đơn hướng và song hướng</t>
+          <t>18. Bản mặt cầu C35 và mối nối liên tục nhiệt</t>
         </is>
       </c>
       <c r="E76" s="44" t="inlineStr">
         <is>
-          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J65 → =QS_DIEN_GIAI_CHI_TIET!J70 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
+          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J74 → =QS_DIEN_GIAI_CHI_TIET!J77+QS_DIEN_GIAI_CHI_TIET!J79 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
         </is>
       </c>
       <c r="F76" s="44">
-        <f>QS_DIEN_GIAI_CHI_TIET!J65</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J74</f>
         <v/>
       </c>
       <c r="G76" s="44">
-        <f>QS_DIEN_GIAI_CHI_TIET!J70</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J77+QS_DIEN_GIAI_CHI_TIET!J79</f>
         <v/>
       </c>
       <c r="H76" s="44" t="inlineStr"/>
@@ -8432,16 +8408,16 @@
         </is>
       </c>
       <c r="C77" s="44" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D77" s="44" t="inlineStr">
         <is>
-          <t>17. Gối chậu cao su di động đơn hướng và song hướng</t>
+          <t>18. Bản mặt cầu C35 và mối nối liên tục nhiệt</t>
         </is>
       </c>
       <c r="E77" s="44" t="inlineStr">
         <is>
-          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D26*0.0)</t>
+          <t>Gộp bản mặt cầu (QS dòng 77) và liên tục nhiệt (QS dòng 79); đơn giá = bình quân gia quyền theo thành tiền 2 dòng.</t>
         </is>
       </c>
       <c r="F77" s="44" t="inlineStr"/>
@@ -8468,17 +8444,11 @@
       </c>
       <c r="E78" s="44" t="inlineStr">
         <is>
-          <t>Sửa tham chiếu QS: =QS_DIEN_GIAI_CHI_TIET!J74 → =QS_DIEN_GIAI_CHI_TIET!J77+QS_DIEN_GIAI_CHI_TIET!J79 (dòng cũ trỏ vào dòng diễn giải, không phải dòng hạng mục — đơn giá về 0)</t>
-        </is>
-      </c>
-      <c r="F78" s="44">
-        <f>QS_DIEN_GIAI_CHI_TIET!J74</f>
-        <v/>
-      </c>
-      <c r="G78" s="44">
-        <f>QS_DIEN_GIAI_CHI_TIET!J77+QS_DIEN_GIAI_CHI_TIET!J79</f>
-        <v/>
-      </c>
+          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D27*0.0)</t>
+        </is>
+      </c>
+      <c r="F78" s="44" t="inlineStr"/>
+      <c r="G78" s="44" t="inlineStr"/>
       <c r="H78" s="44" t="inlineStr"/>
       <c r="I78" s="44" t="inlineStr"/>
     </row>
@@ -8492,16 +8462,16 @@
         </is>
       </c>
       <c r="C79" s="44" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D79" s="44" t="inlineStr">
         <is>
-          <t>18. Bản mặt cầu C35 và mối nối liên tục nhiệt</t>
+          <t>TỔNG CỘNG CHI PHÍ XÂY LẮP (VNĐ). None</t>
         </is>
       </c>
       <c r="E79" s="44" t="inlineStr">
         <is>
-          <t>Gộp bản mặt cầu (QS dòng 77) và liên tục nhiệt (QS dòng 79); đơn giá = bình quân gia quyền theo thành tiền 2 dòng.</t>
+          <t>Chưa có trong 03a: bê tông tường đỉnh/tường cánh mố, xà mũ trụ, dầm ngang, bản quá độ và các hạng mục hoàn thiện (QS dòng 47, 53, 73, 86...) — kiểm tra phạm vi hợp đồng.</t>
         </is>
       </c>
       <c r="F79" s="44" t="inlineStr"/>
@@ -8509,60 +8479,6 @@
       <c r="H79" s="44" t="inlineStr"/>
       <c r="I79" s="44" t="inlineStr"/>
     </row>
-    <row r="80">
-      <c r="A80" s="44" t="n">
-        <v>77</v>
-      </c>
-      <c r="B80" s="44" t="inlineStr">
-        <is>
-          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
-        </is>
-      </c>
-      <c r="C80" s="44" t="n">
-        <v>27</v>
-      </c>
-      <c r="D80" s="44" t="inlineStr">
-        <is>
-          <t>18. Bản mặt cầu C35 và mối nối liên tục nhiệt</t>
-        </is>
-      </c>
-      <c r="E80" s="44" t="inlineStr">
-        <is>
-          <t>Tỷ lệ hoàn thành kỳ này (cột H = D × tỷ lệ) chưa có biên bản nghiệm thu kèm theo — soát và ghim. (H = =D27*0.0)</t>
-        </is>
-      </c>
-      <c r="F80" s="44" t="inlineStr"/>
-      <c r="G80" s="44" t="inlineStr"/>
-      <c r="H80" s="44" t="inlineStr"/>
-      <c r="I80" s="44" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="44" t="n">
-        <v>78</v>
-      </c>
-      <c r="B81" s="44" t="inlineStr">
-        <is>
-          <t>THANH_TOAN_KY_PHU_LUC_03A</t>
-        </is>
-      </c>
-      <c r="C81" s="44" t="n">
-        <v>28</v>
-      </c>
-      <c r="D81" s="44" t="inlineStr">
-        <is>
-          <t>TỔNG CỘNG CHI PHÍ XÂY LẮP (VNĐ). None</t>
-        </is>
-      </c>
-      <c r="E81" s="44" t="inlineStr">
-        <is>
-          <t>Chưa có trong 03a: bê tông tường đỉnh/tường cánh mố, xà mũ trụ, dầm ngang, bản quá độ và các hạng mục hoàn thiện (QS dòng 47, 53, 73, 86...) — kiểm tra phạm vi hợp đồng.</t>
-        </is>
-      </c>
-      <c r="F81" s="44" t="inlineStr"/>
-      <c r="G81" s="44" t="inlineStr"/>
-      <c r="H81" s="44" t="inlineStr"/>
-      <c r="I81" s="44" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
